--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -49051,7 +49051,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="D2117" t="n">
-        <v>21.7000007629395</v>
+        <v>21.3999996185303</v>
       </c>
       <c r="E2117" t="n">
         <v>22.2999992370605</v>
@@ -49060,6 +49060,29 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G2117" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2118" t="n">
+        <v>4305</v>
+      </c>
+      <c r="C2118" t="n">
+        <v>21.7999992370605</v>
+      </c>
+      <c r="D2118" t="n">
+        <v>21</v>
+      </c>
+      <c r="E2118" t="n">
+        <v>21.7999992370605</v>
+      </c>
+      <c r="F2118" t="n">
+        <v>21.2999992370605</v>
+      </c>
+      <c r="G2118" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -49086,6 +49086,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2119">
+      <c r="A2119" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2119" t="n">
+        <v>10589</v>
+      </c>
+      <c r="C2119" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="D2119" t="n">
+        <v>20.3999996185303</v>
+      </c>
+      <c r="E2119" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="F2119" t="n">
+        <v>20.8999996185303</v>
+      </c>
+      <c r="G2119" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -49109,6 +49109,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2120">
+      <c r="A2120" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2120" t="n">
+        <v>17499</v>
+      </c>
+      <c r="C2120" t="n">
+        <v>22.2999992370605</v>
+      </c>
+      <c r="D2120" t="n">
+        <v>20.8999996185303</v>
+      </c>
+      <c r="E2120" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2120" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="G2120" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -49132,6 +49132,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2121">
+      <c r="A2121" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2121" t="n">
+        <v>6252</v>
+      </c>
+      <c r="C2121" t="n">
+        <v>22.2000007629395</v>
+      </c>
+      <c r="D2121" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E2121" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F2121" t="n">
+        <v>22.1000003814697</v>
+      </c>
+      <c r="G2121" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -48973,22 +48973,22 @@
     </row>
     <row r="2114">
       <c r="A2114" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2114" t="n">
-        <v>15343</v>
+        <v>11079</v>
       </c>
       <c r="C2114" t="n">
-        <v>23.6000003814697</v>
+        <v>22.2000007629395</v>
       </c>
       <c r="D2114" t="n">
-        <v>22.2999992370605</v>
+        <v>21.3999996185303</v>
       </c>
       <c r="E2114" t="n">
-        <v>23.2000007629395</v>
+        <v>21.3999996185303</v>
       </c>
       <c r="F2114" t="n">
-        <v>22.3999996185303</v>
+        <v>22</v>
       </c>
       <c r="G2114" t="s">
         <v>7</v>
@@ -48996,22 +48996,22 @@
     </row>
     <row r="2115">
       <c r="A2115" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2115" t="n">
-        <v>6847</v>
+        <v>15343</v>
       </c>
       <c r="C2115" t="n">
-        <v>22.7000007629395</v>
+        <v>23.6000003814697</v>
       </c>
       <c r="D2115" t="n">
-        <v>21.7000007629395</v>
+        <v>22.2999992370605</v>
       </c>
       <c r="E2115" t="n">
-        <v>22.6000003814697</v>
+        <v>23.2000007629395</v>
       </c>
       <c r="F2115" t="n">
-        <v>21.8999996185303</v>
+        <v>22.3999996185303</v>
       </c>
       <c r="G2115" t="s">
         <v>7</v>
@@ -49019,22 +49019,22 @@
     </row>
     <row r="2116">
       <c r="A2116" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2116" t="n">
-        <v>4585</v>
+        <v>6847</v>
       </c>
       <c r="C2116" t="n">
-        <v>22.3999996185303</v>
+        <v>22.7000007629395</v>
       </c>
       <c r="D2116" t="n">
+        <v>21.7000007629395</v>
+      </c>
+      <c r="E2116" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="F2116" t="n">
         <v>21.8999996185303</v>
-      </c>
-      <c r="E2116" t="n">
-        <v>22.2000007629395</v>
-      </c>
-      <c r="F2116" t="n">
-        <v>22</v>
       </c>
       <c r="G2116" t="s">
         <v>7</v>
@@ -49042,22 +49042,22 @@
     </row>
     <row r="2117">
       <c r="A2117" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2117" t="n">
-        <v>3670</v>
+        <v>4585</v>
       </c>
       <c r="C2117" t="n">
-        <v>22.2999992370605</v>
+        <v>22.3999996185303</v>
       </c>
       <c r="D2117" t="n">
-        <v>21.3999996185303</v>
+        <v>21.8999996185303</v>
       </c>
       <c r="E2117" t="n">
-        <v>22.2999992370605</v>
+        <v>22.2000007629395</v>
       </c>
       <c r="F2117" t="n">
-        <v>21.3999996185303</v>
+        <v>22</v>
       </c>
       <c r="G2117" t="s">
         <v>7</v>
@@ -49065,22 +49065,22 @@
     </row>
     <row r="2118">
       <c r="A2118" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2118" t="n">
-        <v>4305</v>
+        <v>3670</v>
       </c>
       <c r="C2118" t="n">
-        <v>21.7999992370605</v>
+        <v>22.2999992370605</v>
       </c>
       <c r="D2118" t="n">
-        <v>21</v>
+        <v>21.3999996185303</v>
       </c>
       <c r="E2118" t="n">
-        <v>21.7999992370605</v>
+        <v>22.2999992370605</v>
       </c>
       <c r="F2118" t="n">
-        <v>21.2999992370605</v>
+        <v>21.3999996185303</v>
       </c>
       <c r="G2118" t="s">
         <v>7</v>
@@ -49088,22 +49088,22 @@
     </row>
     <row r="2119">
       <c r="A2119" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2119" t="n">
-        <v>10589</v>
+        <v>4305</v>
       </c>
       <c r="C2119" t="n">
-        <v>21.3999996185303</v>
+        <v>21.7999992370605</v>
       </c>
       <c r="D2119" t="n">
-        <v>20.3999996185303</v>
+        <v>21</v>
       </c>
       <c r="E2119" t="n">
-        <v>21.3999996185303</v>
+        <v>21.7999992370605</v>
       </c>
       <c r="F2119" t="n">
-        <v>20.8999996185303</v>
+        <v>21.2999992370605</v>
       </c>
       <c r="G2119" t="s">
         <v>7</v>
@@ -49111,22 +49111,22 @@
     </row>
     <row r="2120">
       <c r="A2120" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2120" t="n">
-        <v>17499</v>
+        <v>10589</v>
       </c>
       <c r="C2120" t="n">
-        <v>22.2999992370605</v>
+        <v>21.3999996185303</v>
       </c>
       <c r="D2120" t="n">
+        <v>20.3999996185303</v>
+      </c>
+      <c r="E2120" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="F2120" t="n">
         <v>20.8999996185303</v>
-      </c>
-      <c r="E2120" t="n">
-        <v>21</v>
-      </c>
-      <c r="F2120" t="n">
-        <v>21.3999996185303</v>
       </c>
       <c r="G2120" t="s">
         <v>7</v>
@@ -49134,24 +49134,47 @@
     </row>
     <row r="2121">
       <c r="A2121" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2121" t="n">
-        <v>6252</v>
+        <v>17499</v>
       </c>
       <c r="C2121" t="n">
+        <v>22.2999992370605</v>
+      </c>
+      <c r="D2121" t="n">
+        <v>20.8999996185303</v>
+      </c>
+      <c r="E2121" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2121" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="G2121" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2122" t="n">
+        <v>12215</v>
+      </c>
+      <c r="C2122" t="n">
+        <v>22.8999996185303</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>22</v>
+      </c>
+      <c r="E2122" t="n">
+        <v>22.1000003814697</v>
+      </c>
+      <c r="F2122" t="n">
         <v>22.2000007629395</v>
       </c>
-      <c r="D2121" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="E2121" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F2121" t="n">
-        <v>22.1000003814697</v>
-      </c>
-      <c r="G2121" t="s">
+      <c r="G2122" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -499,7 +499,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G5" t="n">
-        <v>16.4225196838379</v>
+        <v>16.4225234985352</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>17.6979999542236</v>
       </c>
       <c r="G6" t="n">
-        <v>16.2462711334229</v>
+        <v>16.2462730407715</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G8" t="n">
-        <v>16.4225196838379</v>
+        <v>16.4225234985352</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>17.75</v>
       </c>
       <c r="G14" t="n">
-        <v>16.2940082550049</v>
+        <v>16.2940063476562</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>17.8840007781982</v>
       </c>
       <c r="G25" t="n">
-        <v>16.4170150756836</v>
+        <v>16.4170169830322</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>16.3858032226562</v>
+        <v>16.3858051300049</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G30" t="n">
-        <v>16.4500637054443</v>
+        <v>16.4500617980957</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>17.8780002593994</v>
       </c>
       <c r="G31" t="n">
-        <v>16.411506652832</v>
+        <v>16.4115085601807</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G38" t="n">
-        <v>16.3674430847168</v>
+        <v>16.3674449920654</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>16.4776039123535</v>
+        <v>16.4776020050049</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G50" t="n">
-        <v>17.5883483886719</v>
+        <v>17.5883464813232</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G60" t="n">
-        <v>17.4231109619141</v>
+        <v>17.4231128692627</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>17.1201820373535</v>
+        <v>17.1201801300049</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G63" t="n">
-        <v>17.1201820373535</v>
+        <v>17.1201801300049</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>17.0742816925049</v>
+        <v>17.0742835998535</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G69" t="n">
-        <v>16.7988910675049</v>
+        <v>16.7988929748535</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>16.7988910675049</v>
+        <v>16.7988929748535</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>17.0742816925049</v>
+        <v>17.0742835998535</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>18.2280006408691</v>
       </c>
       <c r="G78" t="n">
-        <v>16.7327976226807</v>
+        <v>16.7327995300293</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G81" t="n">
-        <v>16.9090480804443</v>
+        <v>16.909049987793</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>17.8339996337891</v>
       </c>
       <c r="G92" t="n">
-        <v>16.3711166381836</v>
+        <v>16.371114730835</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G97" t="n">
-        <v>15.7615823745728</v>
+        <v>15.7615833282471</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G100" t="n">
-        <v>15.8717412948608</v>
+        <v>15.8717403411865</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G101" t="n">
-        <v>15.7707643508911</v>
+        <v>15.7707633972168</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G102" t="n">
-        <v>15.4219331741333</v>
+        <v>15.421932220459</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>16.9179992675781</v>
       </c>
       <c r="G104" t="n">
-        <v>15.5302515029907</v>
+        <v>15.5302534103394</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G105" t="n">
-        <v>15.5229091644287</v>
+        <v>15.5229110717773</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>15.2383394241333</v>
+        <v>15.238338470459</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G111" t="n">
-        <v>15.100643157959</v>
+        <v>15.1006441116333</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>16.1119995117188</v>
       </c>
       <c r="G112" t="n">
-        <v>14.7903671264648</v>
+        <v>14.7903680801392</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G114" t="n">
-        <v>14.8252506256104</v>
+        <v>14.8252515792847</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G117" t="n">
-        <v>14.9996652603149</v>
+        <v>14.9996662139893</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>14.595757484436</v>
+        <v>14.5957584381104</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G121" t="n">
-        <v>14.595757484436</v>
+        <v>14.5957584381104</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G122" t="n">
-        <v>14.595757484436</v>
+        <v>14.5957584381104</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>14.8252506256104</v>
+        <v>14.8252515792847</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G131" t="n">
-        <v>14.6600170135498</v>
+        <v>14.6600160598755</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>14.366265296936</v>
+        <v>14.3662643432617</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>15.2019996643066</v>
       </c>
       <c r="G137" t="n">
-        <v>13.9550123214722</v>
+        <v>13.9550132751465</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>14.9280004501343</v>
       </c>
       <c r="G138" t="n">
-        <v>13.7034902572632</v>
+        <v>13.7034893035889</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>15.3680000305176</v>
       </c>
       <c r="G139" t="n">
-        <v>14.1073961257935</v>
+        <v>14.1073970794678</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>15.5</v>
       </c>
       <c r="G140" t="n">
-        <v>14.2285690307617</v>
+        <v>14.228569984436</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>15.5</v>
       </c>
       <c r="G141" t="n">
-        <v>14.2285690307617</v>
+        <v>14.228569984436</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>15.5</v>
       </c>
       <c r="G142" t="n">
-        <v>14.2285690307617</v>
+        <v>14.228569984436</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>15.5</v>
       </c>
       <c r="G143" t="n">
-        <v>14.2285690307617</v>
+        <v>14.228569984436</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>15.5979995727539</v>
       </c>
       <c r="G145" t="n">
-        <v>14.3185300827026</v>
+        <v>14.318531036377</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>14.595757484436</v>
+        <v>14.5957584381104</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>14.0449752807617</v>
+        <v>14.0449743270874</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>14.503960609436</v>
+        <v>14.5039615631104</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G151" t="n">
-        <v>14.503960609436</v>
+        <v>14.5039615631104</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G152" t="n">
-        <v>14.503960609436</v>
+        <v>14.5039615631104</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>14.8252506256104</v>
+        <v>14.8252515792847</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G155" t="n">
-        <v>14.733452796936</v>
+        <v>14.7334537506104</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>14.503960609436</v>
+        <v>14.5039615631104</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>16.5179996490479</v>
       </c>
       <c r="G165" t="n">
-        <v>15.163064956665</v>
+        <v>15.1630640029907</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>14.503960609436</v>
+        <v>14.5039615631104</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>15.054744720459</v>
+        <v>15.0547437667847</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G175" t="n">
-        <v>15.3301362991333</v>
+        <v>15.3301372528076</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G176" t="n">
-        <v>15.4219331741333</v>
+        <v>15.421932220459</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G177" t="n">
-        <v>15.1924381256104</v>
+        <v>15.192440032959</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>15.6514253616333</v>
+        <v>15.651424407959</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>17</v>
       </c>
       <c r="G179" t="n">
-        <v>15.6055278778076</v>
+        <v>15.6055269241333</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>17</v>
       </c>
       <c r="G180" t="n">
-        <v>15.6055278778076</v>
+        <v>15.6055269241333</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>17</v>
       </c>
       <c r="G181" t="n">
-        <v>15.6055278778076</v>
+        <v>15.6055269241333</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G182" t="n">
-        <v>15.9268188476562</v>
+        <v>15.9268178939819</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G183" t="n">
-        <v>15.9635353088379</v>
+        <v>15.9635372161865</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G188" t="n">
-        <v>15.9268188476562</v>
+        <v>15.9268178939819</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G189" t="n">
-        <v>16.0002574920654</v>
+        <v>16.0002555847168</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G190" t="n">
-        <v>15.7799415588379</v>
+        <v>15.7799434661865</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>15.9268188476562</v>
+        <v>15.9268178939819</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G197" t="n">
-        <v>16.8539714813232</v>
+        <v>16.8539695739746</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G204" t="n">
-        <v>18.7725315093994</v>
+        <v>18.772533416748</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>21.7250003814697</v>
       </c>
       <c r="G206" t="n">
-        <v>19.9429473876953</v>
+        <v>19.9429454803467</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>19.369213104248</v>
+        <v>19.3692150115967</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G209" t="n">
-        <v>19.002025604248</v>
+        <v>19.0020275115967</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>21.6550006866455</v>
       </c>
       <c r="G212" t="n">
-        <v>19.8786888122559</v>
+        <v>19.8786907196045</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>20.2871856689453</v>
+        <v>20.2871875762939</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>23</v>
       </c>
       <c r="G215" t="n">
-        <v>21.1133613586426</v>
+        <v>21.1133594512939</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G217" t="n">
-        <v>20.3789844512939</v>
+        <v>20.3789825439453</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>22.1650009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>20.3468532562256</v>
+        <v>20.3468551635742</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>22.5249996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>20.6773242950439</v>
+        <v>20.6773223876953</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G222" t="n">
-        <v>21.3703918457031</v>
+        <v>21.3703937530518</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G225" t="n">
-        <v>21.1867961883545</v>
+        <v>21.1867980957031</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>23</v>
       </c>
       <c r="G235" t="n">
-        <v>21.1133613586426</v>
+        <v>21.1133594512939</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>23</v>
       </c>
       <c r="G238" t="n">
-        <v>21.1133613586426</v>
+        <v>21.1133594512939</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>23</v>
       </c>
       <c r="G239" t="n">
-        <v>21.1133613586426</v>
+        <v>21.1133594512939</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>23</v>
       </c>
       <c r="G243" t="n">
-        <v>21.1133613586426</v>
+        <v>21.1133594512939</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G246" t="n">
-        <v>20.5625782012939</v>
+        <v>20.5625762939453</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G248" t="n">
-        <v>20.0117931365967</v>
+        <v>20.0117950439453</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>22</v>
       </c>
       <c r="G249" t="n">
-        <v>20.1953887939453</v>
+        <v>20.1953907012939</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>22</v>
       </c>
       <c r="G250" t="n">
-        <v>20.1953887939453</v>
+        <v>20.1953907012939</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G251" t="n">
-        <v>20.0117931365967</v>
+        <v>20.0117950439453</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>22</v>
       </c>
       <c r="G252" t="n">
-        <v>20.1953887939453</v>
+        <v>20.1953907012939</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>21</v>
       </c>
       <c r="G255" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G258" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G259" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>21</v>
       </c>
       <c r="G261" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G262" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>21</v>
       </c>
       <c r="G263" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>21</v>
       </c>
       <c r="G264" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G265" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>21</v>
       </c>
       <c r="G266" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G271" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G307" t="n">
-        <v>20.2893218994141</v>
+        <v>20.2893199920654</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>21</v>
       </c>
       <c r="G309" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>21</v>
       </c>
       <c r="G311" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>21</v>
       </c>
       <c r="G312" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G313" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>21</v>
       </c>
       <c r="G315" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>21</v>
       </c>
       <c r="G316" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>21</v>
       </c>
       <c r="G317" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>19.3499984741211</v>
+        <v>19.3500003814697</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>19.3499984741211</v>
+        <v>19.3500003814697</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G320" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>21</v>
       </c>
       <c r="G321" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>21</v>
       </c>
       <c r="G324" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>19.3499984741211</v>
+        <v>19.3500003814697</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>19.1621341705322</v>
+        <v>19.1621360778809</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G334" t="n">
-        <v>18.974271774292</v>
+        <v>18.9742736816406</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>18.974271774292</v>
+        <v>18.9742736816406</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G336" t="n">
-        <v>18.974271774292</v>
+        <v>18.9742736816406</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>19.1621341705322</v>
+        <v>19.1621360778809</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>19.1621341705322</v>
+        <v>19.1621360778809</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>19.3499984741211</v>
+        <v>19.3500003814697</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G341" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G343" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>21</v>
       </c>
       <c r="G347" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G350" t="n">
-        <v>20.2893218994141</v>
+        <v>20.2893199920654</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>20.2893218994141</v>
+        <v>20.2893199920654</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>23.1072807312012</v>
+        <v>23.1072826385498</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>24.6101951599121</v>
+        <v>24.6101932525635</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>26</v>
       </c>
       <c r="G397" t="n">
-        <v>24.4223308563232</v>
+        <v>24.4223289489746</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>24.6101951599121</v>
+        <v>24.6101932525635</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G400" t="n">
-        <v>25.7373790740967</v>
+        <v>25.737377166748</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>24.7980575561523</v>
+        <v>24.798059463501</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>24.7980575561523</v>
+        <v>24.798059463501</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>23.2951431274414</v>
+        <v>23.29514503479</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>24.2344665527344</v>
+        <v>24.2344646453857</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G415" t="n">
-        <v>24.2344665527344</v>
+        <v>24.2344646453857</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G416" t="n">
-        <v>24.2344665527344</v>
+        <v>24.2344646453857</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G419" t="n">
-        <v>23.2951431274414</v>
+        <v>23.29514503479</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>23.2951431274414</v>
+        <v>23.29514503479</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G426" t="n">
-        <v>24.6101951599121</v>
+        <v>24.6101932525635</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>24.7980575561523</v>
+        <v>24.798059463501</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>26</v>
       </c>
       <c r="G435" t="n">
-        <v>24.4223308563232</v>
+        <v>24.4223289489746</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>26</v>
       </c>
       <c r="G438" t="n">
-        <v>24.4223308563232</v>
+        <v>24.4223289489746</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>24.7980575561523</v>
+        <v>24.798059463501</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>24.6101951599121</v>
+        <v>24.6101932525635</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>26</v>
       </c>
       <c r="G458" t="n">
-        <v>24.4223308563232</v>
+        <v>24.4223289489746</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G461" t="n">
-        <v>23.1072807312012</v>
+        <v>23.1072826385498</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G466" t="n">
-        <v>18.4106788635254</v>
+        <v>18.410680770874</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G471" t="n">
-        <v>16.1563110351562</v>
+        <v>16.1563129425049</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>14.2776699066162</v>
+        <v>14.2776689529419</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>14.2776699066162</v>
+        <v>14.2776689529419</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G479" t="n">
-        <v>13.9958724975586</v>
+        <v>13.9958734512329</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>15.6866502761841</v>
+        <v>15.6866512298584</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>15.6866502761841</v>
+        <v>15.6866512298584</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G487" t="n">
-        <v>16.1563110351562</v>
+        <v>16.1563129425049</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>17.25</v>
       </c>
       <c r="G490" t="n">
-        <v>16.2032775878906</v>
+        <v>16.203275680542</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>15.6866502761841</v>
+        <v>15.6866512298584</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G496" t="n">
-        <v>16.1563110351562</v>
+        <v>16.1563129425049</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>15.6866502761841</v>
+        <v>15.6866512298584</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G502" t="n">
-        <v>16.813835144043</v>
+        <v>16.8138332366943</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G509" t="n">
-        <v>17.2365303039551</v>
+        <v>17.2365283966064</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>17.1895618438721</v>
+        <v>17.1895637512207</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>16.7668685913086</v>
+        <v>16.7668704986572</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>16.7668685913086</v>
+        <v>16.7668704986572</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>17.1895618438721</v>
+        <v>17.1895637512207</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G518" t="n">
-        <v>17.2365303039551</v>
+        <v>17.2365283966064</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>18.1288814544678</v>
+        <v>18.1288833618164</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>19</v>
       </c>
       <c r="G534" t="n">
-        <v>17.8470878601074</v>
+        <v>17.8470859527588</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>18.4106788635254</v>
+        <v>18.410680770874</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>17.1895618438721</v>
+        <v>17.1895637512207</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>17.4243927001953</v>
+        <v>17.4243907928467</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G540" t="n">
-        <v>17.2365303039551</v>
+        <v>17.2365283966064</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>16.813835144043</v>
+        <v>16.8138332366943</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>17.2365303039551</v>
+        <v>17.2365283966064</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G544" t="n">
-        <v>17.4243927001953</v>
+        <v>17.4243907928467</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>18.5</v>
       </c>
       <c r="G545" t="n">
-        <v>17.3774261474609</v>
+        <v>17.3774280548096</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>19</v>
       </c>
       <c r="G546" t="n">
-        <v>17.8470878601074</v>
+        <v>17.8470859527588</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>18.5</v>
       </c>
       <c r="G548" t="n">
-        <v>17.3774261474609</v>
+        <v>17.3774280548096</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>15.75</v>
       </c>
       <c r="G567" t="n">
-        <v>14.7942962646484</v>
+        <v>14.7942953109741</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>15.75</v>
       </c>
       <c r="G580" t="n">
-        <v>14.7942962646484</v>
+        <v>14.7942953109741</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>14.4655342102051</v>
+        <v>14.4655332565308</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>15.75</v>
       </c>
       <c r="G589" t="n">
-        <v>14.7942962646484</v>
+        <v>14.7942953109741</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G591" t="n">
-        <v>14.4655342102051</v>
+        <v>14.4655332565308</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G593" t="n">
-        <v>14.1837387084961</v>
+        <v>14.1837377548218</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>13.9958724975586</v>
+        <v>13.9958734512329</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G595" t="n">
-        <v>14.042839050293</v>
+        <v>14.0428400039673</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G596" t="n">
-        <v>13.9019412994385</v>
+        <v>13.9019422531128</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>13.9019412994385</v>
+        <v>13.9019422531128</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>14.5</v>
       </c>
       <c r="G600" t="n">
-        <v>13.6201448440552</v>
+        <v>13.6201457977295</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -55596,6 +55596,32 @@
         <v>21.2000007629395</v>
       </c>
       <c r="H2124" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2125" t="n">
+        <v>34147</v>
+      </c>
+      <c r="C2125" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>21.2000007629395</v>
+      </c>
+      <c r="E2125" t="n">
+        <v>21.3999996185303</v>
+      </c>
+      <c r="F2125" t="n">
+        <v>21.8999996185303</v>
+      </c>
+      <c r="G2125" t="n">
+        <v>21.8999996185303</v>
+      </c>
+      <c r="H2125" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -55625,6 +55625,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2126">
+      <c r="A2126" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2126" t="n">
+        <v>7316</v>
+      </c>
+      <c r="C2126" t="n">
+        <v>21.8999996185303</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>21.2999992370605</v>
+      </c>
+      <c r="E2126" t="n">
+        <v>21.8999996185303</v>
+      </c>
+      <c r="F2126" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="G2126" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="H2126" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -421,7 +421,7 @@
         <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>16.5235004425049</v>
+        <v>16.5234985351562</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>17.9139995574951</v>
       </c>
       <c r="G3" t="n">
-        <v>16.4445533752441</v>
+        <v>16.4445552825928</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G9" t="n">
-        <v>16.2481079101562</v>
+        <v>16.2481098175049</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>17.75</v>
       </c>
       <c r="G14" t="n">
-        <v>16.2940063476562</v>
+        <v>16.2940082550049</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>16.2481079101562</v>
+        <v>16.2481098175049</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G16" t="n">
-        <v>16.2481079101562</v>
+        <v>16.2481098175049</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G26" t="n">
-        <v>16.4317016601562</v>
+        <v>16.4317035675049</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>16.3858051300049</v>
+        <v>16.3858032226562</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>17.8780002593994</v>
       </c>
       <c r="G31" t="n">
-        <v>16.4115085601807</v>
+        <v>16.411506652832</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>18</v>
       </c>
       <c r="G32" t="n">
-        <v>16.5235004425049</v>
+        <v>16.5234985351562</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G34" t="n">
-        <v>16.2481079101562</v>
+        <v>16.2481098175049</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>18</v>
       </c>
       <c r="G42" t="n">
-        <v>16.5235004425049</v>
+        <v>16.5234985351562</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>18.5</v>
       </c>
       <c r="G44" t="n">
-        <v>16.9824867248535</v>
+        <v>16.9824848175049</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>19</v>
       </c>
       <c r="G46" t="n">
-        <v>17.4414710998535</v>
+        <v>17.4414730072021</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>19</v>
       </c>
       <c r="G49" t="n">
-        <v>17.4414710998535</v>
+        <v>17.4414730072021</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G50" t="n">
-        <v>17.5883464813232</v>
+        <v>17.5883483886719</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G51" t="n">
-        <v>17.3955745697021</v>
+        <v>17.3955726623535</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G52" t="n">
-        <v>17.3955745697021</v>
+        <v>17.3955726623535</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>17.3955745697021</v>
+        <v>17.3955726623535</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G54" t="n">
-        <v>17.3955745697021</v>
+        <v>17.3955726623535</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>17.3955745697021</v>
+        <v>17.3955726623535</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>19</v>
       </c>
       <c r="G56" t="n">
-        <v>17.4414710998535</v>
+        <v>17.4414730072021</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>19</v>
       </c>
       <c r="G57" t="n">
-        <v>17.4414710998535</v>
+        <v>17.4414730072021</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>19</v>
       </c>
       <c r="G58" t="n">
-        <v>17.4414710998535</v>
+        <v>17.4414730072021</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>17.3496761322021</v>
+        <v>17.3496742248535</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G61" t="n">
-        <v>17.3955745697021</v>
+        <v>17.3955726623535</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>17.3037757873535</v>
+        <v>17.3037776947021</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>18.4340000152588</v>
       </c>
       <c r="G68" t="n">
-        <v>16.9218978881836</v>
+        <v>16.9218997955322</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G69" t="n">
-        <v>16.7988929748535</v>
+        <v>16.7988910675049</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>16.7988929748535</v>
+        <v>16.7988910675049</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>18.4979991912842</v>
       </c>
       <c r="G77" t="n">
-        <v>16.9806499481201</v>
+        <v>16.9806480407715</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>18.2280006408691</v>
       </c>
       <c r="G78" t="n">
-        <v>16.7327995300293</v>
+        <v>16.7327976226807</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G81" t="n">
-        <v>16.909049987793</v>
+        <v>16.9090480804443</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>18</v>
       </c>
       <c r="G82" t="n">
-        <v>16.5235004425049</v>
+        <v>16.5234985351562</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>18</v>
       </c>
       <c r="G83" t="n">
-        <v>16.5235004425049</v>
+        <v>16.5234985351562</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>18</v>
       </c>
       <c r="G84" t="n">
-        <v>16.5235004425049</v>
+        <v>16.5234985351562</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>16.2481079101562</v>
+        <v>16.2481098175049</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>17.8339996337891</v>
       </c>
       <c r="G92" t="n">
-        <v>16.371114730835</v>
+        <v>16.3711166381836</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>16.2022075653076</v>
+        <v>16.2022094726562</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G101" t="n">
-        <v>15.7707633972168</v>
+        <v>15.7707643508911</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>15.238338470459</v>
+        <v>15.2383394241333</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G108" t="n">
-        <v>14.871150970459</v>
+        <v>14.8711500167847</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>16.1119995117188</v>
       </c>
       <c r="G112" t="n">
-        <v>14.7903680801392</v>
+        <v>14.7903671264648</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G114" t="n">
-        <v>14.8252515792847</v>
+        <v>14.8252506256104</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>14.871150970459</v>
+        <v>14.8711500167847</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G123" t="n">
-        <v>14.5406799316406</v>
+        <v>14.5406808853149</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G125" t="n">
-        <v>14.871150970459</v>
+        <v>14.8711500167847</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>14.8252515792847</v>
+        <v>14.8252506256104</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G129" t="n">
-        <v>14.6691951751709</v>
+        <v>14.6691961288452</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G135" t="n">
-        <v>14.6691951751709</v>
+        <v>14.6691961288452</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>14.3662643432617</v>
+        <v>14.366265296936</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>15.2019996643066</v>
       </c>
       <c r="G137" t="n">
-        <v>13.9550132751465</v>
+        <v>13.9550142288208</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>15.5979995727539</v>
       </c>
       <c r="G145" t="n">
-        <v>14.318531036377</v>
+        <v>14.3185300827026</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G146" t="n">
-        <v>14.8160715103149</v>
+        <v>14.8160705566406</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>14.0449743270874</v>
+        <v>14.0449752807617</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>14.8252515792847</v>
+        <v>14.8252506256104</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G160" t="n">
-        <v>14.8527898788452</v>
+        <v>14.8527908325195</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>16.5179996490479</v>
       </c>
       <c r="G165" t="n">
-        <v>15.1630640029907</v>
+        <v>15.1630659103394</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G175" t="n">
-        <v>15.3301372528076</v>
+        <v>15.3301362991333</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G177" t="n">
-        <v>15.192440032959</v>
+        <v>15.1924381256104</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>15.651424407959</v>
+        <v>15.6514272689819</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G183" t="n">
-        <v>15.9635372161865</v>
+        <v>15.9635353088379</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G184" t="n">
-        <v>15.7340421676636</v>
+        <v>15.7340431213379</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G185" t="n">
-        <v>15.7524032592773</v>
+        <v>15.7524013519287</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G186" t="n">
-        <v>15.7524032592773</v>
+        <v>15.7524013519287</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G187" t="n">
-        <v>15.6238870620728</v>
+        <v>15.6238880157471</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G190" t="n">
-        <v>15.7799434661865</v>
+        <v>15.7799425125122</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>16.4317016601562</v>
+        <v>16.4317035675049</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G196" t="n">
-        <v>16.8447895050049</v>
+        <v>16.8447914123535</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G197" t="n">
-        <v>16.8539695739746</v>
+        <v>16.8539714813232</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G200" t="n">
-        <v>16.349084854126</v>
+        <v>16.3490829467773</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G201" t="n">
-        <v>16.5693969726562</v>
+        <v>16.5693988800049</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>21.7250003814697</v>
       </c>
       <c r="G206" t="n">
-        <v>19.9429454803467</v>
+        <v>19.9429473876953</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G209" t="n">
-        <v>19.0020275115967</v>
+        <v>19.0020236968994</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>21.6550006866455</v>
       </c>
       <c r="G212" t="n">
-        <v>19.8786907196045</v>
+        <v>19.8786869049072</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>22.7450008392334</v>
       </c>
       <c r="G214" t="n">
-        <v>20.8792781829834</v>
+        <v>20.879280090332</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G217" t="n">
-        <v>20.3789825439453</v>
+        <v>20.3789844512939</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>22.1650009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>20.3468551635742</v>
+        <v>20.3468532562256</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>22.5249996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>20.6773223876953</v>
+        <v>20.6773242950439</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>22.9950008392334</v>
       </c>
       <c r="G223" t="n">
-        <v>21.108772277832</v>
+        <v>21.1087703704834</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G234" t="n">
-        <v>21.2969551086426</v>
+        <v>21.2969570159912</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G246" t="n">
-        <v>20.5625762939453</v>
+        <v>20.5625782012939</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>19.8281993865967</v>
+        <v>19.8282012939453</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>22</v>
       </c>
       <c r="G249" t="n">
-        <v>20.1953907012939</v>
+        <v>20.1953887939453</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>22</v>
       </c>
       <c r="G250" t="n">
-        <v>20.1953907012939</v>
+        <v>20.1953887939453</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>22</v>
       </c>
       <c r="G252" t="n">
-        <v>20.1953907012939</v>
+        <v>20.1953887939453</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>21</v>
       </c>
       <c r="G255" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G258" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G259" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>21</v>
       </c>
       <c r="G261" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G262" t="n">
-        <v>19.53786277771</v>
+        <v>19.5378646850586</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>21</v>
       </c>
       <c r="G263" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>21</v>
       </c>
       <c r="G264" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G265" t="n">
-        <v>19.53786277771</v>
+        <v>19.5378646850586</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>21</v>
       </c>
       <c r="G266" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G271" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G307" t="n">
-        <v>20.2893199920654</v>
+        <v>20.2893218994141</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>21</v>
       </c>
       <c r="G309" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>21</v>
       </c>
       <c r="G311" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>21</v>
       </c>
       <c r="G312" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G313" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>21</v>
       </c>
       <c r="G315" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>21</v>
       </c>
       <c r="G316" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>21</v>
       </c>
       <c r="G317" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>19.3500003814697</v>
+        <v>19.3499984741211</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>19.3500003814697</v>
+        <v>19.3499984741211</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G320" t="n">
-        <v>19.53786277771</v>
+        <v>19.5378646850586</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>21</v>
       </c>
       <c r="G321" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>21</v>
       </c>
       <c r="G324" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>19.3500003814697</v>
+        <v>19.3499984741211</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>19.1621360778809</v>
+        <v>19.1621341705322</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G334" t="n">
-        <v>18.9742736816406</v>
+        <v>18.974271774292</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>18.9742736816406</v>
+        <v>18.974271774292</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G336" t="n">
-        <v>18.9742736816406</v>
+        <v>18.974271774292</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>19.1621360778809</v>
+        <v>19.1621341705322</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>19.1621360778809</v>
+        <v>19.1621341705322</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>19.3500003814697</v>
+        <v>19.3499984741211</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>19.53786277771</v>
+        <v>19.5378646850586</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G341" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G343" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>21</v>
       </c>
       <c r="G347" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G350" t="n">
-        <v>20.2893199920654</v>
+        <v>20.2893218994141</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>20.2893199920654</v>
+        <v>20.2893218994141</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>23.1072826385498</v>
+        <v>23.1072807312012</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>24.6101932525635</v>
+        <v>24.6101951599121</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>26</v>
       </c>
       <c r="G397" t="n">
-        <v>24.4223289489746</v>
+        <v>24.4223308563232</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>24.6101932525635</v>
+        <v>24.6101951599121</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G400" t="n">
-        <v>25.737377166748</v>
+        <v>25.7373790740967</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>24.798059463501</v>
+        <v>24.7980575561523</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>24.798059463501</v>
+        <v>24.7980575561523</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>23.29514503479</v>
+        <v>23.2951431274414</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>24.2344646453857</v>
+        <v>24.2344665527344</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G415" t="n">
-        <v>24.2344646453857</v>
+        <v>24.2344665527344</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G416" t="n">
-        <v>24.2344646453857</v>
+        <v>24.2344665527344</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G419" t="n">
-        <v>23.29514503479</v>
+        <v>23.2951431274414</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>23.29514503479</v>
+        <v>23.2951431274414</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G426" t="n">
-        <v>24.6101932525635</v>
+        <v>24.6101951599121</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>24.798059463501</v>
+        <v>24.7980575561523</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>26</v>
       </c>
       <c r="G435" t="n">
-        <v>24.4223289489746</v>
+        <v>24.4223308563232</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>26</v>
       </c>
       <c r="G438" t="n">
-        <v>24.4223289489746</v>
+        <v>24.4223308563232</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>24.798059463501</v>
+        <v>24.7980575561523</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>24.6101932525635</v>
+        <v>24.6101951599121</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>26</v>
       </c>
       <c r="G458" t="n">
-        <v>24.4223289489746</v>
+        <v>24.4223308563232</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G461" t="n">
-        <v>23.1072826385498</v>
+        <v>23.1072807312012</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>19.53786277771</v>
+        <v>19.5378646850586</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G466" t="n">
-        <v>18.410680770874</v>
+        <v>18.4106788635254</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G471" t="n">
-        <v>16.1563129425049</v>
+        <v>16.1563110351562</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>14.2776689529419</v>
+        <v>14.2776699066162</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>14.2776689529419</v>
+        <v>14.2776699066162</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G479" t="n">
-        <v>13.9958734512329</v>
+        <v>13.9958724975586</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>15.6866512298584</v>
+        <v>15.6866502761841</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>15.6866512298584</v>
+        <v>15.6866502761841</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G487" t="n">
-        <v>16.1563129425049</v>
+        <v>16.1563110351562</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>17.25</v>
       </c>
       <c r="G490" t="n">
-        <v>16.203275680542</v>
+        <v>16.2032775878906</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>15.6866512298584</v>
+        <v>15.6866502761841</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G496" t="n">
-        <v>16.1563129425049</v>
+        <v>16.1563110351562</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>15.6866512298584</v>
+        <v>15.6866502761841</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G502" t="n">
-        <v>16.8138332366943</v>
+        <v>16.813835144043</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G509" t="n">
-        <v>17.2365283966064</v>
+        <v>17.2365303039551</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>17.1895637512207</v>
+        <v>17.1895618438721</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>16.7668704986572</v>
+        <v>16.7668685913086</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>16.7668704986572</v>
+        <v>16.7668685913086</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>17.1895637512207</v>
+        <v>17.1895618438721</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G518" t="n">
-        <v>17.2365283966064</v>
+        <v>17.2365303039551</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>18.1288833618164</v>
+        <v>18.1288814544678</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>19</v>
       </c>
       <c r="G534" t="n">
-        <v>17.8470859527588</v>
+        <v>17.8470878601074</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>18.410680770874</v>
+        <v>18.4106788635254</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>17.1895637512207</v>
+        <v>17.1895618438721</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>17.4243907928467</v>
+        <v>17.4243927001953</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G540" t="n">
-        <v>17.2365283966064</v>
+        <v>17.2365303039551</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>16.8138332366943</v>
+        <v>16.813835144043</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>17.2365283966064</v>
+        <v>17.2365303039551</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G544" t="n">
-        <v>17.4243907928467</v>
+        <v>17.4243927001953</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>18.5</v>
       </c>
       <c r="G545" t="n">
-        <v>17.3774280548096</v>
+        <v>17.3774261474609</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>19</v>
       </c>
       <c r="G546" t="n">
-        <v>17.8470859527588</v>
+        <v>17.8470878601074</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>18.5</v>
       </c>
       <c r="G548" t="n">
-        <v>17.3774280548096</v>
+        <v>17.3774261474609</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>15.75</v>
       </c>
       <c r="G567" t="n">
-        <v>14.7942953109741</v>
+        <v>14.7942962646484</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>15.75</v>
       </c>
       <c r="G580" t="n">
-        <v>14.7942953109741</v>
+        <v>14.7942962646484</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>14.4655332565308</v>
+        <v>14.4655342102051</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>15.75</v>
       </c>
       <c r="G589" t="n">
-        <v>14.7942953109741</v>
+        <v>14.7942962646484</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G591" t="n">
-        <v>14.4655332565308</v>
+        <v>14.4655342102051</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G593" t="n">
-        <v>14.1837377548218</v>
+        <v>14.1837387084961</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>13.9958734512329</v>
+        <v>13.9958724975586</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G595" t="n">
-        <v>14.0428400039673</v>
+        <v>14.042839050293</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G596" t="n">
-        <v>13.9019422531128</v>
+        <v>13.9019412994385</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>13.9019422531128</v>
+        <v>13.9019412994385</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>14.5</v>
       </c>
       <c r="G600" t="n">
-        <v>13.6201457977295</v>
+        <v>13.6201448440552</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -55648,6 +55648,32 @@
         <v>21.6000003814697</v>
       </c>
       <c r="H2126" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2127" t="n">
+        <v>26277</v>
+      </c>
+      <c r="C2127" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="D2127" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="E2127" t="n">
+        <v>21.6000003814697</v>
+      </c>
+      <c r="F2127" t="n">
+        <v>22</v>
+      </c>
+      <c r="G2127" t="n">
+        <v>22</v>
+      </c>
+      <c r="H2127" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -421,7 +421,7 @@
         <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>16.5234985351562</v>
+        <v>16.5235004425049</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>17.9139995574951</v>
       </c>
       <c r="G3" t="n">
-        <v>16.4445552825928</v>
+        <v>16.4445533752441</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G5" t="n">
-        <v>16.4225234985352</v>
+        <v>16.4225215911865</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>17.6979999542236</v>
       </c>
       <c r="G6" t="n">
-        <v>16.2462730407715</v>
+        <v>16.2462711334229</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G7" t="n">
-        <v>16.2848262786865</v>
+        <v>16.2848281860352</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G8" t="n">
-        <v>16.4225234985352</v>
+        <v>16.4225215911865</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G9" t="n">
-        <v>16.2481098175049</v>
+        <v>16.2481079101562</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>16.2481098175049</v>
+        <v>16.2481079101562</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G16" t="n">
-        <v>16.2481098175049</v>
+        <v>16.2481079101562</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G26" t="n">
-        <v>16.4317035675049</v>
+        <v>16.4317016601562</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>16.3858032226562</v>
+        <v>16.3858051300049</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>18</v>
       </c>
       <c r="G32" t="n">
-        <v>16.5234985351562</v>
+        <v>16.5235004425049</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G34" t="n">
-        <v>16.2481098175049</v>
+        <v>16.2481079101562</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>18</v>
       </c>
       <c r="G42" t="n">
-        <v>16.5234985351562</v>
+        <v>16.5235004425049</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>16.4776020050049</v>
+        <v>16.4776039123535</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>19</v>
       </c>
       <c r="G46" t="n">
-        <v>17.4414730072021</v>
+        <v>17.4414710998535</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>19</v>
       </c>
       <c r="G49" t="n">
-        <v>17.4414730072021</v>
+        <v>17.4414710998535</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G51" t="n">
-        <v>17.3955726623535</v>
+        <v>17.3955745697021</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G52" t="n">
-        <v>17.3955726623535</v>
+        <v>17.3955745697021</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>17.3955726623535</v>
+        <v>17.3955745697021</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G54" t="n">
-        <v>17.3955726623535</v>
+        <v>17.3955745697021</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G55" t="n">
-        <v>17.3955726623535</v>
+        <v>17.3955745697021</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>19</v>
       </c>
       <c r="G56" t="n">
-        <v>17.4414730072021</v>
+        <v>17.4414710998535</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>19</v>
       </c>
       <c r="G57" t="n">
-        <v>17.4414730072021</v>
+        <v>17.4414710998535</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>19</v>
       </c>
       <c r="G58" t="n">
-        <v>17.4414730072021</v>
+        <v>17.4414710998535</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>17.3496742248535</v>
+        <v>17.3496761322021</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G60" t="n">
-        <v>17.4231128692627</v>
+        <v>17.4231109619141</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G61" t="n">
-        <v>17.3955726623535</v>
+        <v>17.3955745697021</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>17.1201801300049</v>
+        <v>17.1201820373535</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G63" t="n">
-        <v>17.1201801300049</v>
+        <v>17.1201820373535</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>17.3037776947021</v>
+        <v>17.3037757873535</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>18.4340000152588</v>
       </c>
       <c r="G68" t="n">
-        <v>16.9218997955322</v>
+        <v>16.9218978881836</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>18.4979991912842</v>
       </c>
       <c r="G77" t="n">
-        <v>16.9806480407715</v>
+        <v>16.9806499481201</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>18.2280006408691</v>
       </c>
       <c r="G78" t="n">
-        <v>16.7327976226807</v>
+        <v>16.7327995300293</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>18.4099998474121</v>
       </c>
       <c r="G79" t="n">
-        <v>16.8998680114746</v>
+        <v>16.899866104126</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>18</v>
       </c>
       <c r="G82" t="n">
-        <v>16.5234985351562</v>
+        <v>16.5235004425049</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>18</v>
       </c>
       <c r="G83" t="n">
-        <v>16.5234985351562</v>
+        <v>16.5235004425049</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>18</v>
       </c>
       <c r="G84" t="n">
-        <v>16.5234985351562</v>
+        <v>16.5235004425049</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G85" t="n">
-        <v>16.5216636657715</v>
+        <v>16.5216655731201</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G86" t="n">
-        <v>16.5216636657715</v>
+        <v>16.5216655731201</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G87" t="n">
-        <v>16.5216636657715</v>
+        <v>16.5216655731201</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G88" t="n">
-        <v>16.5216636657715</v>
+        <v>16.5216655731201</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G89" t="n">
-        <v>16.5216636657715</v>
+        <v>16.5216655731201</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G90" t="n">
-        <v>16.5216636657715</v>
+        <v>16.5216655731201</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>16.2481098175049</v>
+        <v>16.2481079101562</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G96" t="n">
-        <v>16.2848262786865</v>
+        <v>16.2848281860352</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>17.1480007171631</v>
       </c>
       <c r="G99" t="n">
-        <v>15.7413873672485</v>
+        <v>15.7413892745972</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G101" t="n">
-        <v>15.7707643508911</v>
+        <v>15.7707633972168</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G102" t="n">
-        <v>15.421932220459</v>
+        <v>15.4219331741333</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>16.9179992675781</v>
       </c>
       <c r="G104" t="n">
-        <v>15.5302534103394</v>
+        <v>15.530252456665</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G107" t="n">
-        <v>14.9721260070801</v>
+        <v>14.9721250534058</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G108" t="n">
-        <v>14.8711500167847</v>
+        <v>14.871150970459</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>16.25</v>
       </c>
       <c r="G110" t="n">
-        <v>14.9170484542847</v>
+        <v>14.9170475006104</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>16.1119995117188</v>
       </c>
       <c r="G112" t="n">
-        <v>14.7903671264648</v>
+        <v>14.7903680801392</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>16.25</v>
       </c>
       <c r="G115" t="n">
-        <v>14.9170484542847</v>
+        <v>14.9170475006104</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>14.8711500167847</v>
+        <v>14.871150970459</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G123" t="n">
-        <v>14.5406808853149</v>
+        <v>14.5406799316406</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G125" t="n">
-        <v>14.8711500167847</v>
+        <v>14.871150970459</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G131" t="n">
-        <v>14.6600160598755</v>
+        <v>14.6600170135498</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>14.366265296936</v>
+        <v>14.3662643432617</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>15.2019996643066</v>
       </c>
       <c r="G137" t="n">
-        <v>13.9550142288208</v>
+        <v>13.9550132751465</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G146" t="n">
-        <v>14.8160705566406</v>
+        <v>14.8160715103149</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>14.0449752807617</v>
+        <v>14.0449743270874</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>14.5039615631104</v>
+        <v>14.503960609436</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G151" t="n">
-        <v>14.5039615631104</v>
+        <v>14.503960609436</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G152" t="n">
-        <v>14.5039615631104</v>
+        <v>14.503960609436</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G155" t="n">
-        <v>14.7334537506104</v>
+        <v>14.733452796936</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>14.5039615631104</v>
+        <v>14.503960609436</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>16.25</v>
       </c>
       <c r="G159" t="n">
-        <v>14.9170484542847</v>
+        <v>14.9170475006104</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G160" t="n">
-        <v>14.8527908325195</v>
+        <v>14.8527898788452</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>16.5179996490479</v>
       </c>
       <c r="G165" t="n">
-        <v>15.1630659103394</v>
+        <v>15.163064956665</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>14.5039615631104</v>
+        <v>14.503960609436</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>16.25</v>
       </c>
       <c r="G169" t="n">
-        <v>14.9170484542847</v>
+        <v>14.9170475006104</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>16.25</v>
       </c>
       <c r="G170" t="n">
-        <v>14.9170484542847</v>
+        <v>14.9170475006104</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>15.0547437667847</v>
+        <v>15.054744720459</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G176" t="n">
-        <v>15.421932220459</v>
+        <v>15.4219331741333</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G177" t="n">
-        <v>15.1924381256104</v>
+        <v>15.1924390792847</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>15.6514272689819</v>
+        <v>15.6514263153076</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G184" t="n">
-        <v>15.7340431213379</v>
+        <v>15.7340421676636</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G185" t="n">
-        <v>15.7524013519287</v>
+        <v>15.7524032592773</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G186" t="n">
-        <v>15.7524013519287</v>
+        <v>15.7524032592773</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G187" t="n">
-        <v>15.6238880157471</v>
+        <v>15.6238870620728</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G190" t="n">
-        <v>15.7799425125122</v>
+        <v>15.7799415588379</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>16.4317035675049</v>
+        <v>16.4317016601562</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G196" t="n">
-        <v>16.8447914123535</v>
+        <v>16.8447895050049</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G197" t="n">
-        <v>16.8539714813232</v>
+        <v>16.8539695739746</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G200" t="n">
-        <v>16.3490829467773</v>
+        <v>16.349084854126</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G201" t="n">
-        <v>16.5693988800049</v>
+        <v>16.5693969726562</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G204" t="n">
-        <v>18.772533416748</v>
+        <v>18.7725315093994</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>21.7250003814697</v>
       </c>
       <c r="G206" t="n">
-        <v>19.9429473876953</v>
+        <v>19.9429454803467</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>19.3692150115967</v>
+        <v>19.369213104248</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G209" t="n">
-        <v>19.0020236968994</v>
+        <v>19.0020275115967</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>20.6800003051758</v>
       </c>
       <c r="G210" t="n">
-        <v>18.9836654663086</v>
+        <v>18.9836673736572</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>21.6550006866455</v>
       </c>
       <c r="G212" t="n">
-        <v>19.8786869049072</v>
+        <v>19.8786888122559</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>22.7450008392334</v>
       </c>
       <c r="G214" t="n">
-        <v>20.879280090332</v>
+        <v>20.8792781829834</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>23</v>
       </c>
       <c r="G215" t="n">
-        <v>21.1133594512939</v>
+        <v>21.1133613586426</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G217" t="n">
-        <v>20.3789844512939</v>
+        <v>20.3789825439453</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>22.1650009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>20.3468532562256</v>
+        <v>20.3468551635742</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>23.2950000762939</v>
       </c>
       <c r="G224" t="n">
-        <v>21.384162902832</v>
+        <v>21.3841648101807</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G226" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G234" t="n">
-        <v>21.2969570159912</v>
+        <v>21.2969551086426</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>23</v>
       </c>
       <c r="G235" t="n">
-        <v>21.1133594512939</v>
+        <v>21.1133613586426</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G237" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>23</v>
       </c>
       <c r="G238" t="n">
-        <v>21.1133594512939</v>
+        <v>21.1133613586426</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>23</v>
       </c>
       <c r="G239" t="n">
-        <v>21.1133594512939</v>
+        <v>21.1133613586426</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G240" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>23</v>
       </c>
       <c r="G243" t="n">
-        <v>21.1133594512939</v>
+        <v>21.1133613586426</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G246" t="n">
-        <v>20.5625782012939</v>
+        <v>20.5625762939453</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>19.8282012939453</v>
+        <v>19.8281993865967</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G248" t="n">
-        <v>20.0117950439453</v>
+        <v>20.0117931365967</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G251" t="n">
-        <v>20.0117950439453</v>
+        <v>20.0117931365967</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>21</v>
       </c>
       <c r="G255" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G258" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G259" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>21</v>
       </c>
       <c r="G261" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G262" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>21</v>
       </c>
       <c r="G263" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>21</v>
       </c>
       <c r="G264" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G265" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>21</v>
       </c>
       <c r="G266" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G271" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G307" t="n">
-        <v>20.2893218994141</v>
+        <v>20.2893199920654</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>21</v>
       </c>
       <c r="G309" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>21</v>
       </c>
       <c r="G311" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>21</v>
       </c>
       <c r="G312" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G313" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>21</v>
       </c>
       <c r="G315" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>21</v>
       </c>
       <c r="G316" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>21</v>
       </c>
       <c r="G317" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>19.3499984741211</v>
+        <v>19.3500003814697</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>19.3499984741211</v>
+        <v>19.3500003814697</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G320" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>21</v>
       </c>
       <c r="G321" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>21</v>
       </c>
       <c r="G324" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>19.3499984741211</v>
+        <v>19.3500003814697</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>19.1621341705322</v>
+        <v>19.1621360778809</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G334" t="n">
-        <v>18.974271774292</v>
+        <v>18.9742736816406</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>18.974271774292</v>
+        <v>18.9742736816406</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G336" t="n">
-        <v>18.974271774292</v>
+        <v>18.9742736816406</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>19.1621341705322</v>
+        <v>19.1621360778809</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>19.1621341705322</v>
+        <v>19.1621360778809</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>19.3499984741211</v>
+        <v>19.3500003814697</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G341" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G343" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>21</v>
       </c>
       <c r="G347" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G350" t="n">
-        <v>20.2893218994141</v>
+        <v>20.2893199920654</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>20.2893218994141</v>
+        <v>20.2893199920654</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>23.1072807312012</v>
+        <v>23.1072826385498</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>24.6101951599121</v>
+        <v>24.6101932525635</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>26</v>
       </c>
       <c r="G397" t="n">
-        <v>24.4223308563232</v>
+        <v>24.4223289489746</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>24.6101951599121</v>
+        <v>24.6101932525635</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G400" t="n">
-        <v>25.7373790740967</v>
+        <v>25.737377166748</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>24.7980575561523</v>
+        <v>24.798059463501</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>24.7980575561523</v>
+        <v>24.798059463501</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>23.2951431274414</v>
+        <v>23.29514503479</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>24.2344665527344</v>
+        <v>24.2344646453857</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G415" t="n">
-        <v>24.2344665527344</v>
+        <v>24.2344646453857</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G416" t="n">
-        <v>24.2344665527344</v>
+        <v>24.2344646453857</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G419" t="n">
-        <v>23.2951431274414</v>
+        <v>23.29514503479</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>23.2951431274414</v>
+        <v>23.29514503479</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G426" t="n">
-        <v>24.6101951599121</v>
+        <v>24.6101932525635</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>24.7980575561523</v>
+        <v>24.798059463501</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>26</v>
       </c>
       <c r="G435" t="n">
-        <v>24.4223308563232</v>
+        <v>24.4223289489746</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>26</v>
       </c>
       <c r="G438" t="n">
-        <v>24.4223308563232</v>
+        <v>24.4223289489746</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>24.7980575561523</v>
+        <v>24.798059463501</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>24.6101951599121</v>
+        <v>24.6101932525635</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>26</v>
       </c>
       <c r="G458" t="n">
-        <v>24.4223308563232</v>
+        <v>24.4223289489746</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G461" t="n">
-        <v>23.1072807312012</v>
+        <v>23.1072826385498</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G466" t="n">
-        <v>18.4106788635254</v>
+        <v>18.410680770874</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G471" t="n">
-        <v>16.1563110351562</v>
+        <v>16.1563129425049</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>14.2776699066162</v>
+        <v>14.2776689529419</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>14.2776699066162</v>
+        <v>14.2776689529419</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G479" t="n">
-        <v>13.9958724975586</v>
+        <v>13.9958734512329</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>15.6866502761841</v>
+        <v>15.6866512298584</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>15.6866502761841</v>
+        <v>15.6866512298584</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G487" t="n">
-        <v>16.1563110351562</v>
+        <v>16.1563129425049</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>17.25</v>
       </c>
       <c r="G490" t="n">
-        <v>16.2032775878906</v>
+        <v>16.203275680542</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>15.6866502761841</v>
+        <v>15.6866512298584</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G496" t="n">
-        <v>16.1563110351562</v>
+        <v>16.1563129425049</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>15.6866502761841</v>
+        <v>15.6866512298584</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G502" t="n">
-        <v>16.813835144043</v>
+        <v>16.8138332366943</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G509" t="n">
-        <v>17.2365303039551</v>
+        <v>17.2365283966064</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>17.1895618438721</v>
+        <v>17.1895637512207</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>16.7668685913086</v>
+        <v>16.7668704986572</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>16.7668685913086</v>
+        <v>16.7668704986572</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>17.1895618438721</v>
+        <v>17.1895637512207</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G518" t="n">
-        <v>17.2365303039551</v>
+        <v>17.2365283966064</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>18.1288814544678</v>
+        <v>18.1288833618164</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>19</v>
       </c>
       <c r="G534" t="n">
-        <v>17.8470878601074</v>
+        <v>17.8470859527588</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>18.4106788635254</v>
+        <v>18.410680770874</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>17.1895618438721</v>
+        <v>17.1895637512207</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>17.4243927001953</v>
+        <v>17.4243907928467</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G540" t="n">
-        <v>17.2365303039551</v>
+        <v>17.2365283966064</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>16.813835144043</v>
+        <v>16.8138332366943</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>17.2365303039551</v>
+        <v>17.2365283966064</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G544" t="n">
-        <v>17.4243927001953</v>
+        <v>17.4243907928467</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>18.5</v>
       </c>
       <c r="G545" t="n">
-        <v>17.3774261474609</v>
+        <v>17.3774280548096</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>19</v>
       </c>
       <c r="G546" t="n">
-        <v>17.8470878601074</v>
+        <v>17.8470859527588</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>18.5</v>
       </c>
       <c r="G548" t="n">
-        <v>17.3774261474609</v>
+        <v>17.3774280548096</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>15.75</v>
       </c>
       <c r="G567" t="n">
-        <v>14.7942962646484</v>
+        <v>14.7942953109741</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>15.75</v>
       </c>
       <c r="G580" t="n">
-        <v>14.7942962646484</v>
+        <v>14.7942953109741</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>14.4655342102051</v>
+        <v>14.4655332565308</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>15.75</v>
       </c>
       <c r="G589" t="n">
-        <v>14.7942962646484</v>
+        <v>14.7942953109741</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G591" t="n">
-        <v>14.4655342102051</v>
+        <v>14.4655332565308</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G593" t="n">
-        <v>14.1837387084961</v>
+        <v>14.1837377548218</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>13.9958724975586</v>
+        <v>13.9958734512329</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G595" t="n">
-        <v>14.042839050293</v>
+        <v>14.0428400039673</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G596" t="n">
-        <v>13.9019412994385</v>
+        <v>13.9019422531128</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>13.9019412994385</v>
+        <v>13.9019422531128</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>14.5</v>
       </c>
       <c r="G600" t="n">
-        <v>13.6201448440552</v>
+        <v>13.6201457977295</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -55674,6 +55674,32 @@
         <v>22</v>
       </c>
       <c r="H2127" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2128" t="n">
+        <v>9795</v>
+      </c>
+      <c r="C2128" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="D2128" t="n">
+        <v>21.8999996185303</v>
+      </c>
+      <c r="E2128" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2128" t="n">
+        <v>22.1000003814697</v>
+      </c>
+      <c r="G2128" t="n">
+        <v>22.1000003814697</v>
+      </c>
+      <c r="H2128" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -447,7 +447,7 @@
         <v>17.9139995574951</v>
       </c>
       <c r="G3" t="n">
-        <v>16.4445552825928</v>
+        <v>16.4445533752441</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>17.6979999542236</v>
       </c>
       <c r="G6" t="n">
-        <v>16.2462730407715</v>
+        <v>16.2462711334229</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G9" t="n">
-        <v>16.2481098175049</v>
+        <v>16.2481079101562</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>17.5</v>
       </c>
       <c r="G12" t="n">
-        <v>16.0645122528076</v>
+        <v>16.0645141601562</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>17.75</v>
       </c>
       <c r="G14" t="n">
-        <v>16.2940063476562</v>
+        <v>16.2940082550049</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>16.2481098175049</v>
+        <v>16.2481079101562</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G16" t="n">
-        <v>16.2481098175049</v>
+        <v>16.2481079101562</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>17.8840007781982</v>
       </c>
       <c r="G25" t="n">
-        <v>16.4170150756836</v>
+        <v>16.4170169830322</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>16.3858032226562</v>
+        <v>16.3858051300049</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G34" t="n">
-        <v>16.2481098175049</v>
+        <v>16.2481079101562</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>16.4776020050049</v>
+        <v>16.4776039123535</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>17.0283851623535</v>
+        <v>17.0283832550049</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>19</v>
       </c>
       <c r="G46" t="n">
-        <v>17.4414730072021</v>
+        <v>17.4414710998535</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>19</v>
       </c>
       <c r="G49" t="n">
-        <v>17.4414730072021</v>
+        <v>17.4414710998535</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G50" t="n">
-        <v>17.5883464813232</v>
+        <v>17.5883483886719</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>19</v>
       </c>
       <c r="G56" t="n">
-        <v>17.4414730072021</v>
+        <v>17.4414710998535</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>19</v>
       </c>
       <c r="G57" t="n">
-        <v>17.4414730072021</v>
+        <v>17.4414710998535</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>19</v>
       </c>
       <c r="G58" t="n">
-        <v>17.4414730072021</v>
+        <v>17.4414710998535</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>17.3496742248535</v>
+        <v>17.3496761322021</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G60" t="n">
-        <v>17.4231128692627</v>
+        <v>17.4231109619141</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>17.1201801300049</v>
+        <v>17.1201820373535</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G63" t="n">
-        <v>17.1201801300049</v>
+        <v>17.1201820373535</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>17.3037776947021</v>
+        <v>17.3037757873535</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>17.0742816925049</v>
+        <v>17.0742835998535</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G71" t="n">
-        <v>17.0283851623535</v>
+        <v>17.0283832550049</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G72" t="n">
-        <v>17.0283851623535</v>
+        <v>17.0283832550049</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G73" t="n">
-        <v>17.0283851623535</v>
+        <v>17.0283832550049</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G74" t="n">
-        <v>17.0283851623535</v>
+        <v>17.0283832550049</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G75" t="n">
-        <v>17.0283851623535</v>
+        <v>17.0283832550049</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>17.0742816925049</v>
+        <v>17.0742835998535</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>18.2280006408691</v>
       </c>
       <c r="G78" t="n">
-        <v>16.7327976226807</v>
+        <v>16.7327995300293</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>18.4099998474121</v>
       </c>
       <c r="G79" t="n">
-        <v>16.8998680114746</v>
+        <v>16.899866104126</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G85" t="n">
-        <v>16.5216636657715</v>
+        <v>16.5216655731201</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G86" t="n">
-        <v>16.5216636657715</v>
+        <v>16.5216655731201</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G87" t="n">
-        <v>16.5216636657715</v>
+        <v>16.5216655731201</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G88" t="n">
-        <v>16.5216636657715</v>
+        <v>16.5216655731201</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G89" t="n">
-        <v>16.5216636657715</v>
+        <v>16.5216655731201</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G90" t="n">
-        <v>16.5216636657715</v>
+        <v>16.5216655731201</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>16.2481098175049</v>
+        <v>16.2481079101562</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>16.2022075653076</v>
+        <v>16.2022094726562</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G97" t="n">
-        <v>15.7615842819214</v>
+        <v>15.7615833282471</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>17.1480007171631</v>
       </c>
       <c r="G99" t="n">
-        <v>15.7413873672485</v>
+        <v>15.7413892745972</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G100" t="n">
-        <v>15.8717412948608</v>
+        <v>15.8717403411865</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G101" t="n">
-        <v>15.7707643508911</v>
+        <v>15.7707633972168</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G102" t="n">
-        <v>15.421932220459</v>
+        <v>15.4219331741333</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>16.9179992675781</v>
       </c>
       <c r="G104" t="n">
-        <v>15.5302534103394</v>
+        <v>15.530252456665</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G105" t="n">
-        <v>15.5229091644287</v>
+        <v>15.5229110717773</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G107" t="n">
-        <v>14.9721260070801</v>
+        <v>14.9721250534058</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G108" t="n">
-        <v>14.8711500167847</v>
+        <v>14.871150970459</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>16.25</v>
       </c>
       <c r="G110" t="n">
-        <v>14.9170484542847</v>
+        <v>14.9170475006104</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G111" t="n">
-        <v>15.100643157959</v>
+        <v>15.1006441116333</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>16.1119995117188</v>
       </c>
       <c r="G112" t="n">
-        <v>14.7903671264648</v>
+        <v>14.7903680801392</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>14.7793521881104</v>
+        <v>14.7793531417847</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G114" t="n">
-        <v>14.8252515792847</v>
+        <v>14.8252506256104</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>16.25</v>
       </c>
       <c r="G115" t="n">
-        <v>14.9170484542847</v>
+        <v>14.9170475006104</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>14.8711500167847</v>
+        <v>14.871150970459</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>14.595757484436</v>
+        <v>14.5957584381104</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G121" t="n">
-        <v>14.595757484436</v>
+        <v>14.5957584381104</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G122" t="n">
-        <v>14.595757484436</v>
+        <v>14.5957584381104</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G125" t="n">
-        <v>14.8711500167847</v>
+        <v>14.871150970459</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>14.8252515792847</v>
+        <v>14.8252506256104</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G129" t="n">
-        <v>14.6691951751709</v>
+        <v>14.6691961288452</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G131" t="n">
-        <v>14.6600160598755</v>
+        <v>14.6600170135498</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G135" t="n">
-        <v>14.6691951751709</v>
+        <v>14.6691961288452</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>14.366265296936</v>
+        <v>14.3662643432617</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>14.9280004501343</v>
       </c>
       <c r="G138" t="n">
-        <v>13.7034902572632</v>
+        <v>13.7034893035889</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>15.3680000305176</v>
       </c>
       <c r="G139" t="n">
-        <v>14.1073961257935</v>
+        <v>14.1073970794678</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>15.5</v>
       </c>
       <c r="G140" t="n">
-        <v>14.2285690307617</v>
+        <v>14.228569984436</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>15.5</v>
       </c>
       <c r="G141" t="n">
-        <v>14.2285690307617</v>
+        <v>14.228569984436</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>15.5</v>
       </c>
       <c r="G142" t="n">
-        <v>14.2285690307617</v>
+        <v>14.228569984436</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>15.5</v>
       </c>
       <c r="G143" t="n">
-        <v>14.2285690307617</v>
+        <v>14.228569984436</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G146" t="n">
-        <v>14.8160705566406</v>
+        <v>14.8160715103149</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>14.595757484436</v>
+        <v>14.5957584381104</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>14.0449752807617</v>
+        <v>14.0449743270874</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>14.5039615631104</v>
+        <v>14.503960609436</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G151" t="n">
-        <v>14.5039615631104</v>
+        <v>14.503960609436</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G152" t="n">
-        <v>14.5039615631104</v>
+        <v>14.503960609436</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>14.8252515792847</v>
+        <v>14.8252506256104</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G155" t="n">
-        <v>14.7334537506104</v>
+        <v>14.733452796936</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>14.5039615631104</v>
+        <v>14.503960609436</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>16.25</v>
       </c>
       <c r="G159" t="n">
-        <v>14.9170484542847</v>
+        <v>14.9170475006104</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G161" t="n">
-        <v>15.0731039047241</v>
+        <v>15.0731029510498</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G162" t="n">
-        <v>15.0731039047241</v>
+        <v>15.0731029510498</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>14.5039615631104</v>
+        <v>14.503960609436</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>16.25</v>
       </c>
       <c r="G169" t="n">
-        <v>14.9170484542847</v>
+        <v>14.9170475006104</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>16.25</v>
       </c>
       <c r="G170" t="n">
-        <v>14.9170484542847</v>
+        <v>14.9170475006104</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G171" t="n">
-        <v>14.7793521881104</v>
+        <v>14.7793531417847</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>14.7793521881104</v>
+        <v>14.7793531417847</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>15.0547437667847</v>
+        <v>15.054744720459</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G176" t="n">
-        <v>15.421932220459</v>
+        <v>15.4219331741333</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G177" t="n">
-        <v>15.1924381256104</v>
+        <v>15.1924390792847</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>15.6514253616333</v>
+        <v>15.6514263153076</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>17</v>
       </c>
       <c r="G179" t="n">
-        <v>15.6055278778076</v>
+        <v>15.6055269241333</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>17</v>
       </c>
       <c r="G180" t="n">
-        <v>15.6055278778076</v>
+        <v>15.6055269241333</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>17</v>
       </c>
       <c r="G181" t="n">
-        <v>15.6055278778076</v>
+        <v>15.6055269241333</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G182" t="n">
-        <v>15.9268169403076</v>
+        <v>15.9268178939819</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G184" t="n">
-        <v>15.7340440750122</v>
+        <v>15.7340421676636</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G187" t="n">
-        <v>15.6238889694214</v>
+        <v>15.6238870620728</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G188" t="n">
-        <v>15.9268169403076</v>
+        <v>15.9268178939819</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>15.9268169403076</v>
+        <v>15.9268178939819</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G196" t="n">
-        <v>16.8447914123535</v>
+        <v>16.8447895050049</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G197" t="n">
-        <v>16.8539714813232</v>
+        <v>16.8539695739746</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G200" t="n">
-        <v>16.3490829467773</v>
+        <v>16.349084854126</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>18.0840549468994</v>
+        <v>18.0840530395508</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G204" t="n">
-        <v>18.772533416748</v>
+        <v>18.7725315093994</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>21.7250003814697</v>
       </c>
       <c r="G206" t="n">
-        <v>19.9429473876953</v>
+        <v>19.9429454803467</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>19.3692150115967</v>
+        <v>19.369213104248</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>18.956127166748</v>
+        <v>18.9561252593994</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G209" t="n">
-        <v>19.0020236968994</v>
+        <v>19.0020275115967</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>20.2871856689453</v>
+        <v>20.2871875762939</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>22.7450008392334</v>
       </c>
       <c r="G214" t="n">
-        <v>20.879280090332</v>
+        <v>20.8792781829834</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>23</v>
       </c>
       <c r="G215" t="n">
-        <v>21.1133594512939</v>
+        <v>21.1133613586426</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G217" t="n">
-        <v>20.3789844512939</v>
+        <v>20.3789825439453</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>22.1650009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>20.3468532562256</v>
+        <v>20.3468551635742</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>22.5249996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>20.6773223876953</v>
+        <v>20.6773242950439</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>22.9950008392334</v>
       </c>
       <c r="G223" t="n">
-        <v>21.108772277832</v>
+        <v>21.1087703704834</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>23.2950000762939</v>
       </c>
       <c r="G224" t="n">
-        <v>21.384162902832</v>
+        <v>21.3841648101807</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G225" t="n">
-        <v>21.1867961883545</v>
+        <v>21.1867980957031</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G226" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G234" t="n">
-        <v>21.2969570159912</v>
+        <v>21.2969551086426</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>23</v>
       </c>
       <c r="G235" t="n">
-        <v>21.1133594512939</v>
+        <v>21.1133613586426</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G237" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>23</v>
       </c>
       <c r="G238" t="n">
-        <v>21.1133594512939</v>
+        <v>21.1133613586426</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>23</v>
       </c>
       <c r="G239" t="n">
-        <v>21.1133594512939</v>
+        <v>21.1133613586426</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G240" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>23</v>
       </c>
       <c r="G243" t="n">
-        <v>21.1133594512939</v>
+        <v>21.1133613586426</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G246" t="n">
-        <v>20.5625782012939</v>
+        <v>20.5625762939453</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>19.8282012939453</v>
+        <v>19.8281993865967</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G248" t="n">
-        <v>20.0117950439453</v>
+        <v>20.0117931365967</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G251" t="n">
-        <v>20.0117950439453</v>
+        <v>20.0117931365967</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>21</v>
       </c>
       <c r="G255" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G258" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G259" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>21</v>
       </c>
       <c r="G261" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G262" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>21</v>
       </c>
       <c r="G263" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>21</v>
       </c>
       <c r="G264" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G265" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>21</v>
       </c>
       <c r="G266" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G271" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G307" t="n">
-        <v>20.2893218994141</v>
+        <v>20.2893199920654</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>21</v>
       </c>
       <c r="G309" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>21</v>
       </c>
       <c r="G311" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>21</v>
       </c>
       <c r="G312" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G313" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>21</v>
       </c>
       <c r="G315" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>21</v>
       </c>
       <c r="G316" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>21</v>
       </c>
       <c r="G317" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>19.3499984741211</v>
+        <v>19.3500003814697</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>19.3499984741211</v>
+        <v>19.3500003814697</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G320" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>21</v>
       </c>
       <c r="G321" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>21</v>
       </c>
       <c r="G324" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>19.3499984741211</v>
+        <v>19.3500003814697</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>19.1621341705322</v>
+        <v>19.1621360778809</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G334" t="n">
-        <v>18.974271774292</v>
+        <v>18.9742736816406</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>18.974271774292</v>
+        <v>18.9742736816406</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G336" t="n">
-        <v>18.974271774292</v>
+        <v>18.9742736816406</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>19.1621341705322</v>
+        <v>19.1621360778809</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>19.1621341705322</v>
+        <v>19.1621360778809</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>19.3499984741211</v>
+        <v>19.3500003814697</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G341" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G343" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>21</v>
       </c>
       <c r="G347" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G350" t="n">
-        <v>20.2893218994141</v>
+        <v>20.2893199920654</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>20.2893218994141</v>
+        <v>20.2893199920654</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>23.1072807312012</v>
+        <v>23.1072826385498</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>24.6101951599121</v>
+        <v>24.6101932525635</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>26</v>
       </c>
       <c r="G397" t="n">
-        <v>24.4223308563232</v>
+        <v>24.4223289489746</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>24.6101951599121</v>
+        <v>24.6101932525635</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G400" t="n">
-        <v>25.7373790740967</v>
+        <v>25.737377166748</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>24.7980575561523</v>
+        <v>24.798059463501</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>24.7980575561523</v>
+        <v>24.798059463501</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>23.2951431274414</v>
+        <v>23.29514503479</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>24.2344665527344</v>
+        <v>24.2344646453857</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G415" t="n">
-        <v>24.2344665527344</v>
+        <v>24.2344646453857</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G416" t="n">
-        <v>24.2344665527344</v>
+        <v>24.2344646453857</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G419" t="n">
-        <v>23.2951431274414</v>
+        <v>23.29514503479</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>23.2951431274414</v>
+        <v>23.29514503479</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G426" t="n">
-        <v>24.6101951599121</v>
+        <v>24.6101932525635</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>24.7980575561523</v>
+        <v>24.798059463501</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>26</v>
       </c>
       <c r="G435" t="n">
-        <v>24.4223308563232</v>
+        <v>24.4223289489746</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>26</v>
       </c>
       <c r="G438" t="n">
-        <v>24.4223308563232</v>
+        <v>24.4223289489746</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>24.7980575561523</v>
+        <v>24.798059463501</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>24.6101951599121</v>
+        <v>24.6101932525635</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>26</v>
       </c>
       <c r="G458" t="n">
-        <v>24.4223308563232</v>
+        <v>24.4223289489746</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G461" t="n">
-        <v>23.1072807312012</v>
+        <v>23.1072826385498</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G466" t="n">
-        <v>18.4106788635254</v>
+        <v>18.410680770874</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G471" t="n">
-        <v>16.1563110351562</v>
+        <v>16.1563129425049</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>14.2776699066162</v>
+        <v>14.2776689529419</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>14.2776699066162</v>
+        <v>14.2776689529419</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G479" t="n">
-        <v>13.9958724975586</v>
+        <v>13.9958734512329</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>15.6866502761841</v>
+        <v>15.6866512298584</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>15.6866502761841</v>
+        <v>15.6866512298584</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G487" t="n">
-        <v>16.1563110351562</v>
+        <v>16.1563129425049</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>17.25</v>
       </c>
       <c r="G490" t="n">
-        <v>16.2032775878906</v>
+        <v>16.203275680542</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>15.6866502761841</v>
+        <v>15.6866512298584</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G496" t="n">
-        <v>16.1563110351562</v>
+        <v>16.1563129425049</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>15.6866502761841</v>
+        <v>15.6866512298584</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G502" t="n">
-        <v>16.813835144043</v>
+        <v>16.8138332366943</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G509" t="n">
-        <v>17.2365303039551</v>
+        <v>17.2365283966064</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>17.1895618438721</v>
+        <v>17.1895637512207</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>16.7668685913086</v>
+        <v>16.7668704986572</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>16.7668685913086</v>
+        <v>16.7668704986572</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>17.1895618438721</v>
+        <v>17.1895637512207</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G518" t="n">
-        <v>17.2365303039551</v>
+        <v>17.2365283966064</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>18.1288814544678</v>
+        <v>18.1288833618164</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>19</v>
       </c>
       <c r="G534" t="n">
-        <v>17.8470878601074</v>
+        <v>17.8470859527588</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>18.4106788635254</v>
+        <v>18.410680770874</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>17.1895618438721</v>
+        <v>17.1895637512207</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>17.4243927001953</v>
+        <v>17.4243907928467</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G540" t="n">
-        <v>17.2365303039551</v>
+        <v>17.2365283966064</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>16.813835144043</v>
+        <v>16.8138332366943</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>17.2365303039551</v>
+        <v>17.2365283966064</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G544" t="n">
-        <v>17.4243927001953</v>
+        <v>17.4243907928467</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>18.5</v>
       </c>
       <c r="G545" t="n">
-        <v>17.3774261474609</v>
+        <v>17.3774280548096</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>19</v>
       </c>
       <c r="G546" t="n">
-        <v>17.8470878601074</v>
+        <v>17.8470859527588</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>18.5</v>
       </c>
       <c r="G548" t="n">
-        <v>17.3774261474609</v>
+        <v>17.3774280548096</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>15.75</v>
       </c>
       <c r="G567" t="n">
-        <v>14.7942962646484</v>
+        <v>14.7942953109741</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>15.75</v>
       </c>
       <c r="G580" t="n">
-        <v>14.7942962646484</v>
+        <v>14.7942953109741</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>14.4655342102051</v>
+        <v>14.4655332565308</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>15.75</v>
       </c>
       <c r="G589" t="n">
-        <v>14.7942962646484</v>
+        <v>14.7942953109741</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G591" t="n">
-        <v>14.4655342102051</v>
+        <v>14.4655332565308</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G593" t="n">
-        <v>14.1837387084961</v>
+        <v>14.1837377548218</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>13.9958724975586</v>
+        <v>13.9958734512329</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G595" t="n">
-        <v>14.042839050293</v>
+        <v>14.0428400039673</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G596" t="n">
-        <v>13.9019412994385</v>
+        <v>13.9019422531128</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>13.9019412994385</v>
+        <v>13.9019422531128</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>14.5</v>
       </c>
       <c r="G600" t="n">
-        <v>13.6201448440552</v>
+        <v>13.6201457977295</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -55752,6 +55752,32 @@
         <v>22.1000003814697</v>
       </c>
       <c r="H2130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2131" t="n">
+        <v>17893</v>
+      </c>
+      <c r="C2131" t="n">
+        <v>22.8999996185303</v>
+      </c>
+      <c r="D2131" t="n">
+        <v>22.1000003814697</v>
+      </c>
+      <c r="E2131" t="n">
+        <v>22.2000007629395</v>
+      </c>
+      <c r="F2131" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="G2131" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="H2131" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -49447,8 +49447,31 @@
       <c r="E2134" t="n">
         <v>22.8999996185303</v>
       </c>
-      <c r="F2134"/>
+      <c r="F2134" t="n">
+        <v>23.2999992370605</v>
+      </c>
       <c r="G2134" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2135" t="n">
+        <v>24936</v>
+      </c>
+      <c r="C2135" t="n">
+        <v>24.7999992370605</v>
+      </c>
+      <c r="D2135" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="E2135" t="n">
+        <v>23.2999992370605</v>
+      </c>
+      <c r="F2135"/>
+      <c r="G2135" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -49470,8 +49470,31 @@
       <c r="E2135" t="n">
         <v>23.2999992370605</v>
       </c>
-      <c r="F2135"/>
+      <c r="F2135" t="n">
+        <v>24.7999992370605</v>
+      </c>
       <c r="G2135" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2136" t="n">
+        <v>31492</v>
+      </c>
+      <c r="C2136" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2136" t="n">
+        <v>23.3999996185303</v>
+      </c>
+      <c r="E2136" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2136"/>
+      <c r="G2136" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -49493,8 +49493,31 @@
       <c r="E2136" t="n">
         <v>25</v>
       </c>
-      <c r="F2136"/>
+      <c r="F2136" t="n">
+        <v>24.1000003814697</v>
+      </c>
       <c r="G2136" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2137" t="n">
+        <v>39903</v>
+      </c>
+      <c r="C2137" t="n">
+        <v>26.2999992370605</v>
+      </c>
+      <c r="D2137" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="E2137" t="n">
+        <v>25.1000003814697</v>
+      </c>
+      <c r="F2137"/>
+      <c r="G2137" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -49516,8 +49516,31 @@
       <c r="E2137" t="n">
         <v>25.1000003814697</v>
       </c>
-      <c r="F2137"/>
+      <c r="F2137" t="n">
+        <v>24.6000003814697</v>
+      </c>
       <c r="G2137" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2138" t="n">
+        <v>9568</v>
+      </c>
+      <c r="C2138" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2138" t="n">
+        <v>24</v>
+      </c>
+      <c r="E2138" t="n">
+        <v>24.7999992370605</v>
+      </c>
+      <c r="F2138"/>
+      <c r="G2138" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -49546,6 +49546,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2139">
+      <c r="A2139" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2139" t="n">
+        <v>16409</v>
+      </c>
+      <c r="C2139" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="D2139" t="n">
+        <v>23.7000007629395</v>
+      </c>
+      <c r="E2139" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2139" t="n">
+        <v>23.7000007629395</v>
+      </c>
+      <c r="G2139" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -499,7 +499,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G5" t="n">
-        <v>16.4225234985352</v>
+        <v>16.4225215911865</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>17.6979999542236</v>
       </c>
       <c r="G6" t="n">
-        <v>16.2462730407715</v>
+        <v>16.2462711334229</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G7" t="n">
-        <v>16.2848262786865</v>
+        <v>16.2848281860352</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G8" t="n">
-        <v>16.4225234985352</v>
+        <v>16.4225215911865</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>17.75</v>
       </c>
       <c r="G14" t="n">
-        <v>16.2940063476562</v>
+        <v>16.2940082550049</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>17.8780002593994</v>
       </c>
       <c r="G31" t="n">
-        <v>16.4115085601807</v>
+        <v>16.411506652832</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>16.4776020050049</v>
+        <v>16.4776039123535</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>18.5</v>
       </c>
       <c r="G44" t="n">
-        <v>16.9824867248535</v>
+        <v>16.9824848175049</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G50" t="n">
-        <v>17.5883464813232</v>
+        <v>17.5883483886719</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G60" t="n">
-        <v>17.4231128692627</v>
+        <v>17.4231109619141</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>17.1201801300049</v>
+        <v>17.1201820373535</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G63" t="n">
-        <v>17.1201801300049</v>
+        <v>17.1201820373535</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G69" t="n">
-        <v>16.7988929748535</v>
+        <v>16.7988910675049</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>16.7988929748535</v>
+        <v>16.7988910675049</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>18.4099998474121</v>
       </c>
       <c r="G79" t="n">
-        <v>16.8998680114746</v>
+        <v>16.899866104126</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G81" t="n">
-        <v>16.909049987793</v>
+        <v>16.9090480804443</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G85" t="n">
-        <v>16.5216636657715</v>
+        <v>16.5216655731201</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G86" t="n">
-        <v>16.5216636657715</v>
+        <v>16.5216655731201</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G87" t="n">
-        <v>16.5216636657715</v>
+        <v>16.5216655731201</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G88" t="n">
-        <v>16.5216636657715</v>
+        <v>16.5216655731201</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G89" t="n">
-        <v>16.5216636657715</v>
+        <v>16.5216655731201</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G90" t="n">
-        <v>16.5216636657715</v>
+        <v>16.5216655731201</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>17.8339996337891</v>
       </c>
       <c r="G92" t="n">
-        <v>16.371114730835</v>
+        <v>16.3711166381836</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>16.2022075653076</v>
+        <v>16.2022094726562</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G96" t="n">
-        <v>16.2848262786865</v>
+        <v>16.2848281860352</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>17.1480007171631</v>
       </c>
       <c r="G99" t="n">
-        <v>15.7413873672485</v>
+        <v>15.7413892745972</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G102" t="n">
-        <v>15.421932220459</v>
+        <v>15.4219331741333</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>16.9179992675781</v>
       </c>
       <c r="G104" t="n">
-        <v>15.5302534103394</v>
+        <v>15.530252456665</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>15.238338470459</v>
+        <v>15.2383394241333</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G107" t="n">
-        <v>14.9721260070801</v>
+        <v>14.9721250534058</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>16.25</v>
       </c>
       <c r="G110" t="n">
-        <v>14.9170484542847</v>
+        <v>14.9170475006104</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G114" t="n">
-        <v>14.8252515792847</v>
+        <v>14.8252506256104</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>16.25</v>
       </c>
       <c r="G115" t="n">
-        <v>14.9170484542847</v>
+        <v>14.9170475006104</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>14.8252515792847</v>
+        <v>14.8252506256104</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G129" t="n">
-        <v>14.6691951751709</v>
+        <v>14.6691961288452</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G131" t="n">
-        <v>14.6600160598755</v>
+        <v>14.6600170135498</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G135" t="n">
-        <v>14.6691951751709</v>
+        <v>14.6691961288452</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>15.5979995727539</v>
       </c>
       <c r="G145" t="n">
-        <v>14.318531036377</v>
+        <v>14.3185300827026</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>14.5039615631104</v>
+        <v>14.503960609436</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G151" t="n">
-        <v>14.5039615631104</v>
+        <v>14.503960609436</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G152" t="n">
-        <v>14.5039615631104</v>
+        <v>14.503960609436</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>14.8252515792847</v>
+        <v>14.8252506256104</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G155" t="n">
-        <v>14.7334537506104</v>
+        <v>14.733452796936</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>14.5039615631104</v>
+        <v>14.503960609436</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>16.25</v>
       </c>
       <c r="G159" t="n">
-        <v>14.9170484542847</v>
+        <v>14.9170475006104</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>16.5179996490479</v>
       </c>
       <c r="G165" t="n">
-        <v>15.1630640029907</v>
+        <v>15.163064956665</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>14.5039615631104</v>
+        <v>14.503960609436</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>16.25</v>
       </c>
       <c r="G169" t="n">
-        <v>14.9170484542847</v>
+        <v>14.9170475006104</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>16.25</v>
       </c>
       <c r="G170" t="n">
-        <v>14.9170484542847</v>
+        <v>14.9170475006104</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>15.0547437667847</v>
+        <v>15.054744720459</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G175" t="n">
-        <v>15.3301372528076</v>
+        <v>15.3301362991333</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G176" t="n">
-        <v>15.421932220459</v>
+        <v>15.4219331741333</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G177" t="n">
-        <v>15.192440032959</v>
+        <v>15.1924390792847</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>15.651424407959</v>
+        <v>15.6514263153076</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G183" t="n">
-        <v>15.9635372161865</v>
+        <v>15.9635353088379</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G190" t="n">
-        <v>15.7799434661865</v>
+        <v>15.7799415588379</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G204" t="n">
-        <v>18.772533416748</v>
+        <v>18.7725315093994</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>19.3692150115967</v>
+        <v>19.369213104248</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>20.6800003051758</v>
       </c>
       <c r="G210" t="n">
-        <v>18.9836654663086</v>
+        <v>18.9836673736572</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>21.6550006866455</v>
       </c>
       <c r="G212" t="n">
-        <v>19.8786907196045</v>
+        <v>19.8786888122559</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>23</v>
       </c>
       <c r="G215" t="n">
-        <v>21.1133594512939</v>
+        <v>21.1133613586426</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>22.5249996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>20.6773223876953</v>
+        <v>20.6773242950439</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>22.9950008392334</v>
       </c>
       <c r="G223" t="n">
-        <v>21.108772277832</v>
+        <v>21.1087703704834</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>23.2950000762939</v>
       </c>
       <c r="G224" t="n">
-        <v>21.384162902832</v>
+        <v>21.3841648101807</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G226" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>23</v>
       </c>
       <c r="G235" t="n">
-        <v>21.1133594512939</v>
+        <v>21.1133613586426</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G237" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>23</v>
       </c>
       <c r="G238" t="n">
-        <v>21.1133594512939</v>
+        <v>21.1133613586426</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>23</v>
       </c>
       <c r="G239" t="n">
-        <v>21.1133594512939</v>
+        <v>21.1133613586426</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G240" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297676086426</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>23</v>
       </c>
       <c r="G243" t="n">
-        <v>21.1133594512939</v>
+        <v>21.1133613586426</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G248" t="n">
-        <v>20.0117950439453</v>
+        <v>20.0117931365967</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>22</v>
       </c>
       <c r="G249" t="n">
-        <v>20.1953907012939</v>
+        <v>20.1953887939453</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>22</v>
       </c>
       <c r="G250" t="n">
-        <v>20.1953907012939</v>
+        <v>20.1953887939453</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G251" t="n">
-        <v>20.0117950439453</v>
+        <v>20.0117931365967</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>22</v>
       </c>
       <c r="G252" t="n">
-        <v>20.1953907012939</v>
+        <v>20.1953887939453</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -56038,6 +56038,32 @@
         <v>24.1000003814697</v>
       </c>
       <c r="H2141" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2142" t="n">
+        <v>6670</v>
+      </c>
+      <c r="C2142" t="n">
+        <v>24.2999992370605</v>
+      </c>
+      <c r="D2142" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E2142" t="n">
+        <v>24.2999992370605</v>
+      </c>
+      <c r="F2142" t="n">
+        <v>23.7999992370605</v>
+      </c>
+      <c r="G2142" t="n">
+        <v>23.7999992370605</v>
+      </c>
+      <c r="H2142" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -499,7 +499,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G5" t="n">
-        <v>16.4225215911865</v>
+        <v>16.4225234985352</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>17.6979999542236</v>
       </c>
       <c r="G6" t="n">
-        <v>16.2462711334229</v>
+        <v>16.2462730407715</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G7" t="n">
-        <v>16.2848281860352</v>
+        <v>16.2848262786865</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G8" t="n">
-        <v>16.4225215911865</v>
+        <v>16.4225234985352</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>17.75</v>
       </c>
       <c r="G14" t="n">
-        <v>16.2940082550049</v>
+        <v>16.2940063476562</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>17.8780002593994</v>
       </c>
       <c r="G31" t="n">
-        <v>16.411506652832</v>
+        <v>16.4115085601807</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>16.4776039123535</v>
+        <v>16.4776020050049</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>18.5</v>
       </c>
       <c r="G44" t="n">
-        <v>16.9824848175049</v>
+        <v>16.9824867248535</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G50" t="n">
-        <v>17.5883483886719</v>
+        <v>17.5883464813232</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G60" t="n">
-        <v>17.4231109619141</v>
+        <v>17.4231128692627</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>17.1201820373535</v>
+        <v>17.1201801300049</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G63" t="n">
-        <v>17.1201820373535</v>
+        <v>17.1201801300049</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G69" t="n">
-        <v>16.7988910675049</v>
+        <v>16.7988929748535</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>16.7988910675049</v>
+        <v>16.7988929748535</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>18.4099998474121</v>
       </c>
       <c r="G79" t="n">
-        <v>16.899866104126</v>
+        <v>16.8998680114746</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G81" t="n">
-        <v>16.9090480804443</v>
+        <v>16.909049987793</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G85" t="n">
-        <v>16.5216655731201</v>
+        <v>16.5216636657715</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G86" t="n">
-        <v>16.5216655731201</v>
+        <v>16.5216636657715</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G87" t="n">
-        <v>16.5216655731201</v>
+        <v>16.5216636657715</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G88" t="n">
-        <v>16.5216655731201</v>
+        <v>16.5216636657715</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G89" t="n">
-        <v>16.5216655731201</v>
+        <v>16.5216636657715</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>17.9979991912842</v>
       </c>
       <c r="G90" t="n">
-        <v>16.5216655731201</v>
+        <v>16.5216636657715</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>17.8339996337891</v>
       </c>
       <c r="G92" t="n">
-        <v>16.3711166381836</v>
+        <v>16.371114730835</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>16.2022094726562</v>
+        <v>16.2022075653076</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G96" t="n">
-        <v>16.2848281860352</v>
+        <v>16.2848262786865</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>17.1480007171631</v>
       </c>
       <c r="G99" t="n">
-        <v>15.7413892745972</v>
+        <v>15.7413873672485</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G102" t="n">
-        <v>15.4219331741333</v>
+        <v>15.421932220459</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>16.9179992675781</v>
       </c>
       <c r="G104" t="n">
-        <v>15.530252456665</v>
+        <v>15.5302534103394</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>15.2383394241333</v>
+        <v>15.238338470459</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G107" t="n">
-        <v>14.9721250534058</v>
+        <v>14.9721260070801</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>16.25</v>
       </c>
       <c r="G110" t="n">
-        <v>14.9170475006104</v>
+        <v>14.9170484542847</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G114" t="n">
-        <v>14.8252506256104</v>
+        <v>14.8252515792847</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>16.25</v>
       </c>
       <c r="G115" t="n">
-        <v>14.9170475006104</v>
+        <v>14.9170484542847</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>14.8252506256104</v>
+        <v>14.8252515792847</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G129" t="n">
-        <v>14.6691961288452</v>
+        <v>14.6691951751709</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G131" t="n">
-        <v>14.6600170135498</v>
+        <v>14.6600160598755</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G135" t="n">
-        <v>14.6691961288452</v>
+        <v>14.6691951751709</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>15.5979995727539</v>
       </c>
       <c r="G145" t="n">
-        <v>14.3185300827026</v>
+        <v>14.318531036377</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>14.503960609436</v>
+        <v>14.5039615631104</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G151" t="n">
-        <v>14.503960609436</v>
+        <v>14.5039615631104</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G152" t="n">
-        <v>14.503960609436</v>
+        <v>14.5039615631104</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>14.8252506256104</v>
+        <v>14.8252515792847</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G155" t="n">
-        <v>14.733452796936</v>
+        <v>14.7334537506104</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>14.503960609436</v>
+        <v>14.5039615631104</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>16.25</v>
       </c>
       <c r="G159" t="n">
-        <v>14.9170475006104</v>
+        <v>14.9170484542847</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>16.5179996490479</v>
       </c>
       <c r="G165" t="n">
-        <v>15.163064956665</v>
+        <v>15.1630640029907</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>14.503960609436</v>
+        <v>14.5039615631104</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>16.25</v>
       </c>
       <c r="G169" t="n">
-        <v>14.9170475006104</v>
+        <v>14.9170484542847</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>16.25</v>
       </c>
       <c r="G170" t="n">
-        <v>14.9170475006104</v>
+        <v>14.9170484542847</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>15.054744720459</v>
+        <v>15.0547437667847</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G175" t="n">
-        <v>15.3301362991333</v>
+        <v>15.3301372528076</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G176" t="n">
-        <v>15.4219331741333</v>
+        <v>15.421932220459</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G177" t="n">
-        <v>15.1924390792847</v>
+        <v>15.192440032959</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>15.6514263153076</v>
+        <v>15.651424407959</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G183" t="n">
-        <v>15.9635353088379</v>
+        <v>15.9635372161865</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G190" t="n">
-        <v>15.7799415588379</v>
+        <v>15.7799434661865</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>20.4500007629395</v>
       </c>
       <c r="G204" t="n">
-        <v>18.7725315093994</v>
+        <v>18.772533416748</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>19.369213104248</v>
+        <v>19.3692150115967</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>20.6800003051758</v>
       </c>
       <c r="G210" t="n">
-        <v>18.9836673736572</v>
+        <v>18.9836654663086</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>21.6550006866455</v>
       </c>
       <c r="G212" t="n">
-        <v>19.8786888122559</v>
+        <v>19.8786907196045</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>23</v>
       </c>
       <c r="G215" t="n">
-        <v>21.1133613586426</v>
+        <v>21.1133594512939</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>20.9297676086426</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>22.5249996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>20.6773242950439</v>
+        <v>20.6773223876953</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>20.9297676086426</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>22.9950008392334</v>
       </c>
       <c r="G223" t="n">
-        <v>21.1087703704834</v>
+        <v>21.108772277832</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>23.2950000762939</v>
       </c>
       <c r="G224" t="n">
-        <v>21.3841648101807</v>
+        <v>21.384162902832</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G226" t="n">
-        <v>20.9297676086426</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>20.9297676086426</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>23</v>
       </c>
       <c r="G235" t="n">
-        <v>21.1133613586426</v>
+        <v>21.1133594512939</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>20.9297676086426</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G237" t="n">
-        <v>20.9297676086426</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>23</v>
       </c>
       <c r="G238" t="n">
-        <v>21.1133613586426</v>
+        <v>21.1133594512939</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>23</v>
       </c>
       <c r="G239" t="n">
-        <v>21.1133613586426</v>
+        <v>21.1133594512939</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G240" t="n">
-        <v>20.9297676086426</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>20.9297676086426</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>23</v>
       </c>
       <c r="G243" t="n">
-        <v>21.1133613586426</v>
+        <v>21.1133594512939</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G248" t="n">
-        <v>20.0117931365967</v>
+        <v>20.0117950439453</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>22</v>
       </c>
       <c r="G249" t="n">
-        <v>20.1953887939453</v>
+        <v>20.1953907012939</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>22</v>
       </c>
       <c r="G250" t="n">
-        <v>20.1953887939453</v>
+        <v>20.1953907012939</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G251" t="n">
-        <v>20.0117931365967</v>
+        <v>20.0117950439453</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>22</v>
       </c>
       <c r="G252" t="n">
-        <v>20.1953887939453</v>
+        <v>20.1953907012939</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -56064,6 +56064,32 @@
         <v>23.7999992370605</v>
       </c>
       <c r="H2142" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2143" t="n">
+        <v>5225</v>
+      </c>
+      <c r="C2143" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="D2143" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E2143" t="n">
+        <v>24.1000003814697</v>
+      </c>
+      <c r="F2143" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G2143" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="H2143" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -456,7 +456,7 @@
         <v>17.9139995574951</v>
       </c>
       <c r="G3" t="n">
-        <v>16.4445533752441</v>
+        <v>16.4445552825928</v>
       </c>
       <c r="H3" t="n">
         <v>4000</v>
@@ -514,7 +514,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G5" t="n">
-        <v>16.4225234985352</v>
+        <v>16.4225215911865</v>
       </c>
       <c r="H5" t="n">
         <v>1500</v>
@@ -572,7 +572,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G7" t="n">
-        <v>16.2848262786865</v>
+        <v>16.2848281860352</v>
       </c>
       <c r="H7" t="n">
         <v>4600</v>
@@ -601,7 +601,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G8" t="n">
-        <v>16.4225234985352</v>
+        <v>16.4225215911865</v>
       </c>
       <c r="H8" t="n">
         <v>11700</v>
@@ -630,7 +630,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G9" t="n">
-        <v>16.2481079101562</v>
+        <v>16.2481098175049</v>
       </c>
       <c r="H9" t="n">
         <v>1700</v>
@@ -717,7 +717,7 @@
         <v>17.5</v>
       </c>
       <c r="G12" t="n">
-        <v>16.0645141601562</v>
+        <v>16.0645122528076</v>
       </c>
       <c r="H12" t="n">
         <v>2300</v>
@@ -804,7 +804,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>16.2481079101562</v>
+        <v>16.2481098175049</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
@@ -833,7 +833,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G16" t="n">
-        <v>16.2481079101562</v>
+        <v>16.2481098175049</v>
       </c>
       <c r="H16" t="n">
         <v>300</v>
@@ -1094,7 +1094,7 @@
         <v>17.8840007781982</v>
       </c>
       <c r="G25" t="n">
-        <v>16.4170169830322</v>
+        <v>16.4170150756836</v>
       </c>
       <c r="H25" t="n">
         <v>400</v>
@@ -1181,7 +1181,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>16.3858051300049</v>
+        <v>16.3858032226562</v>
       </c>
       <c r="H28" t="n">
         <v>2600</v>
@@ -1268,7 +1268,7 @@
         <v>17.8780002593994</v>
       </c>
       <c r="G31" t="n">
-        <v>16.4115085601807</v>
+        <v>16.411506652832</v>
       </c>
       <c r="H31" t="n">
         <v>3000</v>
@@ -1355,7 +1355,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G34" t="n">
-        <v>16.2481079101562</v>
+        <v>16.2481098175049</v>
       </c>
       <c r="H34" t="n">
         <v>1900</v>
@@ -1645,7 +1645,7 @@
         <v>18.5</v>
       </c>
       <c r="G44" t="n">
-        <v>16.9824867248535</v>
+        <v>16.9824848175049</v>
       </c>
       <c r="H44" t="n">
         <v>17900</v>
@@ -1674,7 +1674,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>17.0283832550049</v>
+        <v>17.0283851623535</v>
       </c>
       <c r="H45" t="n">
         <v>10700</v>
@@ -1703,7 +1703,7 @@
         <v>19</v>
       </c>
       <c r="G46" t="n">
-        <v>17.4414710998535</v>
+        <v>17.4414730072021</v>
       </c>
       <c r="H46" t="n">
         <v>11600</v>
@@ -1790,7 +1790,7 @@
         <v>19</v>
       </c>
       <c r="G49" t="n">
-        <v>17.4414710998535</v>
+        <v>17.4414730072021</v>
       </c>
       <c r="H49" t="n">
         <v>400</v>
@@ -1993,7 +1993,7 @@
         <v>19</v>
       </c>
       <c r="G56" t="n">
-        <v>17.4414710998535</v>
+        <v>17.4414730072021</v>
       </c>
       <c r="H56" t="n">
         <v>1900</v>
@@ -2022,7 +2022,7 @@
         <v>19</v>
       </c>
       <c r="G57" t="n">
-        <v>17.4414710998535</v>
+        <v>17.4414730072021</v>
       </c>
       <c r="H57" t="n">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>19</v>
       </c>
       <c r="G58" t="n">
-        <v>17.4414710998535</v>
+        <v>17.4414730072021</v>
       </c>
       <c r="H58" t="n">
         <v>2100</v>
@@ -2080,7 +2080,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>17.3496761322021</v>
+        <v>17.3496742248535</v>
       </c>
       <c r="H59" t="n">
         <v>40500</v>
@@ -2283,7 +2283,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>17.3037757873535</v>
+        <v>17.3037776947021</v>
       </c>
       <c r="H66" t="n">
         <v>100</v>
@@ -2312,7 +2312,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>17.0742835998535</v>
+        <v>17.0742816925049</v>
       </c>
       <c r="H67" t="n">
         <v>2300</v>
@@ -2370,7 +2370,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G69" t="n">
-        <v>16.7988929748535</v>
+        <v>16.7988910675049</v>
       </c>
       <c r="H69" t="n">
         <v>1000</v>
@@ -2399,7 +2399,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>16.7988929748535</v>
+        <v>16.7988910675049</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G71" t="n">
-        <v>17.0283832550049</v>
+        <v>17.0283851623535</v>
       </c>
       <c r="H71" t="n">
         <v>100</v>
@@ -2457,7 +2457,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G72" t="n">
-        <v>17.0283832550049</v>
+        <v>17.0283851623535</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G73" t="n">
-        <v>17.0283832550049</v>
+        <v>17.0283851623535</v>
       </c>
       <c r="H73" t="n">
         <v>100</v>
@@ -2515,7 +2515,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G74" t="n">
-        <v>17.0283832550049</v>
+        <v>17.0283851623535</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G75" t="n">
-        <v>17.0283832550049</v>
+        <v>17.0283851623535</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>17.0742835998535</v>
+        <v>17.0742816925049</v>
       </c>
       <c r="H76" t="n">
         <v>100</v>
@@ -2631,7 +2631,7 @@
         <v>18.2280006408691</v>
       </c>
       <c r="G78" t="n">
-        <v>16.7327995300293</v>
+        <v>16.7327976226807</v>
       </c>
       <c r="H78" t="n">
         <v>3800</v>
@@ -2718,7 +2718,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G81" t="n">
-        <v>16.909049987793</v>
+        <v>16.9090480804443</v>
       </c>
       <c r="H81" t="n">
         <v>5200</v>
@@ -3008,7 +3008,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>16.2481079101562</v>
+        <v>16.2481098175049</v>
       </c>
       <c r="H91" t="n">
         <v>2800</v>
@@ -3037,7 +3037,7 @@
         <v>17.8339996337891</v>
       </c>
       <c r="G92" t="n">
-        <v>16.371114730835</v>
+        <v>16.3711166381836</v>
       </c>
       <c r="H92" t="n">
         <v>100</v>
@@ -3153,7 +3153,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G96" t="n">
-        <v>16.2848262786865</v>
+        <v>16.2848281860352</v>
       </c>
       <c r="H96" t="n">
         <v>100</v>
@@ -3182,7 +3182,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G97" t="n">
-        <v>15.7615833282471</v>
+        <v>15.7615842819214</v>
       </c>
       <c r="H97" t="n">
         <v>8500</v>
@@ -3269,7 +3269,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G100" t="n">
-        <v>15.8717403411865</v>
+        <v>15.8717412948608</v>
       </c>
       <c r="H100" t="n">
         <v>7000</v>
@@ -3298,7 +3298,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G101" t="n">
-        <v>15.7707633972168</v>
+        <v>15.7707643508911</v>
       </c>
       <c r="H101" t="n">
         <v>2200</v>
@@ -3414,7 +3414,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G105" t="n">
-        <v>15.5229110717773</v>
+        <v>15.5229091644287</v>
       </c>
       <c r="H105" t="n">
         <v>400</v>
@@ -3443,7 +3443,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>15.238338470459</v>
+        <v>15.2383394241333</v>
       </c>
       <c r="H106" t="n">
         <v>400</v>
@@ -3501,7 +3501,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G108" t="n">
-        <v>14.871150970459</v>
+        <v>14.8711500167847</v>
       </c>
       <c r="H108" t="n">
         <v>200</v>
@@ -3588,7 +3588,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G111" t="n">
-        <v>15.1006441116333</v>
+        <v>15.100643157959</v>
       </c>
       <c r="H111" t="n">
         <v>5100</v>
@@ -3617,7 +3617,7 @@
         <v>16.1119995117188</v>
       </c>
       <c r="G112" t="n">
-        <v>14.7903680801392</v>
+        <v>14.7903671264648</v>
       </c>
       <c r="H112" t="n">
         <v>5400</v>
@@ -3646,7 +3646,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>14.7793531417847</v>
+        <v>14.7793521881104</v>
       </c>
       <c r="H113" t="n">
         <v>100</v>
@@ -3820,7 +3820,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>14.871150970459</v>
+        <v>14.8711500167847</v>
       </c>
       <c r="H119" t="n">
         <v>100</v>
@@ -3849,7 +3849,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>14.5957584381104</v>
+        <v>14.595757484436</v>
       </c>
       <c r="H120" t="n">
         <v>1500</v>
@@ -3878,7 +3878,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G121" t="n">
-        <v>14.5957584381104</v>
+        <v>14.595757484436</v>
       </c>
       <c r="H121" t="n">
         <v>2300</v>
@@ -3907,7 +3907,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G122" t="n">
-        <v>14.5957584381104</v>
+        <v>14.595757484436</v>
       </c>
       <c r="H122" t="n">
         <v>100</v>
@@ -3994,7 +3994,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G125" t="n">
-        <v>14.871150970459</v>
+        <v>14.8711500167847</v>
       </c>
       <c r="H125" t="n">
         <v>1900</v>
@@ -4313,7 +4313,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>14.3662643432617</v>
+        <v>14.366265296936</v>
       </c>
       <c r="H136" t="n">
         <v>1600</v>
@@ -4371,7 +4371,7 @@
         <v>14.9280004501343</v>
       </c>
       <c r="G138" t="n">
-        <v>13.7034893035889</v>
+        <v>13.7034902572632</v>
       </c>
       <c r="H138" t="n">
         <v>4400</v>
@@ -4400,7 +4400,7 @@
         <v>15.3680000305176</v>
       </c>
       <c r="G139" t="n">
-        <v>14.1073970794678</v>
+        <v>14.1073961257935</v>
       </c>
       <c r="H139" t="n">
         <v>3000</v>
@@ -4429,7 +4429,7 @@
         <v>15.5</v>
       </c>
       <c r="G140" t="n">
-        <v>14.228569984436</v>
+        <v>14.2285690307617</v>
       </c>
       <c r="H140" t="n">
         <v>4200</v>
@@ -4458,7 +4458,7 @@
         <v>15.5</v>
       </c>
       <c r="G141" t="n">
-        <v>14.228569984436</v>
+        <v>14.2285690307617</v>
       </c>
       <c r="H141" t="n">
         <v>100</v>
@@ -4487,7 +4487,7 @@
         <v>15.5</v>
       </c>
       <c r="G142" t="n">
-        <v>14.228569984436</v>
+        <v>14.2285690307617</v>
       </c>
       <c r="H142" t="n">
         <v>200</v>
@@ -4516,7 +4516,7 @@
         <v>15.5</v>
       </c>
       <c r="G143" t="n">
-        <v>14.228569984436</v>
+        <v>14.2285690307617</v>
       </c>
       <c r="H143" t="n">
         <v>300</v>
@@ -4574,7 +4574,7 @@
         <v>15.5979995727539</v>
       </c>
       <c r="G145" t="n">
-        <v>14.318531036377</v>
+        <v>14.3185300827026</v>
       </c>
       <c r="H145" t="n">
         <v>4400</v>
@@ -4603,7 +4603,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G146" t="n">
-        <v>14.8160715103149</v>
+        <v>14.8160705566406</v>
       </c>
       <c r="H146" t="n">
         <v>1200</v>
@@ -4632,7 +4632,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>14.5957584381104</v>
+        <v>14.595757484436</v>
       </c>
       <c r="H147" t="n">
         <v>3100</v>
@@ -4690,7 +4690,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>14.0449743270874</v>
+        <v>14.0449752807617</v>
       </c>
       <c r="H149" t="n">
         <v>100</v>
@@ -5038,7 +5038,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G161" t="n">
-        <v>15.0731029510498</v>
+        <v>15.0731039047241</v>
       </c>
       <c r="H161" t="n">
         <v>1800</v>
@@ -5067,7 +5067,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G162" t="n">
-        <v>15.0731029510498</v>
+        <v>15.0731039047241</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>16.5179996490479</v>
       </c>
       <c r="G165" t="n">
-        <v>15.1630640029907</v>
+        <v>15.163064956665</v>
       </c>
       <c r="H165" t="n">
         <v>500</v>
@@ -5328,7 +5328,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G171" t="n">
-        <v>14.7793531417847</v>
+        <v>14.7793521881104</v>
       </c>
       <c r="H171" t="n">
         <v>1500</v>
@@ -5357,7 +5357,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>14.7793531417847</v>
+        <v>14.7793521881104</v>
       </c>
       <c r="H172" t="n">
         <v>100</v>
@@ -5444,7 +5444,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G175" t="n">
-        <v>15.3301372528076</v>
+        <v>15.3301362991333</v>
       </c>
       <c r="H175" t="n">
         <v>22000</v>
@@ -5502,7 +5502,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G177" t="n">
-        <v>15.192440032959</v>
+        <v>15.1924381256104</v>
       </c>
       <c r="H177" t="n">
         <v>100</v>
@@ -5531,7 +5531,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>15.651424407959</v>
+        <v>15.6514253616333</v>
       </c>
       <c r="H178" t="n">
         <v>3000</v>
@@ -5560,7 +5560,7 @@
         <v>17</v>
       </c>
       <c r="G179" t="n">
-        <v>15.6055269241333</v>
+        <v>15.6055278778076</v>
       </c>
       <c r="H179" t="n">
         <v>1000</v>
@@ -5589,7 +5589,7 @@
         <v>17</v>
       </c>
       <c r="G180" t="n">
-        <v>15.6055269241333</v>
+        <v>15.6055278778076</v>
       </c>
       <c r="H180" t="n">
         <v>200</v>
@@ -5618,7 +5618,7 @@
         <v>17</v>
       </c>
       <c r="G181" t="n">
-        <v>15.6055269241333</v>
+        <v>15.6055278778076</v>
       </c>
       <c r="H181" t="n">
         <v>1100</v>
@@ -5647,7 +5647,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G182" t="n">
-        <v>15.9268178939819</v>
+        <v>15.9268169403076</v>
       </c>
       <c r="H182" t="n">
         <v>800</v>
@@ -5676,7 +5676,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G183" t="n">
-        <v>15.9635372161865</v>
+        <v>15.9635353088379</v>
       </c>
       <c r="H183" t="n">
         <v>200</v>
@@ -5705,7 +5705,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G184" t="n">
-        <v>15.7340421676636</v>
+        <v>15.7340440750122</v>
       </c>
       <c r="H184" t="n">
         <v>200</v>
@@ -5792,7 +5792,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G187" t="n">
-        <v>15.6238870620728</v>
+        <v>15.6238889694214</v>
       </c>
       <c r="H187" t="n">
         <v>3500</v>
@@ -5821,7 +5821,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G188" t="n">
-        <v>15.9268178939819</v>
+        <v>15.9268169403076</v>
       </c>
       <c r="H188" t="n">
         <v>500</v>
@@ -5879,7 +5879,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G190" t="n">
-        <v>15.7799434661865</v>
+        <v>15.7799415588379</v>
       </c>
       <c r="H190" t="n">
         <v>400</v>
@@ -5937,7 +5937,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>15.9268178939819</v>
+        <v>15.9268169403076</v>
       </c>
       <c r="H192" t="n">
         <v>300</v>
@@ -6053,7 +6053,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G196" t="n">
-        <v>16.8447895050049</v>
+        <v>16.8447914123535</v>
       </c>
       <c r="H196" t="n">
         <v>1400</v>
@@ -6082,7 +6082,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G197" t="n">
-        <v>16.8539695739746</v>
+        <v>16.8539714813232</v>
       </c>
       <c r="H197" t="n">
         <v>400</v>
@@ -6169,7 +6169,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G200" t="n">
-        <v>16.349084854126</v>
+        <v>16.3490829467773</v>
       </c>
       <c r="H200" t="n">
         <v>2900</v>
@@ -6256,7 +6256,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>18.0840530395508</v>
+        <v>18.0840549468994</v>
       </c>
       <c r="H203" t="n">
         <v>18000</v>
@@ -6343,7 +6343,7 @@
         <v>21.7250003814697</v>
       </c>
       <c r="G206" t="n">
-        <v>19.9429454803467</v>
+        <v>19.9429473876953</v>
       </c>
       <c r="H206" t="n">
         <v>4300</v>
@@ -6401,7 +6401,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>18.9561252593994</v>
+        <v>18.956127166748</v>
       </c>
       <c r="H208" t="n">
         <v>1800</v>
@@ -6430,7 +6430,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G209" t="n">
-        <v>19.0020275115967</v>
+        <v>19.0020236968994</v>
       </c>
       <c r="H209" t="n">
         <v>1100</v>
@@ -6459,7 +6459,7 @@
         <v>20.6800003051758</v>
       </c>
       <c r="G210" t="n">
-        <v>18.9836654663086</v>
+        <v>18.9836673736572</v>
       </c>
       <c r="H210" t="n">
         <v>900</v>
@@ -6517,7 +6517,7 @@
         <v>21.6550006866455</v>
       </c>
       <c r="G212" t="n">
-        <v>19.8786907196045</v>
+        <v>19.8786888122559</v>
       </c>
       <c r="H212" t="n">
         <v>5800</v>
@@ -6546,7 +6546,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>20.2871875762939</v>
+        <v>20.2871856689453</v>
       </c>
       <c r="H213" t="n">
         <v>8600</v>
@@ -6575,7 +6575,7 @@
         <v>22.7450008392334</v>
       </c>
       <c r="G214" t="n">
-        <v>20.8792781829834</v>
+        <v>20.879280090332</v>
       </c>
       <c r="H214" t="n">
         <v>8100</v>
@@ -6633,7 +6633,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H216" t="n">
         <v>400</v>
@@ -6662,7 +6662,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G217" t="n">
-        <v>20.3789825439453</v>
+        <v>20.3789844512939</v>
       </c>
       <c r="H217" t="n">
         <v>36200</v>
@@ -6691,7 +6691,7 @@
         <v>22.1650009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>20.3468551635742</v>
+        <v>20.3468532562256</v>
       </c>
       <c r="H218" t="n">
         <v>6000</v>
@@ -6778,7 +6778,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H221" t="n">
         <v>2900</v>
@@ -6894,7 +6894,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G225" t="n">
-        <v>21.1867980957031</v>
+        <v>21.1867961883545</v>
       </c>
       <c r="H225" t="n">
         <v>5500</v>
@@ -6923,7 +6923,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G226" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H226" t="n">
         <v>9100</v>
@@ -6952,7 +6952,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H227" t="n">
         <v>6900</v>
@@ -7155,7 +7155,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G234" t="n">
-        <v>21.2969551086426</v>
+        <v>21.2969570159912</v>
       </c>
       <c r="H234" t="n">
         <v>3800</v>
@@ -7213,7 +7213,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H236" t="n">
         <v>200</v>
@@ -7242,7 +7242,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G237" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H237" t="n">
         <v>115</v>
@@ -7329,7 +7329,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G240" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H240" t="n">
         <v>550</v>
@@ -7387,7 +7387,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H242" t="n">
         <v>1115</v>
@@ -7503,7 +7503,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G246" t="n">
-        <v>20.5625762939453</v>
+        <v>20.5625782012939</v>
       </c>
       <c r="H246" t="n">
         <v>3610</v>
@@ -7532,7 +7532,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>19.8281993865967</v>
+        <v>19.8282012939453</v>
       </c>
       <c r="H247" t="n">
         <v>11926</v>
@@ -7590,7 +7590,7 @@
         <v>22</v>
       </c>
       <c r="G249" t="n">
-        <v>20.1953907012939</v>
+        <v>20.1953887939453</v>
       </c>
       <c r="H249" t="n">
         <v>2862</v>
@@ -7619,7 +7619,7 @@
         <v>22</v>
       </c>
       <c r="G250" t="n">
-        <v>20.1953907012939</v>
+        <v>20.1953887939453</v>
       </c>
       <c r="H250" t="n">
         <v>305</v>
@@ -7677,7 +7677,7 @@
         <v>22</v>
       </c>
       <c r="G252" t="n">
-        <v>20.1953907012939</v>
+        <v>20.1953887939453</v>
       </c>
       <c r="H252" t="n">
         <v>362</v>
@@ -7764,7 +7764,7 @@
         <v>21</v>
       </c>
       <c r="G255" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H255" t="n">
         <v>2005</v>
@@ -7851,7 +7851,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G258" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H258" t="n">
         <v>120</v>
@@ -7880,7 +7880,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G259" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H259" t="n">
         <v>745</v>
@@ -7938,7 +7938,7 @@
         <v>21</v>
       </c>
       <c r="G261" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H261" t="n">
         <v>565</v>
@@ -7967,7 +7967,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G262" t="n">
-        <v>19.53786277771</v>
+        <v>19.5378646850586</v>
       </c>
       <c r="H262" t="n">
         <v>2949</v>
@@ -7996,7 +7996,7 @@
         <v>21</v>
       </c>
       <c r="G263" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H263" t="n">
         <v>1250</v>
@@ -8025,7 +8025,7 @@
         <v>21</v>
       </c>
       <c r="G264" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H264" t="n">
         <v>6111</v>
@@ -8054,7 +8054,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G265" t="n">
-        <v>19.53786277771</v>
+        <v>19.5378646850586</v>
       </c>
       <c r="H265" t="n">
         <v>200</v>
@@ -8083,7 +8083,7 @@
         <v>21</v>
       </c>
       <c r="G266" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H266" t="n">
         <v>120</v>
@@ -8228,7 +8228,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G271" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H271" t="n">
         <v>100</v>
@@ -8257,7 +8257,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H272" t="n">
         <v>1646</v>
@@ -9272,7 +9272,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G307" t="n">
-        <v>20.2893199920654</v>
+        <v>20.2893218994141</v>
       </c>
       <c r="H307" t="n">
         <v>250</v>
@@ -9330,7 +9330,7 @@
         <v>21</v>
       </c>
       <c r="G309" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H309" t="n">
         <v>1476</v>
@@ -9359,7 +9359,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H310" t="n">
         <v>495</v>
@@ -9388,7 +9388,7 @@
         <v>21</v>
       </c>
       <c r="G311" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H311" t="n">
         <v>675</v>
@@ -9417,7 +9417,7 @@
         <v>21</v>
       </c>
       <c r="G312" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H312" t="n">
         <v>265</v>
@@ -9446,7 +9446,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G313" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H313" t="n">
         <v>3230</v>
@@ -9475,7 +9475,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H314" t="n">
         <v>320</v>
@@ -9504,7 +9504,7 @@
         <v>21</v>
       </c>
       <c r="G315" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H315" t="n">
         <v>50</v>
@@ -9533,7 +9533,7 @@
         <v>21</v>
       </c>
       <c r="G316" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H316" t="n">
         <v>465</v>
@@ -9562,7 +9562,7 @@
         <v>21</v>
       </c>
       <c r="G317" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H317" t="n">
         <v>3</v>
@@ -9591,7 +9591,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>19.3500003814697</v>
+        <v>19.3499984741211</v>
       </c>
       <c r="H318" t="n">
         <v>30</v>
@@ -9620,7 +9620,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>19.3500003814697</v>
+        <v>19.3499984741211</v>
       </c>
       <c r="H319" t="n">
         <v>326</v>
@@ -9649,7 +9649,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G320" t="n">
-        <v>19.53786277771</v>
+        <v>19.5378646850586</v>
       </c>
       <c r="H320" t="n">
         <v>422</v>
@@ -9678,7 +9678,7 @@
         <v>21</v>
       </c>
       <c r="G321" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H321" t="n">
         <v>286</v>
@@ -9707,7 +9707,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H322" t="n">
         <v>360</v>
@@ -9765,7 +9765,7 @@
         <v>21</v>
       </c>
       <c r="G324" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H324" t="n">
         <v>940</v>
@@ -9968,7 +9968,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H331" t="n">
         <v>380</v>
@@ -9997,7 +9997,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>19.3500003814697</v>
+        <v>19.3499984741211</v>
       </c>
       <c r="H332" t="n">
         <v>163</v>
@@ -10026,7 +10026,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>19.1621360778809</v>
+        <v>19.1621341705322</v>
       </c>
       <c r="H333" t="n">
         <v>9842</v>
@@ -10055,7 +10055,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G334" t="n">
-        <v>18.9742736816406</v>
+        <v>18.974271774292</v>
       </c>
       <c r="H334" t="n">
         <v>1547</v>
@@ -10084,7 +10084,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>18.9742736816406</v>
+        <v>18.974271774292</v>
       </c>
       <c r="H335" t="n">
         <v>4339</v>
@@ -10113,7 +10113,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G336" t="n">
-        <v>18.9742736816406</v>
+        <v>18.974271774292</v>
       </c>
       <c r="H336" t="n">
         <v>4539</v>
@@ -10142,7 +10142,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>19.1621360778809</v>
+        <v>19.1621341705322</v>
       </c>
       <c r="H337" t="n">
         <v>1942</v>
@@ -10171,7 +10171,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>19.1621360778809</v>
+        <v>19.1621341705322</v>
       </c>
       <c r="H338" t="n">
         <v>284</v>
@@ -10200,7 +10200,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>19.3500003814697</v>
+        <v>19.3499984741211</v>
       </c>
       <c r="H339" t="n">
         <v>2218</v>
@@ -10229,7 +10229,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>19.53786277771</v>
+        <v>19.5378646850586</v>
       </c>
       <c r="H340" t="n">
         <v>5407</v>
@@ -10258,7 +10258,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G341" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H341" t="n">
         <v>3251</v>
@@ -10316,7 +10316,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G343" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H343" t="n">
         <v>100</v>
@@ -10345,7 +10345,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H344" t="n">
         <v>33</v>
@@ -10432,7 +10432,7 @@
         <v>21</v>
       </c>
       <c r="G347" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H347" t="n">
         <v>1330</v>
@@ -10461,7 +10461,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H348" t="n">
         <v>928</v>
@@ -10490,7 +10490,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H349" t="n">
         <v>1366</v>
@@ -10519,7 +10519,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G350" t="n">
-        <v>20.2893199920654</v>
+        <v>20.2893218994141</v>
       </c>
       <c r="H350" t="n">
         <v>18012</v>
@@ -10722,7 +10722,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>20.2893199920654</v>
+        <v>20.2893218994141</v>
       </c>
       <c r="H357" t="n">
         <v>291</v>
@@ -11070,7 +11070,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>23.1072826385498</v>
+        <v>23.1072807312012</v>
       </c>
       <c r="H369" t="n">
         <v>15210</v>
@@ -11534,7 +11534,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>24.6101932525635</v>
+        <v>24.6101951599121</v>
       </c>
       <c r="H385" t="n">
         <v>9687</v>
@@ -11882,7 +11882,7 @@
         <v>26</v>
       </c>
       <c r="G397" t="n">
-        <v>24.4223289489746</v>
+        <v>24.4223308563232</v>
       </c>
       <c r="H397" t="n">
         <v>777</v>
@@ -11911,7 +11911,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>24.6101932525635</v>
+        <v>24.6101951599121</v>
       </c>
       <c r="H398" t="n">
         <v>1281</v>
@@ -11969,7 +11969,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G400" t="n">
-        <v>25.737377166748</v>
+        <v>25.7373790740967</v>
       </c>
       <c r="H400" t="n">
         <v>3487</v>
@@ -12085,7 +12085,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>24.798059463501</v>
+        <v>24.7980575561523</v>
       </c>
       <c r="H404" t="n">
         <v>285</v>
@@ -12172,7 +12172,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>24.798059463501</v>
+        <v>24.7980575561523</v>
       </c>
       <c r="H407" t="n">
         <v>658</v>
@@ -12230,7 +12230,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>23.29514503479</v>
+        <v>23.2951431274414</v>
       </c>
       <c r="H409" t="n">
         <v>3492</v>
@@ -12317,7 +12317,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>24.2344646453857</v>
+        <v>24.2344665527344</v>
       </c>
       <c r="H412" t="n">
         <v>600</v>
@@ -12404,7 +12404,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G415" t="n">
-        <v>24.2344646453857</v>
+        <v>24.2344665527344</v>
       </c>
       <c r="H415" t="n">
         <v>140</v>
@@ -12433,7 +12433,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G416" t="n">
-        <v>24.2344646453857</v>
+        <v>24.2344665527344</v>
       </c>
       <c r="H416" t="n">
         <v>87</v>
@@ -12520,7 +12520,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G419" t="n">
-        <v>23.29514503479</v>
+        <v>23.2951431274414</v>
       </c>
       <c r="H419" t="n">
         <v>210</v>
@@ -12578,7 +12578,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>23.29514503479</v>
+        <v>23.2951431274414</v>
       </c>
       <c r="H421" t="n">
         <v>2392</v>
@@ -12723,7 +12723,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G426" t="n">
-        <v>24.6101932525635</v>
+        <v>24.6101951599121</v>
       </c>
       <c r="H426" t="n">
         <v>3659</v>
@@ -12781,7 +12781,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>24.798059463501</v>
+        <v>24.7980575561523</v>
       </c>
       <c r="H428" t="n">
         <v>4557</v>
@@ -12984,7 +12984,7 @@
         <v>26</v>
       </c>
       <c r="G435" t="n">
-        <v>24.4223289489746</v>
+        <v>24.4223308563232</v>
       </c>
       <c r="H435" t="n">
         <v>16881</v>
@@ -13071,7 +13071,7 @@
         <v>26</v>
       </c>
       <c r="G438" t="n">
-        <v>24.4223289489746</v>
+        <v>24.4223308563232</v>
       </c>
       <c r="H438" t="n">
         <v>193</v>
@@ -13129,7 +13129,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>24.798059463501</v>
+        <v>24.7980575561523</v>
       </c>
       <c r="H440" t="n">
         <v>111</v>
@@ -13564,7 +13564,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>24.6101932525635</v>
+        <v>24.6101951599121</v>
       </c>
       <c r="H455" t="n">
         <v>1466</v>
@@ -13651,7 +13651,7 @@
         <v>26</v>
       </c>
       <c r="G458" t="n">
-        <v>24.4223289489746</v>
+        <v>24.4223308563232</v>
       </c>
       <c r="H458" t="n">
         <v>809</v>
@@ -13738,7 +13738,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G461" t="n">
-        <v>23.1072826385498</v>
+        <v>23.1072807312012</v>
       </c>
       <c r="H461" t="n">
         <v>2523</v>
@@ -13767,7 +13767,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>19.53786277771</v>
+        <v>19.5378646850586</v>
       </c>
       <c r="H462" t="n">
         <v>4429</v>
@@ -13883,7 +13883,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G466" t="n">
-        <v>18.410680770874</v>
+        <v>18.4106788635254</v>
       </c>
       <c r="H466" t="n">
         <v>944</v>
@@ -14028,7 +14028,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G471" t="n">
-        <v>16.1563129425049</v>
+        <v>16.1563110351562</v>
       </c>
       <c r="H471" t="n">
         <v>2772</v>
@@ -14202,7 +14202,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>14.2776689529419</v>
+        <v>14.2776699066162</v>
       </c>
       <c r="H477" t="n">
         <v>1705</v>
@@ -14231,7 +14231,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>14.2776689529419</v>
+        <v>14.2776699066162</v>
       </c>
       <c r="H478" t="n">
         <v>1810</v>
@@ -14260,7 +14260,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G479" t="n">
-        <v>13.9958734512329</v>
+        <v>13.9958724975586</v>
       </c>
       <c r="H479" t="n">
         <v>200</v>
@@ -14347,7 +14347,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>15.6866512298584</v>
+        <v>15.6866502761841</v>
       </c>
       <c r="H482" t="n">
         <v>4167</v>
@@ -14376,7 +14376,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>15.6866512298584</v>
+        <v>15.6866502761841</v>
       </c>
       <c r="H483" t="n">
         <v>3514</v>
@@ -14492,7 +14492,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G487" t="n">
-        <v>16.1563129425049</v>
+        <v>16.1563110351562</v>
       </c>
       <c r="H487" t="n">
         <v>12961</v>
@@ -14579,7 +14579,7 @@
         <v>17.25</v>
       </c>
       <c r="G490" t="n">
-        <v>16.203275680542</v>
+        <v>16.2032775878906</v>
       </c>
       <c r="H490" t="n">
         <v>6624</v>
@@ -14695,7 +14695,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>15.6866512298584</v>
+        <v>15.6866502761841</v>
       </c>
       <c r="H494" t="n">
         <v>5139</v>
@@ -14753,7 +14753,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G496" t="n">
-        <v>16.1563129425049</v>
+        <v>16.1563110351562</v>
       </c>
       <c r="H496" t="n">
         <v>3600</v>
@@ -14811,7 +14811,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>15.6866512298584</v>
+        <v>15.6866502761841</v>
       </c>
       <c r="H498" t="n">
         <v>7270</v>
@@ -14927,7 +14927,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G502" t="n">
-        <v>16.8138332366943</v>
+        <v>16.813835144043</v>
       </c>
       <c r="H502" t="n">
         <v>3773</v>
@@ -15130,7 +15130,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G509" t="n">
-        <v>17.2365283966064</v>
+        <v>17.2365303039551</v>
       </c>
       <c r="H509" t="n">
         <v>1503</v>
@@ -15159,7 +15159,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>17.1895637512207</v>
+        <v>17.1895618438721</v>
       </c>
       <c r="H510" t="n">
         <v>255</v>
@@ -15217,7 +15217,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>16.7668704986572</v>
+        <v>16.7668685913086</v>
       </c>
       <c r="H512" t="n">
         <v>1779</v>
@@ -15246,7 +15246,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>16.7668704986572</v>
+        <v>16.7668685913086</v>
       </c>
       <c r="H513" t="n">
         <v>40</v>
@@ -15333,7 +15333,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>17.1895637512207</v>
+        <v>17.1895618438721</v>
       </c>
       <c r="H516" t="n">
         <v>1360</v>
@@ -15391,7 +15391,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G518" t="n">
-        <v>17.2365283966064</v>
+        <v>17.2365303039551</v>
       </c>
       <c r="H518" t="n">
         <v>1647</v>
@@ -15594,7 +15594,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>18.1288833618164</v>
+        <v>18.1288814544678</v>
       </c>
       <c r="H525" t="n">
         <v>5337</v>
@@ -15855,7 +15855,7 @@
         <v>19</v>
       </c>
       <c r="G534" t="n">
-        <v>17.8470859527588</v>
+        <v>17.8470878601074</v>
       </c>
       <c r="H534" t="n">
         <v>4414</v>
@@ -15884,7 +15884,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>18.410680770874</v>
+        <v>18.4106788635254</v>
       </c>
       <c r="H535" t="n">
         <v>1991</v>
@@ -15942,7 +15942,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>17.1895637512207</v>
+        <v>17.1895618438721</v>
       </c>
       <c r="H537" t="n">
         <v>7342</v>
@@ -15971,7 +15971,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>17.4243907928467</v>
+        <v>17.4243927001953</v>
       </c>
       <c r="H538" t="n">
         <v>589</v>
@@ -16029,7 +16029,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G540" t="n">
-        <v>17.2365283966064</v>
+        <v>17.2365303039551</v>
       </c>
       <c r="H540" t="n">
         <v>1317</v>
@@ -16087,7 +16087,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>16.8138332366943</v>
+        <v>16.813835144043</v>
       </c>
       <c r="H542" t="n">
         <v>756</v>
@@ -16116,7 +16116,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>17.2365283966064</v>
+        <v>17.2365303039551</v>
       </c>
       <c r="H543" t="n">
         <v>668</v>
@@ -16145,7 +16145,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G544" t="n">
-        <v>17.4243907928467</v>
+        <v>17.4243927001953</v>
       </c>
       <c r="H544" t="n">
         <v>800</v>
@@ -16174,7 +16174,7 @@
         <v>18.5</v>
       </c>
       <c r="G545" t="n">
-        <v>17.3774280548096</v>
+        <v>17.3774261474609</v>
       </c>
       <c r="H545" t="n">
         <v>23094</v>
@@ -16203,7 +16203,7 @@
         <v>19</v>
       </c>
       <c r="G546" t="n">
-        <v>17.8470859527588</v>
+        <v>17.8470878601074</v>
       </c>
       <c r="H546" t="n">
         <v>250</v>
@@ -16261,7 +16261,7 @@
         <v>18.5</v>
       </c>
       <c r="G548" t="n">
-        <v>17.3774280548096</v>
+        <v>17.3774261474609</v>
       </c>
       <c r="H548" t="n">
         <v>1240</v>
@@ -16812,7 +16812,7 @@
         <v>15.75</v>
       </c>
       <c r="G567" t="n">
-        <v>14.7942953109741</v>
+        <v>14.7942962646484</v>
       </c>
       <c r="H567" t="n">
         <v>14601</v>
@@ -17189,7 +17189,7 @@
         <v>15.75</v>
       </c>
       <c r="G580" t="n">
-        <v>14.7942953109741</v>
+        <v>14.7942962646484</v>
       </c>
       <c r="H580" t="n">
         <v>8207</v>
@@ -17247,7 +17247,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>14.4655332565308</v>
+        <v>14.4655342102051</v>
       </c>
       <c r="H582" t="n">
         <v>1389</v>
@@ -17450,7 +17450,7 @@
         <v>15.75</v>
       </c>
       <c r="G589" t="n">
-        <v>14.7942953109741</v>
+        <v>14.7942962646484</v>
       </c>
       <c r="H589" t="n">
         <v>4722</v>
@@ -17508,7 +17508,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G591" t="n">
-        <v>14.4655332565308</v>
+        <v>14.4655342102051</v>
       </c>
       <c r="H591" t="n">
         <v>6347</v>
@@ -17566,7 +17566,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G593" t="n">
-        <v>14.1837377548218</v>
+        <v>14.1837387084961</v>
       </c>
       <c r="H593" t="n">
         <v>6222</v>
@@ -17595,7 +17595,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>13.9958734512329</v>
+        <v>13.9958724975586</v>
       </c>
       <c r="H594" t="n">
         <v>11633</v>
@@ -17624,7 +17624,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G595" t="n">
-        <v>14.0428400039673</v>
+        <v>14.042839050293</v>
       </c>
       <c r="H595" t="n">
         <v>5431</v>
@@ -17653,7 +17653,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G596" t="n">
-        <v>13.9019422531128</v>
+        <v>13.9019412994385</v>
       </c>
       <c r="H596" t="n">
         <v>7311</v>
@@ -17711,7 +17711,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>13.9019422531128</v>
+        <v>13.9019412994385</v>
       </c>
       <c r="H598" t="n">
         <v>6014</v>
@@ -17769,7 +17769,7 @@
         <v>14.5</v>
       </c>
       <c r="G600" t="n">
-        <v>13.6201457977295</v>
+        <v>13.6201448440552</v>
       </c>
       <c r="H600" t="n">
         <v>17122</v>
@@ -62522,6 +62522,64 @@
         <v>5225</v>
       </c>
       <c r="I2143" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2144" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2144" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="D2144" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="E2144" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2144" t="n">
+        <v>23.2999992370605</v>
+      </c>
+      <c r="G2144" t="n">
+        <v>23.2999992370605</v>
+      </c>
+      <c r="H2144" t="n">
+        <v>2484</v>
+      </c>
+      <c r="I2144" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2145" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2145" t="n">
+        <v>23.1000003814697</v>
+      </c>
+      <c r="D2145" t="n">
+        <v>24.2999992370605</v>
+      </c>
+      <c r="E2145" t="n">
+        <v>23.1000003814697</v>
+      </c>
+      <c r="F2145" t="n">
+        <v>24.2999992370605</v>
+      </c>
+      <c r="G2145" t="n">
+        <v>24.2999992370605</v>
+      </c>
+      <c r="H2145" t="n">
+        <v>14324</v>
+      </c>
+      <c r="I2145" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -456,7 +456,7 @@
         <v>17.9139995574951</v>
       </c>
       <c r="G3" t="n">
-        <v>16.4445552825928</v>
+        <v>16.4445533752441</v>
       </c>
       <c r="H3" t="n">
         <v>4000</v>
@@ -514,7 +514,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G5" t="n">
-        <v>16.4225215911865</v>
+        <v>16.4225234985352</v>
       </c>
       <c r="H5" t="n">
         <v>1500</v>
@@ -572,7 +572,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G7" t="n">
-        <v>16.2848281860352</v>
+        <v>16.2848262786865</v>
       </c>
       <c r="H7" t="n">
         <v>4600</v>
@@ -601,7 +601,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G8" t="n">
-        <v>16.4225215911865</v>
+        <v>16.4225234985352</v>
       </c>
       <c r="H8" t="n">
         <v>11700</v>
@@ -630,7 +630,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G9" t="n">
-        <v>16.2481098175049</v>
+        <v>16.2481079101562</v>
       </c>
       <c r="H9" t="n">
         <v>1700</v>
@@ -717,7 +717,7 @@
         <v>17.5</v>
       </c>
       <c r="G12" t="n">
-        <v>16.0645122528076</v>
+        <v>16.0645141601562</v>
       </c>
       <c r="H12" t="n">
         <v>2300</v>
@@ -804,7 +804,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>16.2481098175049</v>
+        <v>16.2481079101562</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
@@ -833,7 +833,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G16" t="n">
-        <v>16.2481098175049</v>
+        <v>16.2481079101562</v>
       </c>
       <c r="H16" t="n">
         <v>300</v>
@@ -1094,7 +1094,7 @@
         <v>17.8840007781982</v>
       </c>
       <c r="G25" t="n">
-        <v>16.4170150756836</v>
+        <v>16.4170169830322</v>
       </c>
       <c r="H25" t="n">
         <v>400</v>
@@ -1181,7 +1181,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>16.3858032226562</v>
+        <v>16.3858051300049</v>
       </c>
       <c r="H28" t="n">
         <v>2600</v>
@@ -1268,7 +1268,7 @@
         <v>17.8780002593994</v>
       </c>
       <c r="G31" t="n">
-        <v>16.411506652832</v>
+        <v>16.4115085601807</v>
       </c>
       <c r="H31" t="n">
         <v>3000</v>
@@ -1355,7 +1355,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G34" t="n">
-        <v>16.2481098175049</v>
+        <v>16.2481079101562</v>
       </c>
       <c r="H34" t="n">
         <v>1900</v>
@@ -1645,7 +1645,7 @@
         <v>18.5</v>
       </c>
       <c r="G44" t="n">
-        <v>16.9824848175049</v>
+        <v>16.9824867248535</v>
       </c>
       <c r="H44" t="n">
         <v>17900</v>
@@ -1674,7 +1674,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>17.0283851623535</v>
+        <v>17.0283832550049</v>
       </c>
       <c r="H45" t="n">
         <v>10700</v>
@@ -1703,7 +1703,7 @@
         <v>19</v>
       </c>
       <c r="G46" t="n">
-        <v>17.4414730072021</v>
+        <v>17.4414710998535</v>
       </c>
       <c r="H46" t="n">
         <v>11600</v>
@@ -1790,7 +1790,7 @@
         <v>19</v>
       </c>
       <c r="G49" t="n">
-        <v>17.4414730072021</v>
+        <v>17.4414710998535</v>
       </c>
       <c r="H49" t="n">
         <v>400</v>
@@ -1993,7 +1993,7 @@
         <v>19</v>
       </c>
       <c r="G56" t="n">
-        <v>17.4414730072021</v>
+        <v>17.4414710998535</v>
       </c>
       <c r="H56" t="n">
         <v>1900</v>
@@ -2022,7 +2022,7 @@
         <v>19</v>
       </c>
       <c r="G57" t="n">
-        <v>17.4414730072021</v>
+        <v>17.4414710998535</v>
       </c>
       <c r="H57" t="n">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>19</v>
       </c>
       <c r="G58" t="n">
-        <v>17.4414730072021</v>
+        <v>17.4414710998535</v>
       </c>
       <c r="H58" t="n">
         <v>2100</v>
@@ -2080,7 +2080,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>17.3496742248535</v>
+        <v>17.3496761322021</v>
       </c>
       <c r="H59" t="n">
         <v>40500</v>
@@ -2283,7 +2283,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>17.3037776947021</v>
+        <v>17.3037757873535</v>
       </c>
       <c r="H66" t="n">
         <v>100</v>
@@ -2312,7 +2312,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>17.0742816925049</v>
+        <v>17.0742835998535</v>
       </c>
       <c r="H67" t="n">
         <v>2300</v>
@@ -2370,7 +2370,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G69" t="n">
-        <v>16.7988910675049</v>
+        <v>16.7988929748535</v>
       </c>
       <c r="H69" t="n">
         <v>1000</v>
@@ -2399,7 +2399,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>16.7988910675049</v>
+        <v>16.7988929748535</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G71" t="n">
-        <v>17.0283851623535</v>
+        <v>17.0283832550049</v>
       </c>
       <c r="H71" t="n">
         <v>100</v>
@@ -2457,7 +2457,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G72" t="n">
-        <v>17.0283851623535</v>
+        <v>17.0283832550049</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G73" t="n">
-        <v>17.0283851623535</v>
+        <v>17.0283832550049</v>
       </c>
       <c r="H73" t="n">
         <v>100</v>
@@ -2515,7 +2515,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G74" t="n">
-        <v>17.0283851623535</v>
+        <v>17.0283832550049</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G75" t="n">
-        <v>17.0283851623535</v>
+        <v>17.0283832550049</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>17.0742816925049</v>
+        <v>17.0742835998535</v>
       </c>
       <c r="H76" t="n">
         <v>100</v>
@@ -2631,7 +2631,7 @@
         <v>18.2280006408691</v>
       </c>
       <c r="G78" t="n">
-        <v>16.7327976226807</v>
+        <v>16.7327995300293</v>
       </c>
       <c r="H78" t="n">
         <v>3800</v>
@@ -2718,7 +2718,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G81" t="n">
-        <v>16.9090480804443</v>
+        <v>16.909049987793</v>
       </c>
       <c r="H81" t="n">
         <v>5200</v>
@@ -3008,7 +3008,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>16.2481098175049</v>
+        <v>16.2481079101562</v>
       </c>
       <c r="H91" t="n">
         <v>2800</v>
@@ -3037,7 +3037,7 @@
         <v>17.8339996337891</v>
       </c>
       <c r="G92" t="n">
-        <v>16.3711166381836</v>
+        <v>16.371114730835</v>
       </c>
       <c r="H92" t="n">
         <v>100</v>
@@ -3153,7 +3153,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G96" t="n">
-        <v>16.2848281860352</v>
+        <v>16.2848262786865</v>
       </c>
       <c r="H96" t="n">
         <v>100</v>
@@ -3182,7 +3182,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G97" t="n">
-        <v>15.7615842819214</v>
+        <v>15.7615833282471</v>
       </c>
       <c r="H97" t="n">
         <v>8500</v>
@@ -3269,7 +3269,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G100" t="n">
-        <v>15.8717412948608</v>
+        <v>15.8717403411865</v>
       </c>
       <c r="H100" t="n">
         <v>7000</v>
@@ -3298,7 +3298,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G101" t="n">
-        <v>15.7707643508911</v>
+        <v>15.7707633972168</v>
       </c>
       <c r="H101" t="n">
         <v>2200</v>
@@ -3414,7 +3414,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G105" t="n">
-        <v>15.5229091644287</v>
+        <v>15.5229110717773</v>
       </c>
       <c r="H105" t="n">
         <v>400</v>
@@ -3443,7 +3443,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>15.2383394241333</v>
+        <v>15.238338470459</v>
       </c>
       <c r="H106" t="n">
         <v>400</v>
@@ -3501,7 +3501,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G108" t="n">
-        <v>14.8711500167847</v>
+        <v>14.871150970459</v>
       </c>
       <c r="H108" t="n">
         <v>200</v>
@@ -3588,7 +3588,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G111" t="n">
-        <v>15.100643157959</v>
+        <v>15.1006441116333</v>
       </c>
       <c r="H111" t="n">
         <v>5100</v>
@@ -3617,7 +3617,7 @@
         <v>16.1119995117188</v>
       </c>
       <c r="G112" t="n">
-        <v>14.7903671264648</v>
+        <v>14.7903680801392</v>
       </c>
       <c r="H112" t="n">
         <v>5400</v>
@@ -3646,7 +3646,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>14.7793521881104</v>
+        <v>14.7793531417847</v>
       </c>
       <c r="H113" t="n">
         <v>100</v>
@@ -3820,7 +3820,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>14.8711500167847</v>
+        <v>14.871150970459</v>
       </c>
       <c r="H119" t="n">
         <v>100</v>
@@ -3849,7 +3849,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>14.595757484436</v>
+        <v>14.5957584381104</v>
       </c>
       <c r="H120" t="n">
         <v>1500</v>
@@ -3878,7 +3878,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G121" t="n">
-        <v>14.595757484436</v>
+        <v>14.5957584381104</v>
       </c>
       <c r="H121" t="n">
         <v>2300</v>
@@ -3907,7 +3907,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G122" t="n">
-        <v>14.595757484436</v>
+        <v>14.5957584381104</v>
       </c>
       <c r="H122" t="n">
         <v>100</v>
@@ -3994,7 +3994,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G125" t="n">
-        <v>14.8711500167847</v>
+        <v>14.871150970459</v>
       </c>
       <c r="H125" t="n">
         <v>1900</v>
@@ -4313,7 +4313,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>14.366265296936</v>
+        <v>14.3662643432617</v>
       </c>
       <c r="H136" t="n">
         <v>1600</v>
@@ -4371,7 +4371,7 @@
         <v>14.9280004501343</v>
       </c>
       <c r="G138" t="n">
-        <v>13.7034902572632</v>
+        <v>13.7034893035889</v>
       </c>
       <c r="H138" t="n">
         <v>4400</v>
@@ -4400,7 +4400,7 @@
         <v>15.3680000305176</v>
       </c>
       <c r="G139" t="n">
-        <v>14.1073961257935</v>
+        <v>14.1073970794678</v>
       </c>
       <c r="H139" t="n">
         <v>3000</v>
@@ -4429,7 +4429,7 @@
         <v>15.5</v>
       </c>
       <c r="G140" t="n">
-        <v>14.2285690307617</v>
+        <v>14.228569984436</v>
       </c>
       <c r="H140" t="n">
         <v>4200</v>
@@ -4458,7 +4458,7 @@
         <v>15.5</v>
       </c>
       <c r="G141" t="n">
-        <v>14.2285690307617</v>
+        <v>14.228569984436</v>
       </c>
       <c r="H141" t="n">
         <v>100</v>
@@ -4487,7 +4487,7 @@
         <v>15.5</v>
       </c>
       <c r="G142" t="n">
-        <v>14.2285690307617</v>
+        <v>14.228569984436</v>
       </c>
       <c r="H142" t="n">
         <v>200</v>
@@ -4516,7 +4516,7 @@
         <v>15.5</v>
       </c>
       <c r="G143" t="n">
-        <v>14.2285690307617</v>
+        <v>14.228569984436</v>
       </c>
       <c r="H143" t="n">
         <v>300</v>
@@ -4574,7 +4574,7 @@
         <v>15.5979995727539</v>
       </c>
       <c r="G145" t="n">
-        <v>14.3185300827026</v>
+        <v>14.318531036377</v>
       </c>
       <c r="H145" t="n">
         <v>4400</v>
@@ -4603,7 +4603,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G146" t="n">
-        <v>14.8160705566406</v>
+        <v>14.8160715103149</v>
       </c>
       <c r="H146" t="n">
         <v>1200</v>
@@ -4632,7 +4632,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>14.595757484436</v>
+        <v>14.5957584381104</v>
       </c>
       <c r="H147" t="n">
         <v>3100</v>
@@ -4690,7 +4690,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>14.0449752807617</v>
+        <v>14.0449743270874</v>
       </c>
       <c r="H149" t="n">
         <v>100</v>
@@ -5038,7 +5038,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G161" t="n">
-        <v>15.0731039047241</v>
+        <v>15.0731029510498</v>
       </c>
       <c r="H161" t="n">
         <v>1800</v>
@@ -5067,7 +5067,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G162" t="n">
-        <v>15.0731039047241</v>
+        <v>15.0731029510498</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>16.5179996490479</v>
       </c>
       <c r="G165" t="n">
-        <v>15.163064956665</v>
+        <v>15.1630640029907</v>
       </c>
       <c r="H165" t="n">
         <v>500</v>
@@ -5328,7 +5328,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G171" t="n">
-        <v>14.7793521881104</v>
+        <v>14.7793531417847</v>
       </c>
       <c r="H171" t="n">
         <v>1500</v>
@@ -5357,7 +5357,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>14.7793521881104</v>
+        <v>14.7793531417847</v>
       </c>
       <c r="H172" t="n">
         <v>100</v>
@@ -5444,7 +5444,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G175" t="n">
-        <v>15.3301362991333</v>
+        <v>15.3301372528076</v>
       </c>
       <c r="H175" t="n">
         <v>22000</v>
@@ -5502,7 +5502,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G177" t="n">
-        <v>15.1924381256104</v>
+        <v>15.192440032959</v>
       </c>
       <c r="H177" t="n">
         <v>100</v>
@@ -5531,7 +5531,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>15.6514253616333</v>
+        <v>15.651424407959</v>
       </c>
       <c r="H178" t="n">
         <v>3000</v>
@@ -5560,7 +5560,7 @@
         <v>17</v>
       </c>
       <c r="G179" t="n">
-        <v>15.6055278778076</v>
+        <v>15.6055269241333</v>
       </c>
       <c r="H179" t="n">
         <v>1000</v>
@@ -5589,7 +5589,7 @@
         <v>17</v>
       </c>
       <c r="G180" t="n">
-        <v>15.6055278778076</v>
+        <v>15.6055269241333</v>
       </c>
       <c r="H180" t="n">
         <v>200</v>
@@ -5618,7 +5618,7 @@
         <v>17</v>
       </c>
       <c r="G181" t="n">
-        <v>15.6055278778076</v>
+        <v>15.6055269241333</v>
       </c>
       <c r="H181" t="n">
         <v>1100</v>
@@ -5647,7 +5647,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G182" t="n">
-        <v>15.9268169403076</v>
+        <v>15.9268178939819</v>
       </c>
       <c r="H182" t="n">
         <v>800</v>
@@ -5676,7 +5676,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G183" t="n">
-        <v>15.9635353088379</v>
+        <v>15.9635372161865</v>
       </c>
       <c r="H183" t="n">
         <v>200</v>
@@ -5705,7 +5705,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G184" t="n">
-        <v>15.7340440750122</v>
+        <v>15.7340421676636</v>
       </c>
       <c r="H184" t="n">
         <v>200</v>
@@ -5792,7 +5792,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G187" t="n">
-        <v>15.6238889694214</v>
+        <v>15.6238870620728</v>
       </c>
       <c r="H187" t="n">
         <v>3500</v>
@@ -5821,7 +5821,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G188" t="n">
-        <v>15.9268169403076</v>
+        <v>15.9268178939819</v>
       </c>
       <c r="H188" t="n">
         <v>500</v>
@@ -5879,7 +5879,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G190" t="n">
-        <v>15.7799415588379</v>
+        <v>15.7799434661865</v>
       </c>
       <c r="H190" t="n">
         <v>400</v>
@@ -5937,7 +5937,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>15.9268169403076</v>
+        <v>15.9268178939819</v>
       </c>
       <c r="H192" t="n">
         <v>300</v>
@@ -6053,7 +6053,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G196" t="n">
-        <v>16.8447914123535</v>
+        <v>16.8447895050049</v>
       </c>
       <c r="H196" t="n">
         <v>1400</v>
@@ -6082,7 +6082,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G197" t="n">
-        <v>16.8539714813232</v>
+        <v>16.8539695739746</v>
       </c>
       <c r="H197" t="n">
         <v>400</v>
@@ -6169,7 +6169,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G200" t="n">
-        <v>16.3490829467773</v>
+        <v>16.349084854126</v>
       </c>
       <c r="H200" t="n">
         <v>2900</v>
@@ -6256,7 +6256,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>18.0840549468994</v>
+        <v>18.0840530395508</v>
       </c>
       <c r="H203" t="n">
         <v>18000</v>
@@ -6343,7 +6343,7 @@
         <v>21.7250003814697</v>
       </c>
       <c r="G206" t="n">
-        <v>19.9429473876953</v>
+        <v>19.9429454803467</v>
       </c>
       <c r="H206" t="n">
         <v>4300</v>
@@ -6401,7 +6401,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>18.956127166748</v>
+        <v>18.9561252593994</v>
       </c>
       <c r="H208" t="n">
         <v>1800</v>
@@ -6430,7 +6430,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G209" t="n">
-        <v>19.0020236968994</v>
+        <v>19.0020275115967</v>
       </c>
       <c r="H209" t="n">
         <v>1100</v>
@@ -6459,7 +6459,7 @@
         <v>20.6800003051758</v>
       </c>
       <c r="G210" t="n">
-        <v>18.9836673736572</v>
+        <v>18.9836654663086</v>
       </c>
       <c r="H210" t="n">
         <v>900</v>
@@ -6517,7 +6517,7 @@
         <v>21.6550006866455</v>
       </c>
       <c r="G212" t="n">
-        <v>19.8786888122559</v>
+        <v>19.8786907196045</v>
       </c>
       <c r="H212" t="n">
         <v>5800</v>
@@ -6546,7 +6546,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>20.2871856689453</v>
+        <v>20.2871875762939</v>
       </c>
       <c r="H213" t="n">
         <v>8600</v>
@@ -6575,7 +6575,7 @@
         <v>22.7450008392334</v>
       </c>
       <c r="G214" t="n">
-        <v>20.879280090332</v>
+        <v>20.8792781829834</v>
       </c>
       <c r="H214" t="n">
         <v>8100</v>
@@ -6633,7 +6633,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H216" t="n">
         <v>400</v>
@@ -6662,7 +6662,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G217" t="n">
-        <v>20.3789844512939</v>
+        <v>20.3789825439453</v>
       </c>
       <c r="H217" t="n">
         <v>36200</v>
@@ -6691,7 +6691,7 @@
         <v>22.1650009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>20.3468532562256</v>
+        <v>20.3468551635742</v>
       </c>
       <c r="H218" t="n">
         <v>6000</v>
@@ -6778,7 +6778,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H221" t="n">
         <v>2900</v>
@@ -6894,7 +6894,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G225" t="n">
-        <v>21.1867961883545</v>
+        <v>21.1867980957031</v>
       </c>
       <c r="H225" t="n">
         <v>5500</v>
@@ -6923,7 +6923,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G226" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H226" t="n">
         <v>9100</v>
@@ -6952,7 +6952,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H227" t="n">
         <v>6900</v>
@@ -7155,7 +7155,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G234" t="n">
-        <v>21.2969570159912</v>
+        <v>21.2969551086426</v>
       </c>
       <c r="H234" t="n">
         <v>3800</v>
@@ -7213,7 +7213,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H236" t="n">
         <v>200</v>
@@ -7242,7 +7242,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G237" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H237" t="n">
         <v>115</v>
@@ -7329,7 +7329,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G240" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H240" t="n">
         <v>550</v>
@@ -7387,7 +7387,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H242" t="n">
         <v>1115</v>
@@ -7503,7 +7503,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G246" t="n">
-        <v>20.5625782012939</v>
+        <v>20.5625762939453</v>
       </c>
       <c r="H246" t="n">
         <v>3610</v>
@@ -7532,7 +7532,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>19.8282012939453</v>
+        <v>19.8281993865967</v>
       </c>
       <c r="H247" t="n">
         <v>11926</v>
@@ -7590,7 +7590,7 @@
         <v>22</v>
       </c>
       <c r="G249" t="n">
-        <v>20.1953887939453</v>
+        <v>20.1953907012939</v>
       </c>
       <c r="H249" t="n">
         <v>2862</v>
@@ -7619,7 +7619,7 @@
         <v>22</v>
       </c>
       <c r="G250" t="n">
-        <v>20.1953887939453</v>
+        <v>20.1953907012939</v>
       </c>
       <c r="H250" t="n">
         <v>305</v>
@@ -7677,7 +7677,7 @@
         <v>22</v>
       </c>
       <c r="G252" t="n">
-        <v>20.1953887939453</v>
+        <v>20.1953907012939</v>
       </c>
       <c r="H252" t="n">
         <v>362</v>
@@ -7764,7 +7764,7 @@
         <v>21</v>
       </c>
       <c r="G255" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H255" t="n">
         <v>2005</v>
@@ -7851,7 +7851,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G258" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H258" t="n">
         <v>120</v>
@@ -7880,7 +7880,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G259" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H259" t="n">
         <v>745</v>
@@ -7938,7 +7938,7 @@
         <v>21</v>
       </c>
       <c r="G261" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H261" t="n">
         <v>565</v>
@@ -7967,7 +7967,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G262" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H262" t="n">
         <v>2949</v>
@@ -7996,7 +7996,7 @@
         <v>21</v>
       </c>
       <c r="G263" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H263" t="n">
         <v>1250</v>
@@ -8025,7 +8025,7 @@
         <v>21</v>
       </c>
       <c r="G264" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H264" t="n">
         <v>6111</v>
@@ -8054,7 +8054,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G265" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H265" t="n">
         <v>200</v>
@@ -8083,7 +8083,7 @@
         <v>21</v>
       </c>
       <c r="G266" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H266" t="n">
         <v>120</v>
@@ -8228,7 +8228,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G271" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H271" t="n">
         <v>100</v>
@@ -8257,7 +8257,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H272" t="n">
         <v>1646</v>
@@ -9272,7 +9272,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G307" t="n">
-        <v>20.2893218994141</v>
+        <v>20.2893199920654</v>
       </c>
       <c r="H307" t="n">
         <v>250</v>
@@ -9330,7 +9330,7 @@
         <v>21</v>
       </c>
       <c r="G309" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H309" t="n">
         <v>1476</v>
@@ -9359,7 +9359,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H310" t="n">
         <v>495</v>
@@ -9388,7 +9388,7 @@
         <v>21</v>
       </c>
       <c r="G311" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H311" t="n">
         <v>675</v>
@@ -9417,7 +9417,7 @@
         <v>21</v>
       </c>
       <c r="G312" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H312" t="n">
         <v>265</v>
@@ -9446,7 +9446,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G313" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H313" t="n">
         <v>3230</v>
@@ -9475,7 +9475,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H314" t="n">
         <v>320</v>
@@ -9504,7 +9504,7 @@
         <v>21</v>
       </c>
       <c r="G315" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H315" t="n">
         <v>50</v>
@@ -9533,7 +9533,7 @@
         <v>21</v>
       </c>
       <c r="G316" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H316" t="n">
         <v>465</v>
@@ -9562,7 +9562,7 @@
         <v>21</v>
       </c>
       <c r="G317" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H317" t="n">
         <v>3</v>
@@ -9591,7 +9591,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>19.3499984741211</v>
+        <v>19.3500003814697</v>
       </c>
       <c r="H318" t="n">
         <v>30</v>
@@ -9620,7 +9620,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>19.3499984741211</v>
+        <v>19.3500003814697</v>
       </c>
       <c r="H319" t="n">
         <v>326</v>
@@ -9649,7 +9649,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G320" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H320" t="n">
         <v>422</v>
@@ -9678,7 +9678,7 @@
         <v>21</v>
       </c>
       <c r="G321" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H321" t="n">
         <v>286</v>
@@ -9707,7 +9707,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H322" t="n">
         <v>360</v>
@@ -9765,7 +9765,7 @@
         <v>21</v>
       </c>
       <c r="G324" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H324" t="n">
         <v>940</v>
@@ -9968,7 +9968,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H331" t="n">
         <v>380</v>
@@ -9997,7 +9997,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>19.3499984741211</v>
+        <v>19.3500003814697</v>
       </c>
       <c r="H332" t="n">
         <v>163</v>
@@ -10026,7 +10026,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>19.1621341705322</v>
+        <v>19.1621360778809</v>
       </c>
       <c r="H333" t="n">
         <v>9842</v>
@@ -10055,7 +10055,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G334" t="n">
-        <v>18.974271774292</v>
+        <v>18.9742736816406</v>
       </c>
       <c r="H334" t="n">
         <v>1547</v>
@@ -10084,7 +10084,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>18.974271774292</v>
+        <v>18.9742736816406</v>
       </c>
       <c r="H335" t="n">
         <v>4339</v>
@@ -10113,7 +10113,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G336" t="n">
-        <v>18.974271774292</v>
+        <v>18.9742736816406</v>
       </c>
       <c r="H336" t="n">
         <v>4539</v>
@@ -10142,7 +10142,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>19.1621341705322</v>
+        <v>19.1621360778809</v>
       </c>
       <c r="H337" t="n">
         <v>1942</v>
@@ -10171,7 +10171,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>19.1621341705322</v>
+        <v>19.1621360778809</v>
       </c>
       <c r="H338" t="n">
         <v>284</v>
@@ -10200,7 +10200,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>19.3499984741211</v>
+        <v>19.3500003814697</v>
       </c>
       <c r="H339" t="n">
         <v>2218</v>
@@ -10229,7 +10229,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H340" t="n">
         <v>5407</v>
@@ -10258,7 +10258,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G341" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H341" t="n">
         <v>3251</v>
@@ -10316,7 +10316,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G343" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H343" t="n">
         <v>100</v>
@@ -10345,7 +10345,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H344" t="n">
         <v>33</v>
@@ -10432,7 +10432,7 @@
         <v>21</v>
       </c>
       <c r="G347" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H347" t="n">
         <v>1330</v>
@@ -10461,7 +10461,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H348" t="n">
         <v>928</v>
@@ -10490,7 +10490,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H349" t="n">
         <v>1366</v>
@@ -10519,7 +10519,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G350" t="n">
-        <v>20.2893218994141</v>
+        <v>20.2893199920654</v>
       </c>
       <c r="H350" t="n">
         <v>18012</v>
@@ -10722,7 +10722,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>20.2893218994141</v>
+        <v>20.2893199920654</v>
       </c>
       <c r="H357" t="n">
         <v>291</v>
@@ -11070,7 +11070,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>23.1072807312012</v>
+        <v>23.1072826385498</v>
       </c>
       <c r="H369" t="n">
         <v>15210</v>
@@ -11534,7 +11534,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>24.6101951599121</v>
+        <v>24.6101932525635</v>
       </c>
       <c r="H385" t="n">
         <v>9687</v>
@@ -11882,7 +11882,7 @@
         <v>26</v>
       </c>
       <c r="G397" t="n">
-        <v>24.4223308563232</v>
+        <v>24.4223289489746</v>
       </c>
       <c r="H397" t="n">
         <v>777</v>
@@ -11911,7 +11911,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>24.6101951599121</v>
+        <v>24.6101932525635</v>
       </c>
       <c r="H398" t="n">
         <v>1281</v>
@@ -11969,7 +11969,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G400" t="n">
-        <v>25.7373790740967</v>
+        <v>25.737377166748</v>
       </c>
       <c r="H400" t="n">
         <v>3487</v>
@@ -12085,7 +12085,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>24.7980575561523</v>
+        <v>24.798059463501</v>
       </c>
       <c r="H404" t="n">
         <v>285</v>
@@ -12172,7 +12172,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>24.7980575561523</v>
+        <v>24.798059463501</v>
       </c>
       <c r="H407" t="n">
         <v>658</v>
@@ -12230,7 +12230,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>23.2951431274414</v>
+        <v>23.29514503479</v>
       </c>
       <c r="H409" t="n">
         <v>3492</v>
@@ -12317,7 +12317,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>24.2344665527344</v>
+        <v>24.2344646453857</v>
       </c>
       <c r="H412" t="n">
         <v>600</v>
@@ -12404,7 +12404,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G415" t="n">
-        <v>24.2344665527344</v>
+        <v>24.2344646453857</v>
       </c>
       <c r="H415" t="n">
         <v>140</v>
@@ -12433,7 +12433,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G416" t="n">
-        <v>24.2344665527344</v>
+        <v>24.2344646453857</v>
       </c>
       <c r="H416" t="n">
         <v>87</v>
@@ -12520,7 +12520,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G419" t="n">
-        <v>23.2951431274414</v>
+        <v>23.29514503479</v>
       </c>
       <c r="H419" t="n">
         <v>210</v>
@@ -12578,7 +12578,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>23.2951431274414</v>
+        <v>23.29514503479</v>
       </c>
       <c r="H421" t="n">
         <v>2392</v>
@@ -12723,7 +12723,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G426" t="n">
-        <v>24.6101951599121</v>
+        <v>24.6101932525635</v>
       </c>
       <c r="H426" t="n">
         <v>3659</v>
@@ -12781,7 +12781,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>24.7980575561523</v>
+        <v>24.798059463501</v>
       </c>
       <c r="H428" t="n">
         <v>4557</v>
@@ -12984,7 +12984,7 @@
         <v>26</v>
       </c>
       <c r="G435" t="n">
-        <v>24.4223308563232</v>
+        <v>24.4223289489746</v>
       </c>
       <c r="H435" t="n">
         <v>16881</v>
@@ -13071,7 +13071,7 @@
         <v>26</v>
       </c>
       <c r="G438" t="n">
-        <v>24.4223308563232</v>
+        <v>24.4223289489746</v>
       </c>
       <c r="H438" t="n">
         <v>193</v>
@@ -13129,7 +13129,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>24.7980575561523</v>
+        <v>24.798059463501</v>
       </c>
       <c r="H440" t="n">
         <v>111</v>
@@ -13564,7 +13564,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>24.6101951599121</v>
+        <v>24.6101932525635</v>
       </c>
       <c r="H455" t="n">
         <v>1466</v>
@@ -13651,7 +13651,7 @@
         <v>26</v>
       </c>
       <c r="G458" t="n">
-        <v>24.4223308563232</v>
+        <v>24.4223289489746</v>
       </c>
       <c r="H458" t="n">
         <v>809</v>
@@ -13738,7 +13738,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G461" t="n">
-        <v>23.1072807312012</v>
+        <v>23.1072826385498</v>
       </c>
       <c r="H461" t="n">
         <v>2523</v>
@@ -13767,7 +13767,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H462" t="n">
         <v>4429</v>
@@ -13883,7 +13883,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G466" t="n">
-        <v>18.4106788635254</v>
+        <v>18.410680770874</v>
       </c>
       <c r="H466" t="n">
         <v>944</v>
@@ -14028,7 +14028,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G471" t="n">
-        <v>16.1563110351562</v>
+        <v>16.1563129425049</v>
       </c>
       <c r="H471" t="n">
         <v>2772</v>
@@ -14202,7 +14202,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>14.2776699066162</v>
+        <v>14.2776689529419</v>
       </c>
       <c r="H477" t="n">
         <v>1705</v>
@@ -14231,7 +14231,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>14.2776699066162</v>
+        <v>14.2776689529419</v>
       </c>
       <c r="H478" t="n">
         <v>1810</v>
@@ -14260,7 +14260,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G479" t="n">
-        <v>13.9958724975586</v>
+        <v>13.9958734512329</v>
       </c>
       <c r="H479" t="n">
         <v>200</v>
@@ -14347,7 +14347,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>15.6866502761841</v>
+        <v>15.6866512298584</v>
       </c>
       <c r="H482" t="n">
         <v>4167</v>
@@ -14376,7 +14376,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>15.6866502761841</v>
+        <v>15.6866512298584</v>
       </c>
       <c r="H483" t="n">
         <v>3514</v>
@@ -14492,7 +14492,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G487" t="n">
-        <v>16.1563110351562</v>
+        <v>16.1563129425049</v>
       </c>
       <c r="H487" t="n">
         <v>12961</v>
@@ -14579,7 +14579,7 @@
         <v>17.25</v>
       </c>
       <c r="G490" t="n">
-        <v>16.2032775878906</v>
+        <v>16.203275680542</v>
       </c>
       <c r="H490" t="n">
         <v>6624</v>
@@ -14695,7 +14695,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>15.6866502761841</v>
+        <v>15.6866512298584</v>
       </c>
       <c r="H494" t="n">
         <v>5139</v>
@@ -14753,7 +14753,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G496" t="n">
-        <v>16.1563110351562</v>
+        <v>16.1563129425049</v>
       </c>
       <c r="H496" t="n">
         <v>3600</v>
@@ -14811,7 +14811,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>15.6866502761841</v>
+        <v>15.6866512298584</v>
       </c>
       <c r="H498" t="n">
         <v>7270</v>
@@ -14927,7 +14927,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G502" t="n">
-        <v>16.813835144043</v>
+        <v>16.8138332366943</v>
       </c>
       <c r="H502" t="n">
         <v>3773</v>
@@ -15130,7 +15130,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G509" t="n">
-        <v>17.2365303039551</v>
+        <v>17.2365283966064</v>
       </c>
       <c r="H509" t="n">
         <v>1503</v>
@@ -15159,7 +15159,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>17.1895618438721</v>
+        <v>17.1895637512207</v>
       </c>
       <c r="H510" t="n">
         <v>255</v>
@@ -15217,7 +15217,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>16.7668685913086</v>
+        <v>16.7668704986572</v>
       </c>
       <c r="H512" t="n">
         <v>1779</v>
@@ -15246,7 +15246,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>16.7668685913086</v>
+        <v>16.7668704986572</v>
       </c>
       <c r="H513" t="n">
         <v>40</v>
@@ -15333,7 +15333,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>17.1895618438721</v>
+        <v>17.1895637512207</v>
       </c>
       <c r="H516" t="n">
         <v>1360</v>
@@ -15391,7 +15391,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G518" t="n">
-        <v>17.2365303039551</v>
+        <v>17.2365283966064</v>
       </c>
       <c r="H518" t="n">
         <v>1647</v>
@@ -15594,7 +15594,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>18.1288814544678</v>
+        <v>18.1288833618164</v>
       </c>
       <c r="H525" t="n">
         <v>5337</v>
@@ -15855,7 +15855,7 @@
         <v>19</v>
       </c>
       <c r="G534" t="n">
-        <v>17.8470878601074</v>
+        <v>17.8470859527588</v>
       </c>
       <c r="H534" t="n">
         <v>4414</v>
@@ -15884,7 +15884,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>18.4106788635254</v>
+        <v>18.410680770874</v>
       </c>
       <c r="H535" t="n">
         <v>1991</v>
@@ -15942,7 +15942,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>17.1895618438721</v>
+        <v>17.1895637512207</v>
       </c>
       <c r="H537" t="n">
         <v>7342</v>
@@ -15971,7 +15971,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>17.4243927001953</v>
+        <v>17.4243907928467</v>
       </c>
       <c r="H538" t="n">
         <v>589</v>
@@ -16029,7 +16029,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G540" t="n">
-        <v>17.2365303039551</v>
+        <v>17.2365283966064</v>
       </c>
       <c r="H540" t="n">
         <v>1317</v>
@@ -16087,7 +16087,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>16.813835144043</v>
+        <v>16.8138332366943</v>
       </c>
       <c r="H542" t="n">
         <v>756</v>
@@ -16116,7 +16116,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>17.2365303039551</v>
+        <v>17.2365283966064</v>
       </c>
       <c r="H543" t="n">
         <v>668</v>
@@ -16145,7 +16145,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G544" t="n">
-        <v>17.4243927001953</v>
+        <v>17.4243907928467</v>
       </c>
       <c r="H544" t="n">
         <v>800</v>
@@ -16174,7 +16174,7 @@
         <v>18.5</v>
       </c>
       <c r="G545" t="n">
-        <v>17.3774261474609</v>
+        <v>17.3774280548096</v>
       </c>
       <c r="H545" t="n">
         <v>23094</v>
@@ -16203,7 +16203,7 @@
         <v>19</v>
       </c>
       <c r="G546" t="n">
-        <v>17.8470878601074</v>
+        <v>17.8470859527588</v>
       </c>
       <c r="H546" t="n">
         <v>250</v>
@@ -16261,7 +16261,7 @@
         <v>18.5</v>
       </c>
       <c r="G548" t="n">
-        <v>17.3774261474609</v>
+        <v>17.3774280548096</v>
       </c>
       <c r="H548" t="n">
         <v>1240</v>
@@ -16812,7 +16812,7 @@
         <v>15.75</v>
       </c>
       <c r="G567" t="n">
-        <v>14.7942962646484</v>
+        <v>14.7942953109741</v>
       </c>
       <c r="H567" t="n">
         <v>14601</v>
@@ -17189,7 +17189,7 @@
         <v>15.75</v>
       </c>
       <c r="G580" t="n">
-        <v>14.7942962646484</v>
+        <v>14.7942953109741</v>
       </c>
       <c r="H580" t="n">
         <v>8207</v>
@@ -17247,7 +17247,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>14.4655342102051</v>
+        <v>14.4655332565308</v>
       </c>
       <c r="H582" t="n">
         <v>1389</v>
@@ -17450,7 +17450,7 @@
         <v>15.75</v>
       </c>
       <c r="G589" t="n">
-        <v>14.7942962646484</v>
+        <v>14.7942953109741</v>
       </c>
       <c r="H589" t="n">
         <v>4722</v>
@@ -17508,7 +17508,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G591" t="n">
-        <v>14.4655342102051</v>
+        <v>14.4655332565308</v>
       </c>
       <c r="H591" t="n">
         <v>6347</v>
@@ -17566,7 +17566,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G593" t="n">
-        <v>14.1837387084961</v>
+        <v>14.1837377548218</v>
       </c>
       <c r="H593" t="n">
         <v>6222</v>
@@ -17595,7 +17595,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>13.9958724975586</v>
+        <v>13.9958734512329</v>
       </c>
       <c r="H594" t="n">
         <v>11633</v>
@@ -17624,7 +17624,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G595" t="n">
-        <v>14.042839050293</v>
+        <v>14.0428400039673</v>
       </c>
       <c r="H595" t="n">
         <v>5431</v>
@@ -17653,7 +17653,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G596" t="n">
-        <v>13.9019412994385</v>
+        <v>13.9019422531128</v>
       </c>
       <c r="H596" t="n">
         <v>7311</v>
@@ -17711,7 +17711,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>13.9019412994385</v>
+        <v>13.9019422531128</v>
       </c>
       <c r="H598" t="n">
         <v>6014</v>
@@ -17769,7 +17769,7 @@
         <v>14.5</v>
       </c>
       <c r="G600" t="n">
-        <v>13.6201448440552</v>
+        <v>13.6201457977295</v>
       </c>
       <c r="H600" t="n">
         <v>17122</v>
@@ -62580,6 +62580,35 @@
         <v>14324</v>
       </c>
       <c r="I2145" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2146" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2146" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="D2146" t="n">
+        <v>25</v>
+      </c>
+      <c r="E2146" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2146" t="n">
+        <v>24.7999992370605</v>
+      </c>
+      <c r="G2146" t="n">
+        <v>24.7999992370605</v>
+      </c>
+      <c r="H2146" t="n">
+        <v>16215</v>
+      </c>
+      <c r="I2146" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -62612,6 +62612,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2147">
+      <c r="A2147" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2147" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2147" t="n">
+        <v>24.7000007629395</v>
+      </c>
+      <c r="D2147" t="n">
+        <v>25.7000007629395</v>
+      </c>
+      <c r="E2147" t="n">
+        <v>24.3999996185303</v>
+      </c>
+      <c r="F2147" t="n">
+        <v>25.6000003814697</v>
+      </c>
+      <c r="G2147" t="n">
+        <v>25.6000003814697</v>
+      </c>
+      <c r="H2147" t="n">
+        <v>10722</v>
+      </c>
+      <c r="I2147" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -456,7 +456,7 @@
         <v>17.9139995574951</v>
       </c>
       <c r="G3" t="n">
-        <v>16.4445533752441</v>
+        <v>16.4445552825928</v>
       </c>
       <c r="H3" t="n">
         <v>4000</v>
@@ -514,7 +514,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G5" t="n">
-        <v>16.4225234985352</v>
+        <v>16.4225215911865</v>
       </c>
       <c r="H5" t="n">
         <v>1500</v>
@@ -572,7 +572,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G7" t="n">
-        <v>16.2848262786865</v>
+        <v>16.2848281860352</v>
       </c>
       <c r="H7" t="n">
         <v>4600</v>
@@ -601,7 +601,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G8" t="n">
-        <v>16.4225234985352</v>
+        <v>16.4225215911865</v>
       </c>
       <c r="H8" t="n">
         <v>11700</v>
@@ -630,7 +630,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G9" t="n">
-        <v>16.2481079101562</v>
+        <v>16.2481098175049</v>
       </c>
       <c r="H9" t="n">
         <v>1700</v>
@@ -717,7 +717,7 @@
         <v>17.5</v>
       </c>
       <c r="G12" t="n">
-        <v>16.0645141601562</v>
+        <v>16.0645122528076</v>
       </c>
       <c r="H12" t="n">
         <v>2300</v>
@@ -804,7 +804,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>16.2481079101562</v>
+        <v>16.2481098175049</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
@@ -833,7 +833,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G16" t="n">
-        <v>16.2481079101562</v>
+        <v>16.2481098175049</v>
       </c>
       <c r="H16" t="n">
         <v>300</v>
@@ -1094,7 +1094,7 @@
         <v>17.8840007781982</v>
       </c>
       <c r="G25" t="n">
-        <v>16.4170169830322</v>
+        <v>16.4170150756836</v>
       </c>
       <c r="H25" t="n">
         <v>400</v>
@@ -1181,7 +1181,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>16.3858051300049</v>
+        <v>16.3858032226562</v>
       </c>
       <c r="H28" t="n">
         <v>2600</v>
@@ -1268,7 +1268,7 @@
         <v>17.8780002593994</v>
       </c>
       <c r="G31" t="n">
-        <v>16.4115085601807</v>
+        <v>16.411506652832</v>
       </c>
       <c r="H31" t="n">
         <v>3000</v>
@@ -1355,7 +1355,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G34" t="n">
-        <v>16.2481079101562</v>
+        <v>16.2481098175049</v>
       </c>
       <c r="H34" t="n">
         <v>1900</v>
@@ -1645,7 +1645,7 @@
         <v>18.5</v>
       </c>
       <c r="G44" t="n">
-        <v>16.9824867248535</v>
+        <v>16.9824848175049</v>
       </c>
       <c r="H44" t="n">
         <v>17900</v>
@@ -1674,7 +1674,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>17.0283832550049</v>
+        <v>17.0283851623535</v>
       </c>
       <c r="H45" t="n">
         <v>10700</v>
@@ -1703,7 +1703,7 @@
         <v>19</v>
       </c>
       <c r="G46" t="n">
-        <v>17.4414710998535</v>
+        <v>17.4414730072021</v>
       </c>
       <c r="H46" t="n">
         <v>11600</v>
@@ -1790,7 +1790,7 @@
         <v>19</v>
       </c>
       <c r="G49" t="n">
-        <v>17.4414710998535</v>
+        <v>17.4414730072021</v>
       </c>
       <c r="H49" t="n">
         <v>400</v>
@@ -1993,7 +1993,7 @@
         <v>19</v>
       </c>
       <c r="G56" t="n">
-        <v>17.4414710998535</v>
+        <v>17.4414730072021</v>
       </c>
       <c r="H56" t="n">
         <v>1900</v>
@@ -2022,7 +2022,7 @@
         <v>19</v>
       </c>
       <c r="G57" t="n">
-        <v>17.4414710998535</v>
+        <v>17.4414730072021</v>
       </c>
       <c r="H57" t="n">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>19</v>
       </c>
       <c r="G58" t="n">
-        <v>17.4414710998535</v>
+        <v>17.4414730072021</v>
       </c>
       <c r="H58" t="n">
         <v>2100</v>
@@ -2080,7 +2080,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G59" t="n">
-        <v>17.3496761322021</v>
+        <v>17.3496742248535</v>
       </c>
       <c r="H59" t="n">
         <v>40500</v>
@@ -2283,7 +2283,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G66" t="n">
-        <v>17.3037757873535</v>
+        <v>17.3037776947021</v>
       </c>
       <c r="H66" t="n">
         <v>100</v>
@@ -2312,7 +2312,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>17.0742835998535</v>
+        <v>17.0742816925049</v>
       </c>
       <c r="H67" t="n">
         <v>2300</v>
@@ -2370,7 +2370,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G69" t="n">
-        <v>16.7988929748535</v>
+        <v>16.7988910675049</v>
       </c>
       <c r="H69" t="n">
         <v>1000</v>
@@ -2399,7 +2399,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>16.7988929748535</v>
+        <v>16.7988910675049</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G71" t="n">
-        <v>17.0283832550049</v>
+        <v>17.0283851623535</v>
       </c>
       <c r="H71" t="n">
         <v>100</v>
@@ -2457,7 +2457,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G72" t="n">
-        <v>17.0283832550049</v>
+        <v>17.0283851623535</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G73" t="n">
-        <v>17.0283832550049</v>
+        <v>17.0283851623535</v>
       </c>
       <c r="H73" t="n">
         <v>100</v>
@@ -2515,7 +2515,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G74" t="n">
-        <v>17.0283832550049</v>
+        <v>17.0283851623535</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G75" t="n">
-        <v>17.0283832550049</v>
+        <v>17.0283851623535</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>17.0742835998535</v>
+        <v>17.0742816925049</v>
       </c>
       <c r="H76" t="n">
         <v>100</v>
@@ -2631,7 +2631,7 @@
         <v>18.2280006408691</v>
       </c>
       <c r="G78" t="n">
-        <v>16.7327995300293</v>
+        <v>16.7327976226807</v>
       </c>
       <c r="H78" t="n">
         <v>3800</v>
@@ -2718,7 +2718,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G81" t="n">
-        <v>16.909049987793</v>
+        <v>16.9090480804443</v>
       </c>
       <c r="H81" t="n">
         <v>5200</v>
@@ -3008,7 +3008,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>16.2481079101562</v>
+        <v>16.2481098175049</v>
       </c>
       <c r="H91" t="n">
         <v>2800</v>
@@ -3037,7 +3037,7 @@
         <v>17.8339996337891</v>
       </c>
       <c r="G92" t="n">
-        <v>16.371114730835</v>
+        <v>16.3711166381836</v>
       </c>
       <c r="H92" t="n">
         <v>100</v>
@@ -3153,7 +3153,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G96" t="n">
-        <v>16.2848262786865</v>
+        <v>16.2848281860352</v>
       </c>
       <c r="H96" t="n">
         <v>100</v>
@@ -3182,7 +3182,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G97" t="n">
-        <v>15.7615833282471</v>
+        <v>15.7615842819214</v>
       </c>
       <c r="H97" t="n">
         <v>8500</v>
@@ -3269,7 +3269,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G100" t="n">
-        <v>15.8717403411865</v>
+        <v>15.8717412948608</v>
       </c>
       <c r="H100" t="n">
         <v>7000</v>
@@ -3298,7 +3298,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G101" t="n">
-        <v>15.7707633972168</v>
+        <v>15.7707643508911</v>
       </c>
       <c r="H101" t="n">
         <v>2200</v>
@@ -3414,7 +3414,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G105" t="n">
-        <v>15.5229110717773</v>
+        <v>15.5229091644287</v>
       </c>
       <c r="H105" t="n">
         <v>400</v>
@@ -3443,7 +3443,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>15.238338470459</v>
+        <v>15.2383394241333</v>
       </c>
       <c r="H106" t="n">
         <v>400</v>
@@ -3501,7 +3501,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G108" t="n">
-        <v>14.871150970459</v>
+        <v>14.8711500167847</v>
       </c>
       <c r="H108" t="n">
         <v>200</v>
@@ -3588,7 +3588,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G111" t="n">
-        <v>15.1006441116333</v>
+        <v>15.100643157959</v>
       </c>
       <c r="H111" t="n">
         <v>5100</v>
@@ -3617,7 +3617,7 @@
         <v>16.1119995117188</v>
       </c>
       <c r="G112" t="n">
-        <v>14.7903680801392</v>
+        <v>14.7903671264648</v>
       </c>
       <c r="H112" t="n">
         <v>5400</v>
@@ -3646,7 +3646,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>14.7793531417847</v>
+        <v>14.7793521881104</v>
       </c>
       <c r="H113" t="n">
         <v>100</v>
@@ -3820,7 +3820,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>14.871150970459</v>
+        <v>14.8711500167847</v>
       </c>
       <c r="H119" t="n">
         <v>100</v>
@@ -3849,7 +3849,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>14.5957584381104</v>
+        <v>14.595757484436</v>
       </c>
       <c r="H120" t="n">
         <v>1500</v>
@@ -3878,7 +3878,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G121" t="n">
-        <v>14.5957584381104</v>
+        <v>14.595757484436</v>
       </c>
       <c r="H121" t="n">
         <v>2300</v>
@@ -3907,7 +3907,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G122" t="n">
-        <v>14.5957584381104</v>
+        <v>14.595757484436</v>
       </c>
       <c r="H122" t="n">
         <v>100</v>
@@ -3994,7 +3994,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G125" t="n">
-        <v>14.871150970459</v>
+        <v>14.8711500167847</v>
       </c>
       <c r="H125" t="n">
         <v>1900</v>
@@ -4313,7 +4313,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>14.3662643432617</v>
+        <v>14.366265296936</v>
       </c>
       <c r="H136" t="n">
         <v>1600</v>
@@ -4371,7 +4371,7 @@
         <v>14.9280004501343</v>
       </c>
       <c r="G138" t="n">
-        <v>13.7034893035889</v>
+        <v>13.7034902572632</v>
       </c>
       <c r="H138" t="n">
         <v>4400</v>
@@ -4400,7 +4400,7 @@
         <v>15.3680000305176</v>
       </c>
       <c r="G139" t="n">
-        <v>14.1073970794678</v>
+        <v>14.1073961257935</v>
       </c>
       <c r="H139" t="n">
         <v>3000</v>
@@ -4429,7 +4429,7 @@
         <v>15.5</v>
       </c>
       <c r="G140" t="n">
-        <v>14.228569984436</v>
+        <v>14.2285690307617</v>
       </c>
       <c r="H140" t="n">
         <v>4200</v>
@@ -4458,7 +4458,7 @@
         <v>15.5</v>
       </c>
       <c r="G141" t="n">
-        <v>14.228569984436</v>
+        <v>14.2285690307617</v>
       </c>
       <c r="H141" t="n">
         <v>100</v>
@@ -4487,7 +4487,7 @@
         <v>15.5</v>
       </c>
       <c r="G142" t="n">
-        <v>14.228569984436</v>
+        <v>14.2285690307617</v>
       </c>
       <c r="H142" t="n">
         <v>200</v>
@@ -4516,7 +4516,7 @@
         <v>15.5</v>
       </c>
       <c r="G143" t="n">
-        <v>14.228569984436</v>
+        <v>14.2285690307617</v>
       </c>
       <c r="H143" t="n">
         <v>300</v>
@@ -4574,7 +4574,7 @@
         <v>15.5979995727539</v>
       </c>
       <c r="G145" t="n">
-        <v>14.318531036377</v>
+        <v>14.3185300827026</v>
       </c>
       <c r="H145" t="n">
         <v>4400</v>
@@ -4603,7 +4603,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G146" t="n">
-        <v>14.8160715103149</v>
+        <v>14.8160705566406</v>
       </c>
       <c r="H146" t="n">
         <v>1200</v>
@@ -4632,7 +4632,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>14.5957584381104</v>
+        <v>14.595757484436</v>
       </c>
       <c r="H147" t="n">
         <v>3100</v>
@@ -4690,7 +4690,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>14.0449743270874</v>
+        <v>14.0449752807617</v>
       </c>
       <c r="H149" t="n">
         <v>100</v>
@@ -5038,7 +5038,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G161" t="n">
-        <v>15.0731029510498</v>
+        <v>15.0731039047241</v>
       </c>
       <c r="H161" t="n">
         <v>1800</v>
@@ -5067,7 +5067,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G162" t="n">
-        <v>15.0731029510498</v>
+        <v>15.0731039047241</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>16.5179996490479</v>
       </c>
       <c r="G165" t="n">
-        <v>15.1630640029907</v>
+        <v>15.163064956665</v>
       </c>
       <c r="H165" t="n">
         <v>500</v>
@@ -5328,7 +5328,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G171" t="n">
-        <v>14.7793531417847</v>
+        <v>14.7793521881104</v>
       </c>
       <c r="H171" t="n">
         <v>1500</v>
@@ -5357,7 +5357,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>14.7793531417847</v>
+        <v>14.7793521881104</v>
       </c>
       <c r="H172" t="n">
         <v>100</v>
@@ -5444,7 +5444,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G175" t="n">
-        <v>15.3301372528076</v>
+        <v>15.3301362991333</v>
       </c>
       <c r="H175" t="n">
         <v>22000</v>
@@ -5502,7 +5502,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G177" t="n">
-        <v>15.192440032959</v>
+        <v>15.1924381256104</v>
       </c>
       <c r="H177" t="n">
         <v>100</v>
@@ -5531,7 +5531,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>15.651424407959</v>
+        <v>15.6514253616333</v>
       </c>
       <c r="H178" t="n">
         <v>3000</v>
@@ -5560,7 +5560,7 @@
         <v>17</v>
       </c>
       <c r="G179" t="n">
-        <v>15.6055269241333</v>
+        <v>15.6055278778076</v>
       </c>
       <c r="H179" t="n">
         <v>1000</v>
@@ -5589,7 +5589,7 @@
         <v>17</v>
       </c>
       <c r="G180" t="n">
-        <v>15.6055269241333</v>
+        <v>15.6055278778076</v>
       </c>
       <c r="H180" t="n">
         <v>200</v>
@@ -5618,7 +5618,7 @@
         <v>17</v>
       </c>
       <c r="G181" t="n">
-        <v>15.6055269241333</v>
+        <v>15.6055278778076</v>
       </c>
       <c r="H181" t="n">
         <v>1100</v>
@@ -5647,7 +5647,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G182" t="n">
-        <v>15.9268178939819</v>
+        <v>15.9268169403076</v>
       </c>
       <c r="H182" t="n">
         <v>800</v>
@@ -5676,7 +5676,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G183" t="n">
-        <v>15.9635372161865</v>
+        <v>15.9635353088379</v>
       </c>
       <c r="H183" t="n">
         <v>200</v>
@@ -5705,7 +5705,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G184" t="n">
-        <v>15.7340421676636</v>
+        <v>15.7340440750122</v>
       </c>
       <c r="H184" t="n">
         <v>200</v>
@@ -5792,7 +5792,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G187" t="n">
-        <v>15.6238870620728</v>
+        <v>15.6238889694214</v>
       </c>
       <c r="H187" t="n">
         <v>3500</v>
@@ -5821,7 +5821,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G188" t="n">
-        <v>15.9268178939819</v>
+        <v>15.9268169403076</v>
       </c>
       <c r="H188" t="n">
         <v>500</v>
@@ -5879,7 +5879,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G190" t="n">
-        <v>15.7799434661865</v>
+        <v>15.7799415588379</v>
       </c>
       <c r="H190" t="n">
         <v>400</v>
@@ -5937,7 +5937,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>15.9268178939819</v>
+        <v>15.9268169403076</v>
       </c>
       <c r="H192" t="n">
         <v>300</v>
@@ -6053,7 +6053,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G196" t="n">
-        <v>16.8447895050049</v>
+        <v>16.8447914123535</v>
       </c>
       <c r="H196" t="n">
         <v>1400</v>
@@ -6082,7 +6082,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G197" t="n">
-        <v>16.8539695739746</v>
+        <v>16.8539714813232</v>
       </c>
       <c r="H197" t="n">
         <v>400</v>
@@ -6169,7 +6169,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G200" t="n">
-        <v>16.349084854126</v>
+        <v>16.3490829467773</v>
       </c>
       <c r="H200" t="n">
         <v>2900</v>
@@ -6256,7 +6256,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>18.0840530395508</v>
+        <v>18.0840549468994</v>
       </c>
       <c r="H203" t="n">
         <v>18000</v>
@@ -6343,7 +6343,7 @@
         <v>21.7250003814697</v>
       </c>
       <c r="G206" t="n">
-        <v>19.9429454803467</v>
+        <v>19.9429473876953</v>
       </c>
       <c r="H206" t="n">
         <v>4300</v>
@@ -6401,7 +6401,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>18.9561252593994</v>
+        <v>18.956127166748</v>
       </c>
       <c r="H208" t="n">
         <v>1800</v>
@@ -6430,7 +6430,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G209" t="n">
-        <v>19.0020275115967</v>
+        <v>19.0020236968994</v>
       </c>
       <c r="H209" t="n">
         <v>1100</v>
@@ -6459,7 +6459,7 @@
         <v>20.6800003051758</v>
       </c>
       <c r="G210" t="n">
-        <v>18.9836654663086</v>
+        <v>18.9836673736572</v>
       </c>
       <c r="H210" t="n">
         <v>900</v>
@@ -6517,7 +6517,7 @@
         <v>21.6550006866455</v>
       </c>
       <c r="G212" t="n">
-        <v>19.8786907196045</v>
+        <v>19.8786888122559</v>
       </c>
       <c r="H212" t="n">
         <v>5800</v>
@@ -6546,7 +6546,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>20.2871875762939</v>
+        <v>20.2871856689453</v>
       </c>
       <c r="H213" t="n">
         <v>8600</v>
@@ -6575,7 +6575,7 @@
         <v>22.7450008392334</v>
       </c>
       <c r="G214" t="n">
-        <v>20.8792781829834</v>
+        <v>20.879280090332</v>
       </c>
       <c r="H214" t="n">
         <v>8100</v>
@@ -6633,7 +6633,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H216" t="n">
         <v>400</v>
@@ -6662,7 +6662,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G217" t="n">
-        <v>20.3789825439453</v>
+        <v>20.3789844512939</v>
       </c>
       <c r="H217" t="n">
         <v>36200</v>
@@ -6691,7 +6691,7 @@
         <v>22.1650009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>20.3468551635742</v>
+        <v>20.3468532562256</v>
       </c>
       <c r="H218" t="n">
         <v>6000</v>
@@ -6778,7 +6778,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H221" t="n">
         <v>2900</v>
@@ -6894,7 +6894,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G225" t="n">
-        <v>21.1867980957031</v>
+        <v>21.1867961883545</v>
       </c>
       <c r="H225" t="n">
         <v>5500</v>
@@ -6923,7 +6923,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G226" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H226" t="n">
         <v>9100</v>
@@ -6952,7 +6952,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H227" t="n">
         <v>6900</v>
@@ -7155,7 +7155,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G234" t="n">
-        <v>21.2969551086426</v>
+        <v>21.2969570159912</v>
       </c>
       <c r="H234" t="n">
         <v>3800</v>
@@ -7213,7 +7213,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H236" t="n">
         <v>200</v>
@@ -7242,7 +7242,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G237" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H237" t="n">
         <v>115</v>
@@ -7329,7 +7329,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G240" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H240" t="n">
         <v>550</v>
@@ -7387,7 +7387,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H242" t="n">
         <v>1115</v>
@@ -7503,7 +7503,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G246" t="n">
-        <v>20.5625762939453</v>
+        <v>20.5625782012939</v>
       </c>
       <c r="H246" t="n">
         <v>3610</v>
@@ -7532,7 +7532,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>19.8281993865967</v>
+        <v>19.8282012939453</v>
       </c>
       <c r="H247" t="n">
         <v>11926</v>
@@ -7590,7 +7590,7 @@
         <v>22</v>
       </c>
       <c r="G249" t="n">
-        <v>20.1953907012939</v>
+        <v>20.1953887939453</v>
       </c>
       <c r="H249" t="n">
         <v>2862</v>
@@ -7619,7 +7619,7 @@
         <v>22</v>
       </c>
       <c r="G250" t="n">
-        <v>20.1953907012939</v>
+        <v>20.1953887939453</v>
       </c>
       <c r="H250" t="n">
         <v>305</v>
@@ -7677,7 +7677,7 @@
         <v>22</v>
       </c>
       <c r="G252" t="n">
-        <v>20.1953907012939</v>
+        <v>20.1953887939453</v>
       </c>
       <c r="H252" t="n">
         <v>362</v>
@@ -7764,7 +7764,7 @@
         <v>21</v>
       </c>
       <c r="G255" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H255" t="n">
         <v>2005</v>
@@ -7851,7 +7851,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G258" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H258" t="n">
         <v>120</v>
@@ -7880,7 +7880,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G259" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H259" t="n">
         <v>745</v>
@@ -7938,7 +7938,7 @@
         <v>21</v>
       </c>
       <c r="G261" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H261" t="n">
         <v>565</v>
@@ -7967,7 +7967,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G262" t="n">
-        <v>19.53786277771</v>
+        <v>19.5378646850586</v>
       </c>
       <c r="H262" t="n">
         <v>2949</v>
@@ -7996,7 +7996,7 @@
         <v>21</v>
       </c>
       <c r="G263" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H263" t="n">
         <v>1250</v>
@@ -8025,7 +8025,7 @@
         <v>21</v>
       </c>
       <c r="G264" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H264" t="n">
         <v>6111</v>
@@ -8054,7 +8054,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G265" t="n">
-        <v>19.53786277771</v>
+        <v>19.5378646850586</v>
       </c>
       <c r="H265" t="n">
         <v>200</v>
@@ -8083,7 +8083,7 @@
         <v>21</v>
       </c>
       <c r="G266" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H266" t="n">
         <v>120</v>
@@ -8228,7 +8228,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G271" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H271" t="n">
         <v>100</v>
@@ -8257,7 +8257,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H272" t="n">
         <v>1646</v>
@@ -9272,7 +9272,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G307" t="n">
-        <v>20.2893199920654</v>
+        <v>20.2893218994141</v>
       </c>
       <c r="H307" t="n">
         <v>250</v>
@@ -9330,7 +9330,7 @@
         <v>21</v>
       </c>
       <c r="G309" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H309" t="n">
         <v>1476</v>
@@ -9359,7 +9359,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H310" t="n">
         <v>495</v>
@@ -9388,7 +9388,7 @@
         <v>21</v>
       </c>
       <c r="G311" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H311" t="n">
         <v>675</v>
@@ -9417,7 +9417,7 @@
         <v>21</v>
       </c>
       <c r="G312" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H312" t="n">
         <v>265</v>
@@ -9446,7 +9446,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G313" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H313" t="n">
         <v>3230</v>
@@ -9475,7 +9475,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H314" t="n">
         <v>320</v>
@@ -9504,7 +9504,7 @@
         <v>21</v>
       </c>
       <c r="G315" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H315" t="n">
         <v>50</v>
@@ -9533,7 +9533,7 @@
         <v>21</v>
       </c>
       <c r="G316" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H316" t="n">
         <v>465</v>
@@ -9562,7 +9562,7 @@
         <v>21</v>
       </c>
       <c r="G317" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H317" t="n">
         <v>3</v>
@@ -9591,7 +9591,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>19.3500003814697</v>
+        <v>19.3499984741211</v>
       </c>
       <c r="H318" t="n">
         <v>30</v>
@@ -9620,7 +9620,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>19.3500003814697</v>
+        <v>19.3499984741211</v>
       </c>
       <c r="H319" t="n">
         <v>326</v>
@@ -9649,7 +9649,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G320" t="n">
-        <v>19.53786277771</v>
+        <v>19.5378646850586</v>
       </c>
       <c r="H320" t="n">
         <v>422</v>
@@ -9678,7 +9678,7 @@
         <v>21</v>
       </c>
       <c r="G321" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H321" t="n">
         <v>286</v>
@@ -9707,7 +9707,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H322" t="n">
         <v>360</v>
@@ -9765,7 +9765,7 @@
         <v>21</v>
       </c>
       <c r="G324" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H324" t="n">
         <v>940</v>
@@ -9968,7 +9968,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H331" t="n">
         <v>380</v>
@@ -9997,7 +9997,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>19.3500003814697</v>
+        <v>19.3499984741211</v>
       </c>
       <c r="H332" t="n">
         <v>163</v>
@@ -10026,7 +10026,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>19.1621360778809</v>
+        <v>19.1621341705322</v>
       </c>
       <c r="H333" t="n">
         <v>9842</v>
@@ -10055,7 +10055,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G334" t="n">
-        <v>18.9742736816406</v>
+        <v>18.974271774292</v>
       </c>
       <c r="H334" t="n">
         <v>1547</v>
@@ -10084,7 +10084,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>18.9742736816406</v>
+        <v>18.974271774292</v>
       </c>
       <c r="H335" t="n">
         <v>4339</v>
@@ -10113,7 +10113,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G336" t="n">
-        <v>18.9742736816406</v>
+        <v>18.974271774292</v>
       </c>
       <c r="H336" t="n">
         <v>4539</v>
@@ -10142,7 +10142,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>19.1621360778809</v>
+        <v>19.1621341705322</v>
       </c>
       <c r="H337" t="n">
         <v>1942</v>
@@ -10171,7 +10171,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>19.1621360778809</v>
+        <v>19.1621341705322</v>
       </c>
       <c r="H338" t="n">
         <v>284</v>
@@ -10200,7 +10200,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>19.3500003814697</v>
+        <v>19.3499984741211</v>
       </c>
       <c r="H339" t="n">
         <v>2218</v>
@@ -10229,7 +10229,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>19.53786277771</v>
+        <v>19.5378646850586</v>
       </c>
       <c r="H340" t="n">
         <v>5407</v>
@@ -10258,7 +10258,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G341" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H341" t="n">
         <v>3251</v>
@@ -10316,7 +10316,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G343" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H343" t="n">
         <v>100</v>
@@ -10345,7 +10345,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H344" t="n">
         <v>33</v>
@@ -10432,7 +10432,7 @@
         <v>21</v>
       </c>
       <c r="G347" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H347" t="n">
         <v>1330</v>
@@ -10461,7 +10461,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H348" t="n">
         <v>928</v>
@@ -10490,7 +10490,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H349" t="n">
         <v>1366</v>
@@ -10519,7 +10519,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G350" t="n">
-        <v>20.2893199920654</v>
+        <v>20.2893218994141</v>
       </c>
       <c r="H350" t="n">
         <v>18012</v>
@@ -10722,7 +10722,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>20.2893199920654</v>
+        <v>20.2893218994141</v>
       </c>
       <c r="H357" t="n">
         <v>291</v>
@@ -11070,7 +11070,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>23.1072826385498</v>
+        <v>23.1072807312012</v>
       </c>
       <c r="H369" t="n">
         <v>15210</v>
@@ -11534,7 +11534,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>24.6101932525635</v>
+        <v>24.6101951599121</v>
       </c>
       <c r="H385" t="n">
         <v>9687</v>
@@ -11882,7 +11882,7 @@
         <v>26</v>
       </c>
       <c r="G397" t="n">
-        <v>24.4223289489746</v>
+        <v>24.4223308563232</v>
       </c>
       <c r="H397" t="n">
         <v>777</v>
@@ -11911,7 +11911,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>24.6101932525635</v>
+        <v>24.6101951599121</v>
       </c>
       <c r="H398" t="n">
         <v>1281</v>
@@ -11969,7 +11969,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G400" t="n">
-        <v>25.737377166748</v>
+        <v>25.7373790740967</v>
       </c>
       <c r="H400" t="n">
         <v>3487</v>
@@ -12085,7 +12085,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>24.798059463501</v>
+        <v>24.7980575561523</v>
       </c>
       <c r="H404" t="n">
         <v>285</v>
@@ -12172,7 +12172,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>24.798059463501</v>
+        <v>24.7980575561523</v>
       </c>
       <c r="H407" t="n">
         <v>658</v>
@@ -12230,7 +12230,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>23.29514503479</v>
+        <v>23.2951431274414</v>
       </c>
       <c r="H409" t="n">
         <v>3492</v>
@@ -12317,7 +12317,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>24.2344646453857</v>
+        <v>24.2344665527344</v>
       </c>
       <c r="H412" t="n">
         <v>600</v>
@@ -12404,7 +12404,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G415" t="n">
-        <v>24.2344646453857</v>
+        <v>24.2344665527344</v>
       </c>
       <c r="H415" t="n">
         <v>140</v>
@@ -12433,7 +12433,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G416" t="n">
-        <v>24.2344646453857</v>
+        <v>24.2344665527344</v>
       </c>
       <c r="H416" t="n">
         <v>87</v>
@@ -12520,7 +12520,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G419" t="n">
-        <v>23.29514503479</v>
+        <v>23.2951431274414</v>
       </c>
       <c r="H419" t="n">
         <v>210</v>
@@ -12578,7 +12578,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>23.29514503479</v>
+        <v>23.2951431274414</v>
       </c>
       <c r="H421" t="n">
         <v>2392</v>
@@ -12723,7 +12723,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G426" t="n">
-        <v>24.6101932525635</v>
+        <v>24.6101951599121</v>
       </c>
       <c r="H426" t="n">
         <v>3659</v>
@@ -12781,7 +12781,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>24.798059463501</v>
+        <v>24.7980575561523</v>
       </c>
       <c r="H428" t="n">
         <v>4557</v>
@@ -12984,7 +12984,7 @@
         <v>26</v>
       </c>
       <c r="G435" t="n">
-        <v>24.4223289489746</v>
+        <v>24.4223308563232</v>
       </c>
       <c r="H435" t="n">
         <v>16881</v>
@@ -13071,7 +13071,7 @@
         <v>26</v>
       </c>
       <c r="G438" t="n">
-        <v>24.4223289489746</v>
+        <v>24.4223308563232</v>
       </c>
       <c r="H438" t="n">
         <v>193</v>
@@ -13129,7 +13129,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>24.798059463501</v>
+        <v>24.7980575561523</v>
       </c>
       <c r="H440" t="n">
         <v>111</v>
@@ -13564,7 +13564,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>24.6101932525635</v>
+        <v>24.6101951599121</v>
       </c>
       <c r="H455" t="n">
         <v>1466</v>
@@ -13651,7 +13651,7 @@
         <v>26</v>
       </c>
       <c r="G458" t="n">
-        <v>24.4223289489746</v>
+        <v>24.4223308563232</v>
       </c>
       <c r="H458" t="n">
         <v>809</v>
@@ -13738,7 +13738,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G461" t="n">
-        <v>23.1072826385498</v>
+        <v>23.1072807312012</v>
       </c>
       <c r="H461" t="n">
         <v>2523</v>
@@ -13767,7 +13767,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>19.53786277771</v>
+        <v>19.5378646850586</v>
       </c>
       <c r="H462" t="n">
         <v>4429</v>
@@ -13883,7 +13883,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G466" t="n">
-        <v>18.410680770874</v>
+        <v>18.4106788635254</v>
       </c>
       <c r="H466" t="n">
         <v>944</v>
@@ -14028,7 +14028,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G471" t="n">
-        <v>16.1563129425049</v>
+        <v>16.1563110351562</v>
       </c>
       <c r="H471" t="n">
         <v>2772</v>
@@ -14202,7 +14202,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>14.2776689529419</v>
+        <v>14.2776699066162</v>
       </c>
       <c r="H477" t="n">
         <v>1705</v>
@@ -14231,7 +14231,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>14.2776689529419</v>
+        <v>14.2776699066162</v>
       </c>
       <c r="H478" t="n">
         <v>1810</v>
@@ -14260,7 +14260,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G479" t="n">
-        <v>13.9958734512329</v>
+        <v>13.9958724975586</v>
       </c>
       <c r="H479" t="n">
         <v>200</v>
@@ -14347,7 +14347,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>15.6866512298584</v>
+        <v>15.6866502761841</v>
       </c>
       <c r="H482" t="n">
         <v>4167</v>
@@ -14376,7 +14376,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>15.6866512298584</v>
+        <v>15.6866502761841</v>
       </c>
       <c r="H483" t="n">
         <v>3514</v>
@@ -14492,7 +14492,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G487" t="n">
-        <v>16.1563129425049</v>
+        <v>16.1563110351562</v>
       </c>
       <c r="H487" t="n">
         <v>12961</v>
@@ -14579,7 +14579,7 @@
         <v>17.25</v>
       </c>
       <c r="G490" t="n">
-        <v>16.203275680542</v>
+        <v>16.2032775878906</v>
       </c>
       <c r="H490" t="n">
         <v>6624</v>
@@ -14695,7 +14695,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>15.6866512298584</v>
+        <v>15.6866502761841</v>
       </c>
       <c r="H494" t="n">
         <v>5139</v>
@@ -14753,7 +14753,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G496" t="n">
-        <v>16.1563129425049</v>
+        <v>16.1563110351562</v>
       </c>
       <c r="H496" t="n">
         <v>3600</v>
@@ -14811,7 +14811,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>15.6866512298584</v>
+        <v>15.6866502761841</v>
       </c>
       <c r="H498" t="n">
         <v>7270</v>
@@ -14927,7 +14927,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G502" t="n">
-        <v>16.8138332366943</v>
+        <v>16.813835144043</v>
       </c>
       <c r="H502" t="n">
         <v>3773</v>
@@ -15130,7 +15130,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G509" t="n">
-        <v>17.2365283966064</v>
+        <v>17.2365303039551</v>
       </c>
       <c r="H509" t="n">
         <v>1503</v>
@@ -15159,7 +15159,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>17.1895637512207</v>
+        <v>17.1895618438721</v>
       </c>
       <c r="H510" t="n">
         <v>255</v>
@@ -15217,7 +15217,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>16.7668704986572</v>
+        <v>16.7668685913086</v>
       </c>
       <c r="H512" t="n">
         <v>1779</v>
@@ -15246,7 +15246,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>16.7668704986572</v>
+        <v>16.7668685913086</v>
       </c>
       <c r="H513" t="n">
         <v>40</v>
@@ -15333,7 +15333,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>17.1895637512207</v>
+        <v>17.1895618438721</v>
       </c>
       <c r="H516" t="n">
         <v>1360</v>
@@ -15391,7 +15391,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G518" t="n">
-        <v>17.2365283966064</v>
+        <v>17.2365303039551</v>
       </c>
       <c r="H518" t="n">
         <v>1647</v>
@@ -15594,7 +15594,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>18.1288833618164</v>
+        <v>18.1288814544678</v>
       </c>
       <c r="H525" t="n">
         <v>5337</v>
@@ -15855,7 +15855,7 @@
         <v>19</v>
       </c>
       <c r="G534" t="n">
-        <v>17.8470859527588</v>
+        <v>17.8470878601074</v>
       </c>
       <c r="H534" t="n">
         <v>4414</v>
@@ -15884,7 +15884,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>18.410680770874</v>
+        <v>18.4106788635254</v>
       </c>
       <c r="H535" t="n">
         <v>1991</v>
@@ -15942,7 +15942,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>17.1895637512207</v>
+        <v>17.1895618438721</v>
       </c>
       <c r="H537" t="n">
         <v>7342</v>
@@ -15971,7 +15971,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>17.4243907928467</v>
+        <v>17.4243927001953</v>
       </c>
       <c r="H538" t="n">
         <v>589</v>
@@ -16029,7 +16029,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G540" t="n">
-        <v>17.2365283966064</v>
+        <v>17.2365303039551</v>
       </c>
       <c r="H540" t="n">
         <v>1317</v>
@@ -16087,7 +16087,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>16.8138332366943</v>
+        <v>16.813835144043</v>
       </c>
       <c r="H542" t="n">
         <v>756</v>
@@ -16116,7 +16116,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>17.2365283966064</v>
+        <v>17.2365303039551</v>
       </c>
       <c r="H543" t="n">
         <v>668</v>
@@ -16145,7 +16145,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G544" t="n">
-        <v>17.4243907928467</v>
+        <v>17.4243927001953</v>
       </c>
       <c r="H544" t="n">
         <v>800</v>
@@ -16174,7 +16174,7 @@
         <v>18.5</v>
       </c>
       <c r="G545" t="n">
-        <v>17.3774280548096</v>
+        <v>17.3774261474609</v>
       </c>
       <c r="H545" t="n">
         <v>23094</v>
@@ -16203,7 +16203,7 @@
         <v>19</v>
       </c>
       <c r="G546" t="n">
-        <v>17.8470859527588</v>
+        <v>17.8470878601074</v>
       </c>
       <c r="H546" t="n">
         <v>250</v>
@@ -16261,7 +16261,7 @@
         <v>18.5</v>
       </c>
       <c r="G548" t="n">
-        <v>17.3774280548096</v>
+        <v>17.3774261474609</v>
       </c>
       <c r="H548" t="n">
         <v>1240</v>
@@ -16812,7 +16812,7 @@
         <v>15.75</v>
       </c>
       <c r="G567" t="n">
-        <v>14.7942953109741</v>
+        <v>14.7942962646484</v>
       </c>
       <c r="H567" t="n">
         <v>14601</v>
@@ -17189,7 +17189,7 @@
         <v>15.75</v>
       </c>
       <c r="G580" t="n">
-        <v>14.7942953109741</v>
+        <v>14.7942962646484</v>
       </c>
       <c r="H580" t="n">
         <v>8207</v>
@@ -17247,7 +17247,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>14.4655332565308</v>
+        <v>14.4655342102051</v>
       </c>
       <c r="H582" t="n">
         <v>1389</v>
@@ -17450,7 +17450,7 @@
         <v>15.75</v>
       </c>
       <c r="G589" t="n">
-        <v>14.7942953109741</v>
+        <v>14.7942962646484</v>
       </c>
       <c r="H589" t="n">
         <v>4722</v>
@@ -17508,7 +17508,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G591" t="n">
-        <v>14.4655332565308</v>
+        <v>14.4655342102051</v>
       </c>
       <c r="H591" t="n">
         <v>6347</v>
@@ -17566,7 +17566,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G593" t="n">
-        <v>14.1837377548218</v>
+        <v>14.1837387084961</v>
       </c>
       <c r="H593" t="n">
         <v>6222</v>
@@ -17595,7 +17595,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>13.9958734512329</v>
+        <v>13.9958724975586</v>
       </c>
       <c r="H594" t="n">
         <v>11633</v>
@@ -17624,7 +17624,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G595" t="n">
-        <v>14.0428400039673</v>
+        <v>14.042839050293</v>
       </c>
       <c r="H595" t="n">
         <v>5431</v>
@@ -17653,7 +17653,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G596" t="n">
-        <v>13.9019422531128</v>
+        <v>13.9019412994385</v>
       </c>
       <c r="H596" t="n">
         <v>7311</v>
@@ -17711,7 +17711,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>13.9019422531128</v>
+        <v>13.9019412994385</v>
       </c>
       <c r="H598" t="n">
         <v>6014</v>
@@ -17769,7 +17769,7 @@
         <v>14.5</v>
       </c>
       <c r="G600" t="n">
-        <v>13.6201457977295</v>
+        <v>13.6201448440552</v>
       </c>
       <c r="H600" t="n">
         <v>17122</v>
@@ -62638,6 +62638,35 @@
         <v>10722</v>
       </c>
       <c r="I2147" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2148" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2148" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D2148" t="n">
+        <v>25.7999992370605</v>
+      </c>
+      <c r="E2148" t="n">
+        <v>25.1000003814697</v>
+      </c>
+      <c r="F2148" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G2148" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="H2148" t="n">
+        <v>13009</v>
+      </c>
+      <c r="I2148" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -62670,6 +62670,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2149">
+      <c r="A2149" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2149" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2149" t="n">
+        <v>25.7999992370605</v>
+      </c>
+      <c r="D2149" t="n">
+        <v>26.2000007629395</v>
+      </c>
+      <c r="E2149" t="n">
+        <v>25.3999996185303</v>
+      </c>
+      <c r="F2149" t="n">
+        <v>26</v>
+      </c>
+      <c r="G2149" t="n">
+        <v>26</v>
+      </c>
+      <c r="H2149" t="n">
+        <v>29315</v>
+      </c>
+      <c r="I2149" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -62699,6 +62699,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2150">
+      <c r="A2150" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2150" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2150" t="n">
+        <v>25.8999996185303</v>
+      </c>
+      <c r="D2150" t="n">
+        <v>26.2999992370605</v>
+      </c>
+      <c r="E2150" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F2150" t="n">
+        <v>26.2999992370605</v>
+      </c>
+      <c r="G2150" t="n">
+        <v>26.2999992370605</v>
+      </c>
+      <c r="H2150" t="n">
+        <v>17883</v>
+      </c>
+      <c r="I2150" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -427,7 +427,7 @@
         <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>16.5235004425049</v>
+        <v>16.5234985351562</v>
       </c>
       <c r="H2" t="n">
         <v>36200</v>
@@ -456,7 +456,7 @@
         <v>17.9139995574951</v>
       </c>
       <c r="G3" t="n">
-        <v>16.4445552825928</v>
+        <v>16.4445533752441</v>
       </c>
       <c r="H3" t="n">
         <v>4000</v>
@@ -485,7 +485,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G4" t="n">
-        <v>16.5051403045654</v>
+        <v>16.5051383972168</v>
       </c>
       <c r="H4" t="n">
         <v>9100</v>
@@ -514,7 +514,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G5" t="n">
-        <v>16.4225215911865</v>
+        <v>16.4225234985352</v>
       </c>
       <c r="H5" t="n">
         <v>1500</v>
@@ -572,7 +572,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G7" t="n">
-        <v>16.2848281860352</v>
+        <v>16.2848262786865</v>
       </c>
       <c r="H7" t="n">
         <v>4600</v>
@@ -601,7 +601,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G8" t="n">
-        <v>16.4225215911865</v>
+        <v>16.4225234985352</v>
       </c>
       <c r="H8" t="n">
         <v>11700</v>
@@ -630,7 +630,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G9" t="n">
-        <v>16.2481098175049</v>
+        <v>16.2481079101562</v>
       </c>
       <c r="H9" t="n">
         <v>1700</v>
@@ -717,7 +717,7 @@
         <v>17.5</v>
       </c>
       <c r="G12" t="n">
-        <v>16.0645122528076</v>
+        <v>16.0645141601562</v>
       </c>
       <c r="H12" t="n">
         <v>2300</v>
@@ -775,7 +775,7 @@
         <v>17.75</v>
       </c>
       <c r="G14" t="n">
-        <v>16.2940063476562</v>
+        <v>16.2940082550049</v>
       </c>
       <c r="H14" t="n">
         <v>700</v>
@@ -804,7 +804,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>16.2481098175049</v>
+        <v>16.2481079101562</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
@@ -833,7 +833,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G16" t="n">
-        <v>16.2481098175049</v>
+        <v>16.2481079101562</v>
       </c>
       <c r="H16" t="n">
         <v>300</v>
@@ -1094,7 +1094,7 @@
         <v>17.8840007781982</v>
       </c>
       <c r="G25" t="n">
-        <v>16.4170150756836</v>
+        <v>16.4170169830322</v>
       </c>
       <c r="H25" t="n">
         <v>400</v>
@@ -1181,7 +1181,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>16.3858032226562</v>
+        <v>16.3858051300049</v>
       </c>
       <c r="H28" t="n">
         <v>2600</v>
@@ -1239,7 +1239,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G30" t="n">
-        <v>16.4500617980957</v>
+        <v>16.4500637054443</v>
       </c>
       <c r="H30" t="n">
         <v>100</v>
@@ -1297,7 +1297,7 @@
         <v>18</v>
       </c>
       <c r="G32" t="n">
-        <v>16.5235004425049</v>
+        <v>16.5234985351562</v>
       </c>
       <c r="H32" t="n">
         <v>17300</v>
@@ -1326,7 +1326,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G33" t="n">
-        <v>16.5051403045654</v>
+        <v>16.5051383972168</v>
       </c>
       <c r="H33" t="n">
         <v>10200</v>
@@ -1355,7 +1355,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G34" t="n">
-        <v>16.2481098175049</v>
+        <v>16.2481079101562</v>
       </c>
       <c r="H34" t="n">
         <v>1900</v>
@@ -1500,7 +1500,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G39" t="n">
-        <v>16.5051403045654</v>
+        <v>16.5051383972168</v>
       </c>
       <c r="H39" t="n">
         <v>800</v>
@@ -1587,7 +1587,7 @@
         <v>18</v>
       </c>
       <c r="G42" t="n">
-        <v>16.5235004425049</v>
+        <v>16.5234985351562</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
@@ -1645,7 +1645,7 @@
         <v>18.5</v>
       </c>
       <c r="G44" t="n">
-        <v>16.9824848175049</v>
+        <v>16.9824867248535</v>
       </c>
       <c r="H44" t="n">
         <v>17900</v>
@@ -1674,7 +1674,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>17.0283851623535</v>
+        <v>17.0283813476562</v>
       </c>
       <c r="H45" t="n">
         <v>10700</v>
@@ -1703,7 +1703,7 @@
         <v>19</v>
       </c>
       <c r="G46" t="n">
-        <v>17.4414730072021</v>
+        <v>17.4414710998535</v>
       </c>
       <c r="H46" t="n">
         <v>11600</v>
@@ -1790,7 +1790,7 @@
         <v>19</v>
       </c>
       <c r="G49" t="n">
-        <v>17.4414730072021</v>
+        <v>17.4414710998535</v>
       </c>
       <c r="H49" t="n">
         <v>400</v>
@@ -1993,7 +1993,7 @@
         <v>19</v>
       </c>
       <c r="G56" t="n">
-        <v>17.4414730072021</v>
+        <v>17.4414710998535</v>
       </c>
       <c r="H56" t="n">
         <v>1900</v>
@@ -2022,7 +2022,7 @@
         <v>19</v>
       </c>
       <c r="G57" t="n">
-        <v>17.4414730072021</v>
+        <v>17.4414710998535</v>
       </c>
       <c r="H57" t="n">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>19</v>
       </c>
       <c r="G58" t="n">
-        <v>17.4414730072021</v>
+        <v>17.4414710998535</v>
       </c>
       <c r="H58" t="n">
         <v>2100</v>
@@ -2167,7 +2167,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>17.1201801300049</v>
+        <v>17.1201820373535</v>
       </c>
       <c r="H62" t="n">
         <v>3200</v>
@@ -2196,7 +2196,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G63" t="n">
-        <v>17.1201801300049</v>
+        <v>17.1201820373535</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>17.0742816925049</v>
+        <v>17.0742835998535</v>
       </c>
       <c r="H67" t="n">
         <v>2300</v>
@@ -2341,7 +2341,7 @@
         <v>18.4340000152588</v>
       </c>
       <c r="G68" t="n">
-        <v>16.9218978881836</v>
+        <v>16.9218997955322</v>
       </c>
       <c r="H68" t="n">
         <v>400</v>
@@ -2370,7 +2370,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G69" t="n">
-        <v>16.7988910675049</v>
+        <v>16.7988929748535</v>
       </c>
       <c r="H69" t="n">
         <v>1000</v>
@@ -2399,7 +2399,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>16.7988910675049</v>
+        <v>16.7988929748535</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G71" t="n">
-        <v>17.0283851623535</v>
+        <v>17.0283813476562</v>
       </c>
       <c r="H71" t="n">
         <v>100</v>
@@ -2457,7 +2457,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G72" t="n">
-        <v>17.0283851623535</v>
+        <v>17.0283813476562</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G73" t="n">
-        <v>17.0283851623535</v>
+        <v>17.0283813476562</v>
       </c>
       <c r="H73" t="n">
         <v>100</v>
@@ -2515,7 +2515,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G74" t="n">
-        <v>17.0283851623535</v>
+        <v>17.0283813476562</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G75" t="n">
-        <v>17.0283851623535</v>
+        <v>17.0283813476562</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>17.0742816925049</v>
+        <v>17.0742835998535</v>
       </c>
       <c r="H76" t="n">
         <v>100</v>
@@ -2602,7 +2602,7 @@
         <v>18.4979991912842</v>
       </c>
       <c r="G77" t="n">
-        <v>16.9806499481201</v>
+        <v>16.9806480407715</v>
       </c>
       <c r="H77" t="n">
         <v>100</v>
@@ -2747,7 +2747,7 @@
         <v>18</v>
       </c>
       <c r="G82" t="n">
-        <v>16.5235004425049</v>
+        <v>16.5234985351562</v>
       </c>
       <c r="H82" t="n">
         <v>3200</v>
@@ -2776,7 +2776,7 @@
         <v>18</v>
       </c>
       <c r="G83" t="n">
-        <v>16.5235004425049</v>
+        <v>16.5234985351562</v>
       </c>
       <c r="H83" t="n">
         <v>5000</v>
@@ -2805,7 +2805,7 @@
         <v>18</v>
       </c>
       <c r="G84" t="n">
-        <v>16.5235004425049</v>
+        <v>16.5234985351562</v>
       </c>
       <c r="H84" t="n">
         <v>200</v>
@@ -3008,7 +3008,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>16.2481098175049</v>
+        <v>16.2481079101562</v>
       </c>
       <c r="H91" t="n">
         <v>2800</v>
@@ -3037,7 +3037,7 @@
         <v>17.8339996337891</v>
       </c>
       <c r="G92" t="n">
-        <v>16.3711166381836</v>
+        <v>16.371114730835</v>
       </c>
       <c r="H92" t="n">
         <v>100</v>
@@ -3124,7 +3124,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>16.2022075653076</v>
+        <v>16.2022094726562</v>
       </c>
       <c r="H95" t="n">
         <v>500</v>
@@ -3153,7 +3153,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G96" t="n">
-        <v>16.2848281860352</v>
+        <v>16.2848262786865</v>
       </c>
       <c r="H96" t="n">
         <v>100</v>
@@ -3182,7 +3182,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G97" t="n">
-        <v>15.7615842819214</v>
+        <v>15.7615823745728</v>
       </c>
       <c r="H97" t="n">
         <v>8500</v>
@@ -3269,7 +3269,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G100" t="n">
-        <v>15.8717412948608</v>
+        <v>15.8717403411865</v>
       </c>
       <c r="H100" t="n">
         <v>7000</v>
@@ -3298,7 +3298,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G101" t="n">
-        <v>15.7707643508911</v>
+        <v>15.7707624435425</v>
       </c>
       <c r="H101" t="n">
         <v>2200</v>
@@ -3414,7 +3414,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G105" t="n">
-        <v>15.5229091644287</v>
+        <v>15.5229110717773</v>
       </c>
       <c r="H105" t="n">
         <v>400</v>
@@ -3443,7 +3443,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>15.2383394241333</v>
+        <v>15.238338470459</v>
       </c>
       <c r="H106" t="n">
         <v>400</v>
@@ -3472,7 +3472,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G107" t="n">
-        <v>14.9721260070801</v>
+        <v>14.9721269607544</v>
       </c>
       <c r="H107" t="n">
         <v>200</v>
@@ -3530,7 +3530,7 @@
         <v>16.2140007019043</v>
       </c>
       <c r="G109" t="n">
-        <v>14.8840017318726</v>
+        <v>14.8840026855469</v>
       </c>
       <c r="H109" t="n">
         <v>1300</v>
@@ -3588,7 +3588,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G111" t="n">
-        <v>15.100643157959</v>
+        <v>15.1006441116333</v>
       </c>
       <c r="H111" t="n">
         <v>5100</v>
@@ -3617,7 +3617,7 @@
         <v>16.1119995117188</v>
       </c>
       <c r="G112" t="n">
-        <v>14.7903671264648</v>
+        <v>14.7903680801392</v>
       </c>
       <c r="H112" t="n">
         <v>5400</v>
@@ -3646,7 +3646,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>14.7793521881104</v>
+        <v>14.7793531417847</v>
       </c>
       <c r="H113" t="n">
         <v>100</v>
@@ -3675,7 +3675,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G114" t="n">
-        <v>14.8252515792847</v>
+        <v>14.8252506256104</v>
       </c>
       <c r="H114" t="n">
         <v>6200</v>
@@ -3762,7 +3762,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G117" t="n">
-        <v>14.9996662139893</v>
+        <v>14.9996652603149</v>
       </c>
       <c r="H117" t="n">
         <v>100</v>
@@ -3849,7 +3849,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>14.595757484436</v>
+        <v>14.5957584381104</v>
       </c>
       <c r="H120" t="n">
         <v>1500</v>
@@ -3878,7 +3878,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G121" t="n">
-        <v>14.595757484436</v>
+        <v>14.5957584381104</v>
       </c>
       <c r="H121" t="n">
         <v>2300</v>
@@ -3907,7 +3907,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G122" t="n">
-        <v>14.595757484436</v>
+        <v>14.5957584381104</v>
       </c>
       <c r="H122" t="n">
         <v>100</v>
@@ -4023,7 +4023,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>14.8252515792847</v>
+        <v>14.8252506256104</v>
       </c>
       <c r="H126" t="n">
         <v>100</v>
@@ -4052,7 +4052,7 @@
         <v>16.0979995727539</v>
       </c>
       <c r="G127" t="n">
-        <v>14.7775163650513</v>
+        <v>14.777515411377</v>
       </c>
       <c r="H127" t="n">
         <v>100</v>
@@ -4313,7 +4313,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>14.366265296936</v>
+        <v>14.3662643432617</v>
       </c>
       <c r="H136" t="n">
         <v>1600</v>
@@ -4371,7 +4371,7 @@
         <v>14.9280004501343</v>
       </c>
       <c r="G138" t="n">
-        <v>13.7034902572632</v>
+        <v>13.7034893035889</v>
       </c>
       <c r="H138" t="n">
         <v>4400</v>
@@ -4400,7 +4400,7 @@
         <v>15.3680000305176</v>
       </c>
       <c r="G139" t="n">
-        <v>14.1073961257935</v>
+        <v>14.1073970794678</v>
       </c>
       <c r="H139" t="n">
         <v>3000</v>
@@ -4429,7 +4429,7 @@
         <v>15.5</v>
       </c>
       <c r="G140" t="n">
-        <v>14.2285690307617</v>
+        <v>14.228569984436</v>
       </c>
       <c r="H140" t="n">
         <v>4200</v>
@@ -4458,7 +4458,7 @@
         <v>15.5</v>
       </c>
       <c r="G141" t="n">
-        <v>14.2285690307617</v>
+        <v>14.228569984436</v>
       </c>
       <c r="H141" t="n">
         <v>100</v>
@@ -4487,7 +4487,7 @@
         <v>15.5</v>
       </c>
       <c r="G142" t="n">
-        <v>14.2285690307617</v>
+        <v>14.228569984436</v>
       </c>
       <c r="H142" t="n">
         <v>200</v>
@@ -4516,7 +4516,7 @@
         <v>15.5</v>
       </c>
       <c r="G143" t="n">
-        <v>14.2285690307617</v>
+        <v>14.228569984436</v>
       </c>
       <c r="H143" t="n">
         <v>300</v>
@@ -4574,7 +4574,7 @@
         <v>15.5979995727539</v>
       </c>
       <c r="G145" t="n">
-        <v>14.3185300827026</v>
+        <v>14.318531036377</v>
       </c>
       <c r="H145" t="n">
         <v>4400</v>
@@ -4632,7 +4632,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>14.595757484436</v>
+        <v>14.5957584381104</v>
       </c>
       <c r="H147" t="n">
         <v>3100</v>
@@ -4661,7 +4661,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G148" t="n">
-        <v>14.3295459747314</v>
+        <v>14.3295450210571</v>
       </c>
       <c r="H148" t="n">
         <v>700</v>
@@ -4835,7 +4835,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>14.8252515792847</v>
+        <v>14.8252506256104</v>
       </c>
       <c r="H154" t="n">
         <v>100</v>
@@ -5009,7 +5009,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G160" t="n">
-        <v>14.8527898788452</v>
+        <v>14.8527908325195</v>
       </c>
       <c r="H160" t="n">
         <v>800</v>
@@ -5038,7 +5038,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G161" t="n">
-        <v>15.0731039047241</v>
+        <v>15.0731029510498</v>
       </c>
       <c r="H161" t="n">
         <v>1800</v>
@@ -5067,7 +5067,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G162" t="n">
-        <v>15.0731039047241</v>
+        <v>15.0731029510498</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>16.4179992675781</v>
       </c>
       <c r="G163" t="n">
-        <v>15.0712661743164</v>
+        <v>15.0712671279907</v>
       </c>
       <c r="H163" t="n">
         <v>300</v>
@@ -5125,7 +5125,7 @@
         <v>16.4179992675781</v>
       </c>
       <c r="G164" t="n">
-        <v>15.0712661743164</v>
+        <v>15.0712671279907</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>16.0979995727539</v>
       </c>
       <c r="G166" t="n">
-        <v>14.7775163650513</v>
+        <v>14.777515411377</v>
       </c>
       <c r="H166" t="n">
         <v>3400</v>
@@ -5328,7 +5328,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G171" t="n">
-        <v>14.7793521881104</v>
+        <v>14.7793531417847</v>
       </c>
       <c r="H171" t="n">
         <v>1500</v>
@@ -5357,7 +5357,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>14.7793521881104</v>
+        <v>14.7793531417847</v>
       </c>
       <c r="H172" t="n">
         <v>100</v>
@@ -5502,7 +5502,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G177" t="n">
-        <v>15.1924381256104</v>
+        <v>15.1924390792847</v>
       </c>
       <c r="H177" t="n">
         <v>100</v>
@@ -5560,7 +5560,7 @@
         <v>17</v>
       </c>
       <c r="G179" t="n">
-        <v>15.6055278778076</v>
+        <v>15.6055269241333</v>
       </c>
       <c r="H179" t="n">
         <v>1000</v>
@@ -5589,7 +5589,7 @@
         <v>17</v>
       </c>
       <c r="G180" t="n">
-        <v>15.6055278778076</v>
+        <v>15.6055269241333</v>
       </c>
       <c r="H180" t="n">
         <v>200</v>
@@ -5618,7 +5618,7 @@
         <v>17</v>
       </c>
       <c r="G181" t="n">
-        <v>15.6055278778076</v>
+        <v>15.6055269241333</v>
       </c>
       <c r="H181" t="n">
         <v>1100</v>
@@ -5647,7 +5647,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G182" t="n">
-        <v>15.9268169403076</v>
+        <v>15.9268178939819</v>
       </c>
       <c r="H182" t="n">
         <v>800</v>
@@ -5676,7 +5676,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G183" t="n">
-        <v>15.9635353088379</v>
+        <v>15.9635372161865</v>
       </c>
       <c r="H183" t="n">
         <v>200</v>
@@ -5705,7 +5705,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G184" t="n">
-        <v>15.7340440750122</v>
+        <v>15.7340431213379</v>
       </c>
       <c r="H184" t="n">
         <v>200</v>
@@ -5792,7 +5792,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G187" t="n">
-        <v>15.6238889694214</v>
+        <v>15.6238870620728</v>
       </c>
       <c r="H187" t="n">
         <v>3500</v>
@@ -5821,7 +5821,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G188" t="n">
-        <v>15.9268169403076</v>
+        <v>15.9268178939819</v>
       </c>
       <c r="H188" t="n">
         <v>500</v>
@@ -5879,7 +5879,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G190" t="n">
-        <v>15.7799415588379</v>
+        <v>15.7799425125122</v>
       </c>
       <c r="H190" t="n">
         <v>400</v>
@@ -5937,7 +5937,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>15.9268169403076</v>
+        <v>15.9268178939819</v>
       </c>
       <c r="H192" t="n">
         <v>300</v>
@@ -6053,7 +6053,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G196" t="n">
-        <v>16.8447914123535</v>
+        <v>16.8447895050049</v>
       </c>
       <c r="H196" t="n">
         <v>1400</v>
@@ -6082,7 +6082,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G197" t="n">
-        <v>16.8539714813232</v>
+        <v>16.8539695739746</v>
       </c>
       <c r="H197" t="n">
         <v>400</v>
@@ -6169,7 +6169,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G200" t="n">
-        <v>16.3490829467773</v>
+        <v>16.349084854126</v>
       </c>
       <c r="H200" t="n">
         <v>2900</v>
@@ -6198,7 +6198,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G201" t="n">
-        <v>16.5693969726562</v>
+        <v>16.5693988800049</v>
       </c>
       <c r="H201" t="n">
         <v>2000</v>
@@ -6256,7 +6256,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>18.0840549468994</v>
+        <v>18.0840530395508</v>
       </c>
       <c r="H203" t="n">
         <v>18000</v>
@@ -6372,7 +6372,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>19.3692150115967</v>
+        <v>19.369213104248</v>
       </c>
       <c r="H207" t="n">
         <v>5100</v>
@@ -6401,7 +6401,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>18.956127166748</v>
+        <v>18.9561252593994</v>
       </c>
       <c r="H208" t="n">
         <v>1800</v>
@@ -6430,7 +6430,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G209" t="n">
-        <v>19.0020236968994</v>
+        <v>19.002025604248</v>
       </c>
       <c r="H209" t="n">
         <v>1100</v>
@@ -6459,7 +6459,7 @@
         <v>20.6800003051758</v>
       </c>
       <c r="G210" t="n">
-        <v>18.9836673736572</v>
+        <v>18.9836654663086</v>
       </c>
       <c r="H210" t="n">
         <v>900</v>
@@ -6633,7 +6633,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H216" t="n">
         <v>400</v>
@@ -6691,7 +6691,7 @@
         <v>22.1650009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>20.3468532562256</v>
+        <v>20.3468551635742</v>
       </c>
       <c r="H218" t="n">
         <v>6000</v>
@@ -6720,7 +6720,7 @@
         <v>22.5249996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>20.6773223876953</v>
+        <v>20.6773242950439</v>
       </c>
       <c r="H219" t="n">
         <v>2000</v>
@@ -6778,7 +6778,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H221" t="n">
         <v>2900</v>
@@ -6894,7 +6894,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G225" t="n">
-        <v>21.1867961883545</v>
+        <v>21.1867980957031</v>
       </c>
       <c r="H225" t="n">
         <v>5500</v>
@@ -6923,7 +6923,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G226" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H226" t="n">
         <v>9100</v>
@@ -6952,7 +6952,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H227" t="n">
         <v>6900</v>
@@ -7155,7 +7155,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G234" t="n">
-        <v>21.2969570159912</v>
+        <v>21.2969551086426</v>
       </c>
       <c r="H234" t="n">
         <v>3800</v>
@@ -7213,7 +7213,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H236" t="n">
         <v>200</v>
@@ -7242,7 +7242,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G237" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H237" t="n">
         <v>115</v>
@@ -7329,7 +7329,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G240" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H240" t="n">
         <v>550</v>
@@ -7387,7 +7387,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>20.9297637939453</v>
+        <v>20.9297657012939</v>
       </c>
       <c r="H242" t="n">
         <v>1115</v>
@@ -7532,7 +7532,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>19.8282012939453</v>
+        <v>19.8281993865967</v>
       </c>
       <c r="H247" t="n">
         <v>11926</v>
@@ -7764,7 +7764,7 @@
         <v>21</v>
       </c>
       <c r="G255" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H255" t="n">
         <v>2005</v>
@@ -7851,7 +7851,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G258" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H258" t="n">
         <v>120</v>
@@ -7880,7 +7880,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G259" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H259" t="n">
         <v>745</v>
@@ -7938,7 +7938,7 @@
         <v>21</v>
       </c>
       <c r="G261" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H261" t="n">
         <v>565</v>
@@ -7967,7 +7967,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G262" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H262" t="n">
         <v>2949</v>
@@ -7996,7 +7996,7 @@
         <v>21</v>
       </c>
       <c r="G263" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H263" t="n">
         <v>1250</v>
@@ -8025,7 +8025,7 @@
         <v>21</v>
       </c>
       <c r="G264" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H264" t="n">
         <v>6111</v>
@@ -8054,7 +8054,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G265" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H265" t="n">
         <v>200</v>
@@ -8083,7 +8083,7 @@
         <v>21</v>
       </c>
       <c r="G266" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H266" t="n">
         <v>120</v>
@@ -8228,7 +8228,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G271" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H271" t="n">
         <v>100</v>
@@ -8257,7 +8257,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H272" t="n">
         <v>1646</v>
@@ -9272,7 +9272,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G307" t="n">
-        <v>20.2893218994141</v>
+        <v>20.2893199920654</v>
       </c>
       <c r="H307" t="n">
         <v>250</v>
@@ -9330,7 +9330,7 @@
         <v>21</v>
       </c>
       <c r="G309" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H309" t="n">
         <v>1476</v>
@@ -9359,7 +9359,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H310" t="n">
         <v>495</v>
@@ -9388,7 +9388,7 @@
         <v>21</v>
       </c>
       <c r="G311" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H311" t="n">
         <v>675</v>
@@ -9417,7 +9417,7 @@
         <v>21</v>
       </c>
       <c r="G312" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H312" t="n">
         <v>265</v>
@@ -9446,7 +9446,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G313" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H313" t="n">
         <v>3230</v>
@@ -9475,7 +9475,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H314" t="n">
         <v>320</v>
@@ -9504,7 +9504,7 @@
         <v>21</v>
       </c>
       <c r="G315" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H315" t="n">
         <v>50</v>
@@ -9533,7 +9533,7 @@
         <v>21</v>
       </c>
       <c r="G316" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H316" t="n">
         <v>465</v>
@@ -9562,7 +9562,7 @@
         <v>21</v>
       </c>
       <c r="G317" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H317" t="n">
         <v>3</v>
@@ -9591,7 +9591,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>19.3499984741211</v>
+        <v>19.3500003814697</v>
       </c>
       <c r="H318" t="n">
         <v>30</v>
@@ -9620,7 +9620,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>19.3499984741211</v>
+        <v>19.3500003814697</v>
       </c>
       <c r="H319" t="n">
         <v>326</v>
@@ -9649,7 +9649,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G320" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H320" t="n">
         <v>422</v>
@@ -9678,7 +9678,7 @@
         <v>21</v>
       </c>
       <c r="G321" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H321" t="n">
         <v>286</v>
@@ -9707,7 +9707,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H322" t="n">
         <v>360</v>
@@ -9765,7 +9765,7 @@
         <v>21</v>
       </c>
       <c r="G324" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H324" t="n">
         <v>940</v>
@@ -9968,7 +9968,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H331" t="n">
         <v>380</v>
@@ -9997,7 +9997,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>19.3499984741211</v>
+        <v>19.3500003814697</v>
       </c>
       <c r="H332" t="n">
         <v>163</v>
@@ -10026,7 +10026,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>19.1621341705322</v>
+        <v>19.1621360778809</v>
       </c>
       <c r="H333" t="n">
         <v>9842</v>
@@ -10055,7 +10055,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G334" t="n">
-        <v>18.974271774292</v>
+        <v>18.9742736816406</v>
       </c>
       <c r="H334" t="n">
         <v>1547</v>
@@ -10084,7 +10084,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>18.974271774292</v>
+        <v>18.9742736816406</v>
       </c>
       <c r="H335" t="n">
         <v>4339</v>
@@ -10113,7 +10113,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G336" t="n">
-        <v>18.974271774292</v>
+        <v>18.9742736816406</v>
       </c>
       <c r="H336" t="n">
         <v>4539</v>
@@ -10142,7 +10142,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>19.1621341705322</v>
+        <v>19.1621360778809</v>
       </c>
       <c r="H337" t="n">
         <v>1942</v>
@@ -10171,7 +10171,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>19.1621341705322</v>
+        <v>19.1621360778809</v>
       </c>
       <c r="H338" t="n">
         <v>284</v>
@@ -10200,7 +10200,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>19.3499984741211</v>
+        <v>19.3500003814697</v>
       </c>
       <c r="H339" t="n">
         <v>2218</v>
@@ -10229,7 +10229,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H340" t="n">
         <v>5407</v>
@@ -10258,7 +10258,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G341" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H341" t="n">
         <v>3251</v>
@@ -10316,7 +10316,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G343" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H343" t="n">
         <v>100</v>
@@ -10345,7 +10345,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H344" t="n">
         <v>33</v>
@@ -10432,7 +10432,7 @@
         <v>21</v>
       </c>
       <c r="G347" t="n">
-        <v>19.7257289886475</v>
+        <v>19.7257270812988</v>
       </c>
       <c r="H347" t="n">
         <v>1330</v>
@@ -10461,7 +10461,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H348" t="n">
         <v>928</v>
@@ -10490,7 +10490,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>19.9135932922363</v>
+        <v>19.9135913848877</v>
       </c>
       <c r="H349" t="n">
         <v>1366</v>
@@ -10519,7 +10519,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G350" t="n">
-        <v>20.2893218994141</v>
+        <v>20.2893199920654</v>
       </c>
       <c r="H350" t="n">
         <v>18012</v>
@@ -10722,7 +10722,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>20.2893218994141</v>
+        <v>20.2893199920654</v>
       </c>
       <c r="H357" t="n">
         <v>291</v>
@@ -11070,7 +11070,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>23.1072807312012</v>
+        <v>23.1072826385498</v>
       </c>
       <c r="H369" t="n">
         <v>15210</v>
@@ -11534,7 +11534,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>24.6101951599121</v>
+        <v>24.6101932525635</v>
       </c>
       <c r="H385" t="n">
         <v>9687</v>
@@ -11882,7 +11882,7 @@
         <v>26</v>
       </c>
       <c r="G397" t="n">
-        <v>24.4223308563232</v>
+        <v>24.4223289489746</v>
       </c>
       <c r="H397" t="n">
         <v>777</v>
@@ -11911,7 +11911,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>24.6101951599121</v>
+        <v>24.6101932525635</v>
       </c>
       <c r="H398" t="n">
         <v>1281</v>
@@ -11969,7 +11969,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G400" t="n">
-        <v>25.7373790740967</v>
+        <v>25.737377166748</v>
       </c>
       <c r="H400" t="n">
         <v>3487</v>
@@ -12085,7 +12085,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>24.7980575561523</v>
+        <v>24.798059463501</v>
       </c>
       <c r="H404" t="n">
         <v>285</v>
@@ -12172,7 +12172,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>24.7980575561523</v>
+        <v>24.798059463501</v>
       </c>
       <c r="H407" t="n">
         <v>658</v>
@@ -12230,7 +12230,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>23.2951431274414</v>
+        <v>23.29514503479</v>
       </c>
       <c r="H409" t="n">
         <v>3492</v>
@@ -12317,7 +12317,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>24.2344665527344</v>
+        <v>24.2344646453857</v>
       </c>
       <c r="H412" t="n">
         <v>600</v>
@@ -12404,7 +12404,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G415" t="n">
-        <v>24.2344665527344</v>
+        <v>24.2344646453857</v>
       </c>
       <c r="H415" t="n">
         <v>140</v>
@@ -12433,7 +12433,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G416" t="n">
-        <v>24.2344665527344</v>
+        <v>24.2344646453857</v>
       </c>
       <c r="H416" t="n">
         <v>87</v>
@@ -12520,7 +12520,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G419" t="n">
-        <v>23.2951431274414</v>
+        <v>23.29514503479</v>
       </c>
       <c r="H419" t="n">
         <v>210</v>
@@ -12578,7 +12578,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>23.2951431274414</v>
+        <v>23.29514503479</v>
       </c>
       <c r="H421" t="n">
         <v>2392</v>
@@ -12723,7 +12723,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G426" t="n">
-        <v>24.6101951599121</v>
+        <v>24.6101932525635</v>
       </c>
       <c r="H426" t="n">
         <v>3659</v>
@@ -12781,7 +12781,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>24.7980575561523</v>
+        <v>24.798059463501</v>
       </c>
       <c r="H428" t="n">
         <v>4557</v>
@@ -12984,7 +12984,7 @@
         <v>26</v>
       </c>
       <c r="G435" t="n">
-        <v>24.4223308563232</v>
+        <v>24.4223289489746</v>
       </c>
       <c r="H435" t="n">
         <v>16881</v>
@@ -13071,7 +13071,7 @@
         <v>26</v>
       </c>
       <c r="G438" t="n">
-        <v>24.4223308563232</v>
+        <v>24.4223289489746</v>
       </c>
       <c r="H438" t="n">
         <v>193</v>
@@ -13129,7 +13129,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>24.7980575561523</v>
+        <v>24.798059463501</v>
       </c>
       <c r="H440" t="n">
         <v>111</v>
@@ -13564,7 +13564,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>24.6101951599121</v>
+        <v>24.6101932525635</v>
       </c>
       <c r="H455" t="n">
         <v>1466</v>
@@ -13651,7 +13651,7 @@
         <v>26</v>
       </c>
       <c r="G458" t="n">
-        <v>24.4223308563232</v>
+        <v>24.4223289489746</v>
       </c>
       <c r="H458" t="n">
         <v>809</v>
@@ -13738,7 +13738,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G461" t="n">
-        <v>23.1072807312012</v>
+        <v>23.1072826385498</v>
       </c>
       <c r="H461" t="n">
         <v>2523</v>
@@ -13767,7 +13767,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>19.5378646850586</v>
+        <v>19.53786277771</v>
       </c>
       <c r="H462" t="n">
         <v>4429</v>
@@ -13883,7 +13883,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G466" t="n">
-        <v>18.4106788635254</v>
+        <v>18.410680770874</v>
       </c>
       <c r="H466" t="n">
         <v>944</v>
@@ -14028,7 +14028,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G471" t="n">
-        <v>16.1563110351562</v>
+        <v>16.1563129425049</v>
       </c>
       <c r="H471" t="n">
         <v>2772</v>
@@ -14202,7 +14202,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>14.2776699066162</v>
+        <v>14.2776689529419</v>
       </c>
       <c r="H477" t="n">
         <v>1705</v>
@@ -14231,7 +14231,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>14.2776699066162</v>
+        <v>14.2776689529419</v>
       </c>
       <c r="H478" t="n">
         <v>1810</v>
@@ -14260,7 +14260,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G479" t="n">
-        <v>13.9958724975586</v>
+        <v>13.9958734512329</v>
       </c>
       <c r="H479" t="n">
         <v>200</v>
@@ -14347,7 +14347,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>15.6866502761841</v>
+        <v>15.6866512298584</v>
       </c>
       <c r="H482" t="n">
         <v>4167</v>
@@ -14376,7 +14376,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>15.6866502761841</v>
+        <v>15.6866512298584</v>
       </c>
       <c r="H483" t="n">
         <v>3514</v>
@@ -14492,7 +14492,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G487" t="n">
-        <v>16.1563110351562</v>
+        <v>16.1563129425049</v>
       </c>
       <c r="H487" t="n">
         <v>12961</v>
@@ -14579,7 +14579,7 @@
         <v>17.25</v>
       </c>
       <c r="G490" t="n">
-        <v>16.2032775878906</v>
+        <v>16.203275680542</v>
       </c>
       <c r="H490" t="n">
         <v>6624</v>
@@ -14695,7 +14695,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>15.6866502761841</v>
+        <v>15.6866512298584</v>
       </c>
       <c r="H494" t="n">
         <v>5139</v>
@@ -14753,7 +14753,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G496" t="n">
-        <v>16.1563110351562</v>
+        <v>16.1563129425049</v>
       </c>
       <c r="H496" t="n">
         <v>3600</v>
@@ -14811,7 +14811,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>15.6866502761841</v>
+        <v>15.6866512298584</v>
       </c>
       <c r="H498" t="n">
         <v>7270</v>
@@ -14927,7 +14927,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G502" t="n">
-        <v>16.813835144043</v>
+        <v>16.8138332366943</v>
       </c>
       <c r="H502" t="n">
         <v>3773</v>
@@ -15130,7 +15130,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G509" t="n">
-        <v>17.2365303039551</v>
+        <v>17.2365283966064</v>
       </c>
       <c r="H509" t="n">
         <v>1503</v>
@@ -15159,7 +15159,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>17.1895618438721</v>
+        <v>17.1895637512207</v>
       </c>
       <c r="H510" t="n">
         <v>255</v>
@@ -15217,7 +15217,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>16.7668685913086</v>
+        <v>16.7668704986572</v>
       </c>
       <c r="H512" t="n">
         <v>1779</v>
@@ -15246,7 +15246,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>16.7668685913086</v>
+        <v>16.7668704986572</v>
       </c>
       <c r="H513" t="n">
         <v>40</v>
@@ -15333,7 +15333,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>17.1895618438721</v>
+        <v>17.1895637512207</v>
       </c>
       <c r="H516" t="n">
         <v>1360</v>
@@ -15391,7 +15391,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G518" t="n">
-        <v>17.2365303039551</v>
+        <v>17.2365283966064</v>
       </c>
       <c r="H518" t="n">
         <v>1647</v>
@@ -15594,7 +15594,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>18.1288814544678</v>
+        <v>18.1288833618164</v>
       </c>
       <c r="H525" t="n">
         <v>5337</v>
@@ -15855,7 +15855,7 @@
         <v>19</v>
       </c>
       <c r="G534" t="n">
-        <v>17.8470878601074</v>
+        <v>17.8470859527588</v>
       </c>
       <c r="H534" t="n">
         <v>4414</v>
@@ -15884,7 +15884,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>18.4106788635254</v>
+        <v>18.410680770874</v>
       </c>
       <c r="H535" t="n">
         <v>1991</v>
@@ -15942,7 +15942,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>17.1895618438721</v>
+        <v>17.1895637512207</v>
       </c>
       <c r="H537" t="n">
         <v>7342</v>
@@ -15971,7 +15971,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>17.4243927001953</v>
+        <v>17.4243907928467</v>
       </c>
       <c r="H538" t="n">
         <v>589</v>
@@ -16029,7 +16029,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G540" t="n">
-        <v>17.2365303039551</v>
+        <v>17.2365283966064</v>
       </c>
       <c r="H540" t="n">
         <v>1317</v>
@@ -16087,7 +16087,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>16.813835144043</v>
+        <v>16.8138332366943</v>
       </c>
       <c r="H542" t="n">
         <v>756</v>
@@ -16116,7 +16116,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>17.2365303039551</v>
+        <v>17.2365283966064</v>
       </c>
       <c r="H543" t="n">
         <v>668</v>
@@ -16145,7 +16145,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G544" t="n">
-        <v>17.4243927001953</v>
+        <v>17.4243907928467</v>
       </c>
       <c r="H544" t="n">
         <v>800</v>
@@ -16174,7 +16174,7 @@
         <v>18.5</v>
       </c>
       <c r="G545" t="n">
-        <v>17.3774261474609</v>
+        <v>17.3774280548096</v>
       </c>
       <c r="H545" t="n">
         <v>23094</v>
@@ -16203,7 +16203,7 @@
         <v>19</v>
       </c>
       <c r="G546" t="n">
-        <v>17.8470878601074</v>
+        <v>17.8470859527588</v>
       </c>
       <c r="H546" t="n">
         <v>250</v>
@@ -16261,7 +16261,7 @@
         <v>18.5</v>
       </c>
       <c r="G548" t="n">
-        <v>17.3774261474609</v>
+        <v>17.3774280548096</v>
       </c>
       <c r="H548" t="n">
         <v>1240</v>
@@ -16812,7 +16812,7 @@
         <v>15.75</v>
       </c>
       <c r="G567" t="n">
-        <v>14.7942962646484</v>
+        <v>14.7942953109741</v>
       </c>
       <c r="H567" t="n">
         <v>14601</v>
@@ -17189,7 +17189,7 @@
         <v>15.75</v>
       </c>
       <c r="G580" t="n">
-        <v>14.7942962646484</v>
+        <v>14.7942953109741</v>
       </c>
       <c r="H580" t="n">
         <v>8207</v>
@@ -17247,7 +17247,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>14.4655342102051</v>
+        <v>14.4655332565308</v>
       </c>
       <c r="H582" t="n">
         <v>1389</v>
@@ -17450,7 +17450,7 @@
         <v>15.75</v>
       </c>
       <c r="G589" t="n">
-        <v>14.7942962646484</v>
+        <v>14.7942953109741</v>
       </c>
       <c r="H589" t="n">
         <v>4722</v>
@@ -17508,7 +17508,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G591" t="n">
-        <v>14.4655342102051</v>
+        <v>14.4655332565308</v>
       </c>
       <c r="H591" t="n">
         <v>6347</v>
@@ -17566,7 +17566,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G593" t="n">
-        <v>14.1837387084961</v>
+        <v>14.1837377548218</v>
       </c>
       <c r="H593" t="n">
         <v>6222</v>
@@ -17595,7 +17595,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>13.9958724975586</v>
+        <v>13.9958734512329</v>
       </c>
       <c r="H594" t="n">
         <v>11633</v>
@@ -17624,7 +17624,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G595" t="n">
-        <v>14.042839050293</v>
+        <v>14.0428400039673</v>
       </c>
       <c r="H595" t="n">
         <v>5431</v>
@@ -17653,7 +17653,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G596" t="n">
-        <v>13.9019412994385</v>
+        <v>13.9019422531128</v>
       </c>
       <c r="H596" t="n">
         <v>7311</v>
@@ -17711,7 +17711,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>13.9019412994385</v>
+        <v>13.9019422531128</v>
       </c>
       <c r="H598" t="n">
         <v>6014</v>
@@ -17769,7 +17769,7 @@
         <v>14.5</v>
       </c>
       <c r="G600" t="n">
-        <v>13.6201448440552</v>
+        <v>13.6201457977295</v>
       </c>
       <c r="H600" t="n">
         <v>17122</v>
@@ -62722,9 +62722,38 @@
         <v>26.2999992370605</v>
       </c>
       <c r="H2150" t="n">
-        <v>17883</v>
+        <v>17907</v>
       </c>
       <c r="I2150" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2151" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2151" t="n">
+        <v>26.2000007629395</v>
+      </c>
+      <c r="D2151" t="n">
+        <v>26.7000007629395</v>
+      </c>
+      <c r="E2151" t="n">
+        <v>25.8999996185303</v>
+      </c>
+      <c r="F2151" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G2151" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="H2151" t="n">
+        <v>14020</v>
+      </c>
+      <c r="I2151" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -62757,6 +62757,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2152">
+      <c r="A2152" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2152" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2152" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="D2152" t="n">
+        <v>25.2000007629395</v>
+      </c>
+      <c r="E2152" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="F2152" t="n">
+        <v>25</v>
+      </c>
+      <c r="G2152" t="n">
+        <v>25</v>
+      </c>
+      <c r="H2152" t="n">
+        <v>731357</v>
+      </c>
+      <c r="I2152" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOM.MI.xlsx
+++ b/data/SOM.MI.xlsx
@@ -427,7 +427,7 @@
         <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>16.5234985351562</v>
+        <v>16.5235004425049</v>
       </c>
       <c r="H2" t="n">
         <v>36200</v>
@@ -456,7 +456,7 @@
         <v>17.9139995574951</v>
       </c>
       <c r="G3" t="n">
-        <v>16.4445533752441</v>
+        <v>16.4445552825928</v>
       </c>
       <c r="H3" t="n">
         <v>4000</v>
@@ -485,7 +485,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G4" t="n">
-        <v>16.5051383972168</v>
+        <v>16.5051403045654</v>
       </c>
       <c r="H4" t="n">
         <v>9100</v>
@@ -514,7 +514,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G5" t="n">
-        <v>16.4225234985352</v>
+        <v>16.4225215911865</v>
       </c>
       <c r="H5" t="n">
         <v>1500</v>
@@ -572,7 +572,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G7" t="n">
-        <v>16.2848262786865</v>
+        <v>16.2848281860352</v>
       </c>
       <c r="H7" t="n">
         <v>4600</v>
@@ -601,7 +601,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G8" t="n">
-        <v>16.4225234985352</v>
+        <v>16.4225215911865</v>
       </c>
       <c r="H8" t="n">
         <v>11700</v>
@@ -630,7 +630,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G9" t="n">
-        <v>16.2481079101562</v>
+        <v>16.2481098175049</v>
       </c>
       <c r="H9" t="n">
         <v>1700</v>
@@ -717,7 +717,7 @@
         <v>17.5</v>
       </c>
       <c r="G12" t="n">
-        <v>16.0645141601562</v>
+        <v>16.0645122528076</v>
       </c>
       <c r="H12" t="n">
         <v>2300</v>
@@ -775,7 +775,7 @@
         <v>17.75</v>
       </c>
       <c r="G14" t="n">
-        <v>16.2940082550049</v>
+        <v>16.2940063476562</v>
       </c>
       <c r="H14" t="n">
         <v>700</v>
@@ -804,7 +804,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G15" t="n">
-        <v>16.2481079101562</v>
+        <v>16.2481098175049</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
@@ -833,7 +833,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G16" t="n">
-        <v>16.2481079101562</v>
+        <v>16.2481098175049</v>
       </c>
       <c r="H16" t="n">
         <v>300</v>
@@ -1094,7 +1094,7 @@
         <v>17.8840007781982</v>
       </c>
       <c r="G25" t="n">
-        <v>16.4170169830322</v>
+        <v>16.4170150756836</v>
       </c>
       <c r="H25" t="n">
         <v>400</v>
@@ -1181,7 +1181,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>16.3858051300049</v>
+        <v>16.3858032226562</v>
       </c>
       <c r="H28" t="n">
         <v>2600</v>
@@ -1239,7 +1239,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G30" t="n">
-        <v>16.4500637054443</v>
+        <v>16.4500617980957</v>
       </c>
       <c r="H30" t="n">
         <v>100</v>
@@ -1297,7 +1297,7 @@
         <v>18</v>
       </c>
       <c r="G32" t="n">
-        <v>16.5234985351562</v>
+        <v>16.5235004425049</v>
       </c>
       <c r="H32" t="n">
         <v>17300</v>
@@ -1326,7 +1326,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G33" t="n">
-        <v>16.5051383972168</v>
+        <v>16.5051403045654</v>
       </c>
       <c r="H33" t="n">
         <v>10200</v>
@@ -1355,7 +1355,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G34" t="n">
-        <v>16.2481079101562</v>
+        <v>16.2481098175049</v>
       </c>
       <c r="H34" t="n">
         <v>1900</v>
@@ -1500,7 +1500,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G39" t="n">
-        <v>16.5051383972168</v>
+        <v>16.5051403045654</v>
       </c>
       <c r="H39" t="n">
         <v>800</v>
@@ -1587,7 +1587,7 @@
         <v>18</v>
       </c>
       <c r="G42" t="n">
-        <v>16.5234985351562</v>
+        <v>16.5235004425049</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
@@ -1645,7 +1645,7 @@
         <v>18.5</v>
       </c>
       <c r="G44" t="n">
-        <v>16.9824867248535</v>
+        <v>16.9824848175049</v>
       </c>
       <c r="H44" t="n">
         <v>17900</v>
@@ -1674,7 +1674,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>17.0283813476562</v>
+        <v>17.0283851623535</v>
       </c>
       <c r="H45" t="n">
         <v>10700</v>
@@ -1703,7 +1703,7 @@
         <v>19</v>
       </c>
       <c r="G46" t="n">
-        <v>17.4414710998535</v>
+        <v>17.4414730072021</v>
       </c>
       <c r="H46" t="n">
         <v>11600</v>
@@ -1790,7 +1790,7 @@
         <v>19</v>
       </c>
       <c r="G49" t="n">
-        <v>17.4414710998535</v>
+        <v>17.4414730072021</v>
       </c>
       <c r="H49" t="n">
         <v>400</v>
@@ -1993,7 +1993,7 @@
         <v>19</v>
       </c>
       <c r="G56" t="n">
-        <v>17.4414710998535</v>
+        <v>17.4414730072021</v>
       </c>
       <c r="H56" t="n">
         <v>1900</v>
@@ -2022,7 +2022,7 @@
         <v>19</v>
       </c>
       <c r="G57" t="n">
-        <v>17.4414710998535</v>
+        <v>17.4414730072021</v>
       </c>
       <c r="H57" t="n">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>19</v>
       </c>
       <c r="G58" t="n">
-        <v>17.4414710998535</v>
+        <v>17.4414730072021</v>
       </c>
       <c r="H58" t="n">
         <v>2100</v>
@@ -2167,7 +2167,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G62" t="n">
-        <v>17.1201820373535</v>
+        <v>17.1201801300049</v>
       </c>
       <c r="H62" t="n">
         <v>3200</v>
@@ -2196,7 +2196,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G63" t="n">
-        <v>17.1201820373535</v>
+        <v>17.1201801300049</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G67" t="n">
-        <v>17.0742835998535</v>
+        <v>17.0742816925049</v>
       </c>
       <c r="H67" t="n">
         <v>2300</v>
@@ -2341,7 +2341,7 @@
         <v>18.4340000152588</v>
       </c>
       <c r="G68" t="n">
-        <v>16.9218997955322</v>
+        <v>16.9218978881836</v>
       </c>
       <c r="H68" t="n">
         <v>400</v>
@@ -2370,7 +2370,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G69" t="n">
-        <v>16.7988929748535</v>
+        <v>16.7988910675049</v>
       </c>
       <c r="H69" t="n">
         <v>1000</v>
@@ -2399,7 +2399,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G70" t="n">
-        <v>16.7988929748535</v>
+        <v>16.7988910675049</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G71" t="n">
-        <v>17.0283813476562</v>
+        <v>17.0283851623535</v>
       </c>
       <c r="H71" t="n">
         <v>100</v>
@@ -2457,7 +2457,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G72" t="n">
-        <v>17.0283813476562</v>
+        <v>17.0283851623535</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G73" t="n">
-        <v>17.0283813476562</v>
+        <v>17.0283851623535</v>
       </c>
       <c r="H73" t="n">
         <v>100</v>
@@ -2515,7 +2515,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G74" t="n">
-        <v>17.0283813476562</v>
+        <v>17.0283851623535</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G75" t="n">
-        <v>17.0283813476562</v>
+        <v>17.0283851623535</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>17.0742835998535</v>
+        <v>17.0742816925049</v>
       </c>
       <c r="H76" t="n">
         <v>100</v>
@@ -2602,7 +2602,7 @@
         <v>18.4979991912842</v>
       </c>
       <c r="G77" t="n">
-        <v>16.9806480407715</v>
+        <v>16.9806499481201</v>
       </c>
       <c r="H77" t="n">
         <v>100</v>
@@ -2747,7 +2747,7 @@
         <v>18</v>
       </c>
       <c r="G82" t="n">
-        <v>16.5234985351562</v>
+        <v>16.5235004425049</v>
       </c>
       <c r="H82" t="n">
         <v>3200</v>
@@ -2776,7 +2776,7 @@
         <v>18</v>
       </c>
       <c r="G83" t="n">
-        <v>16.5234985351562</v>
+        <v>16.5235004425049</v>
       </c>
       <c r="H83" t="n">
         <v>5000</v>
@@ -2805,7 +2805,7 @@
         <v>18</v>
       </c>
       <c r="G84" t="n">
-        <v>16.5234985351562</v>
+        <v>16.5235004425049</v>
       </c>
       <c r="H84" t="n">
         <v>200</v>
@@ -3008,7 +3008,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>16.2481079101562</v>
+        <v>16.2481098175049</v>
       </c>
       <c r="H91" t="n">
         <v>2800</v>
@@ -3037,7 +3037,7 @@
         <v>17.8339996337891</v>
       </c>
       <c r="G92" t="n">
-        <v>16.371114730835</v>
+        <v>16.3711166381836</v>
       </c>
       <c r="H92" t="n">
         <v>100</v>
@@ -3124,7 +3124,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G95" t="n">
-        <v>16.2022094726562</v>
+        <v>16.2022075653076</v>
       </c>
       <c r="H95" t="n">
         <v>500</v>
@@ -3153,7 +3153,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G96" t="n">
-        <v>16.2848262786865</v>
+        <v>16.2848281860352</v>
       </c>
       <c r="H96" t="n">
         <v>100</v>
@@ -3182,7 +3182,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G97" t="n">
-        <v>15.7615823745728</v>
+        <v>15.7615842819214</v>
       </c>
       <c r="H97" t="n">
         <v>8500</v>
@@ -3269,7 +3269,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G100" t="n">
-        <v>15.8717403411865</v>
+        <v>15.8717412948608</v>
       </c>
       <c r="H100" t="n">
         <v>7000</v>
@@ -3298,7 +3298,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G101" t="n">
-        <v>15.7707624435425</v>
+        <v>15.7707643508911</v>
       </c>
       <c r="H101" t="n">
         <v>2200</v>
@@ -3414,7 +3414,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G105" t="n">
-        <v>15.5229110717773</v>
+        <v>15.5229091644287</v>
       </c>
       <c r="H105" t="n">
         <v>400</v>
@@ -3443,7 +3443,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G106" t="n">
-        <v>15.238338470459</v>
+        <v>15.2383394241333</v>
       </c>
       <c r="H106" t="n">
         <v>400</v>
@@ -3472,7 +3472,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G107" t="n">
-        <v>14.9721269607544</v>
+        <v>14.9721260070801</v>
       </c>
       <c r="H107" t="n">
         <v>200</v>
@@ -3530,7 +3530,7 @@
         <v>16.2140007019043</v>
       </c>
       <c r="G109" t="n">
-        <v>14.8840026855469</v>
+        <v>14.8840017318726</v>
       </c>
       <c r="H109" t="n">
         <v>1300</v>
@@ -3588,7 +3588,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G111" t="n">
-        <v>15.1006441116333</v>
+        <v>15.100643157959</v>
       </c>
       <c r="H111" t="n">
         <v>5100</v>
@@ -3617,7 +3617,7 @@
         <v>16.1119995117188</v>
       </c>
       <c r="G112" t="n">
-        <v>14.7903680801392</v>
+        <v>14.7903671264648</v>
       </c>
       <c r="H112" t="n">
         <v>5400</v>
@@ -3646,7 +3646,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>14.7793531417847</v>
+        <v>14.7793521881104</v>
       </c>
       <c r="H113" t="n">
         <v>100</v>
@@ -3675,7 +3675,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G114" t="n">
-        <v>14.8252506256104</v>
+        <v>14.8252515792847</v>
       </c>
       <c r="H114" t="n">
         <v>6200</v>
@@ -3762,7 +3762,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G117" t="n">
-        <v>14.9996652603149</v>
+        <v>14.9996662139893</v>
       </c>
       <c r="H117" t="n">
         <v>100</v>
@@ -3849,7 +3849,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>14.5957584381104</v>
+        <v>14.595757484436</v>
       </c>
       <c r="H120" t="n">
         <v>1500</v>
@@ -3878,7 +3878,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G121" t="n">
-        <v>14.5957584381104</v>
+        <v>14.595757484436</v>
       </c>
       <c r="H121" t="n">
         <v>2300</v>
@@ -3907,7 +3907,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G122" t="n">
-        <v>14.5957584381104</v>
+        <v>14.595757484436</v>
       </c>
       <c r="H122" t="n">
         <v>100</v>
@@ -4023,7 +4023,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>14.8252506256104</v>
+        <v>14.8252515792847</v>
       </c>
       <c r="H126" t="n">
         <v>100</v>
@@ -4052,7 +4052,7 @@
         <v>16.0979995727539</v>
       </c>
       <c r="G127" t="n">
-        <v>14.777515411377</v>
+        <v>14.7775163650513</v>
       </c>
       <c r="H127" t="n">
         <v>100</v>
@@ -4313,7 +4313,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>14.3662643432617</v>
+        <v>14.366265296936</v>
       </c>
       <c r="H136" t="n">
         <v>1600</v>
@@ -4371,7 +4371,7 @@
         <v>14.9280004501343</v>
       </c>
       <c r="G138" t="n">
-        <v>13.7034893035889</v>
+        <v>13.7034902572632</v>
       </c>
       <c r="H138" t="n">
         <v>4400</v>
@@ -4400,7 +4400,7 @@
         <v>15.3680000305176</v>
       </c>
       <c r="G139" t="n">
-        <v>14.1073970794678</v>
+        <v>14.1073961257935</v>
       </c>
       <c r="H139" t="n">
         <v>3000</v>
@@ -4429,7 +4429,7 @@
         <v>15.5</v>
       </c>
       <c r="G140" t="n">
-        <v>14.228569984436</v>
+        <v>14.2285690307617</v>
       </c>
       <c r="H140" t="n">
         <v>4200</v>
@@ -4458,7 +4458,7 @@
         <v>15.5</v>
       </c>
       <c r="G141" t="n">
-        <v>14.228569984436</v>
+        <v>14.2285690307617</v>
       </c>
       <c r="H141" t="n">
         <v>100</v>
@@ -4487,7 +4487,7 @@
         <v>15.5</v>
       </c>
       <c r="G142" t="n">
-        <v>14.228569984436</v>
+        <v>14.2285690307617</v>
       </c>
       <c r="H142" t="n">
         <v>200</v>
@@ -4516,7 +4516,7 @@
         <v>15.5</v>
       </c>
       <c r="G143" t="n">
-        <v>14.228569984436</v>
+        <v>14.2285690307617</v>
       </c>
       <c r="H143" t="n">
         <v>300</v>
@@ -4574,7 +4574,7 @@
         <v>15.5979995727539</v>
       </c>
       <c r="G145" t="n">
-        <v>14.318531036377</v>
+        <v>14.3185300827026</v>
       </c>
       <c r="H145" t="n">
         <v>4400</v>
@@ -4632,7 +4632,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>14.5957584381104</v>
+        <v>14.595757484436</v>
       </c>
       <c r="H147" t="n">
         <v>3100</v>
@@ -4661,7 +4661,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G148" t="n">
-        <v>14.3295450210571</v>
+        <v>14.3295459747314</v>
       </c>
       <c r="H148" t="n">
         <v>700</v>
@@ -4835,7 +4835,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>14.8252506256104</v>
+        <v>14.8252515792847</v>
       </c>
       <c r="H154" t="n">
         <v>100</v>
@@ -5009,7 +5009,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G160" t="n">
-        <v>14.8527908325195</v>
+        <v>14.8527898788452</v>
       </c>
       <c r="H160" t="n">
         <v>800</v>
@@ -5038,7 +5038,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G161" t="n">
-        <v>15.0731029510498</v>
+        <v>15.0731039047241</v>
       </c>
       <c r="H161" t="n">
         <v>1800</v>
@@ -5067,7 +5067,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G162" t="n">
-        <v>15.0731029510498</v>
+        <v>15.0731039047241</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>16.4179992675781</v>
       </c>
       <c r="G163" t="n">
-        <v>15.0712671279907</v>
+        <v>15.0712661743164</v>
       </c>
       <c r="H163" t="n">
         <v>300</v>
@@ -5125,7 +5125,7 @@
         <v>16.4179992675781</v>
       </c>
       <c r="G164" t="n">
-        <v>15.0712671279907</v>
+        <v>15.0712661743164</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>16.0979995727539</v>
       </c>
       <c r="G166" t="n">
-        <v>14.777515411377</v>
+        <v>14.7775163650513</v>
       </c>
       <c r="H166" t="n">
         <v>3400</v>
@@ -5328,7 +5328,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G171" t="n">
-        <v>14.7793531417847</v>
+        <v>14.7793521881104</v>
       </c>
       <c r="H171" t="n">
         <v>1500</v>
@@ -5357,7 +5357,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>14.7793531417847</v>
+        <v>14.7793521881104</v>
       </c>
       <c r="H172" t="n">
         <v>100</v>
@@ -5502,7 +5502,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G177" t="n">
-        <v>15.1924390792847</v>
+        <v>15.1924381256104</v>
       </c>
       <c r="H177" t="n">
         <v>100</v>
@@ -5560,7 +5560,7 @@
         <v>17</v>
       </c>
       <c r="G179" t="n">
-        <v>15.6055269241333</v>
+        <v>15.6055278778076</v>
       </c>
       <c r="H179" t="n">
         <v>1000</v>
@@ -5589,7 +5589,7 @@
         <v>17</v>
       </c>
       <c r="G180" t="n">
-        <v>15.6055269241333</v>
+        <v>15.6055278778076</v>
       </c>
       <c r="H180" t="n">
         <v>200</v>
@@ -5618,7 +5618,7 @@
         <v>17</v>
       </c>
       <c r="G181" t="n">
-        <v>15.6055269241333</v>
+        <v>15.6055278778076</v>
       </c>
       <c r="H181" t="n">
         <v>1100</v>
@@ -5647,7 +5647,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G182" t="n">
-        <v>15.9268178939819</v>
+        <v>15.9268169403076</v>
       </c>
       <c r="H182" t="n">
         <v>800</v>
@@ -5676,7 +5676,7 @@
         <v>17.3899993896484</v>
       </c>
       <c r="G183" t="n">
-        <v>15.9635372161865</v>
+        <v>15.9635353088379</v>
       </c>
       <c r="H183" t="n">
         <v>200</v>
@@ -5705,7 +5705,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G184" t="n">
-        <v>15.7340431213379</v>
+        <v>15.7340440750122</v>
       </c>
       <c r="H184" t="n">
         <v>200</v>
@@ -5792,7 +5792,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G187" t="n">
-        <v>15.6238870620728</v>
+        <v>15.6238889694214</v>
       </c>
       <c r="H187" t="n">
         <v>3500</v>
@@ -5821,7 +5821,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G188" t="n">
-        <v>15.9268178939819</v>
+        <v>15.9268169403076</v>
       </c>
       <c r="H188" t="n">
         <v>500</v>
@@ -5879,7 +5879,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G190" t="n">
-        <v>15.7799425125122</v>
+        <v>15.7799415588379</v>
       </c>
       <c r="H190" t="n">
         <v>400</v>
@@ -5937,7 +5937,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>15.9268178939819</v>
+        <v>15.9268169403076</v>
       </c>
       <c r="H192" t="n">
         <v>300</v>
@@ -6053,7 +6053,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G196" t="n">
-        <v>16.8447895050049</v>
+        <v>16.8447914123535</v>
       </c>
       <c r="H196" t="n">
         <v>1400</v>
@@ -6082,7 +6082,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G197" t="n">
-        <v>16.8539695739746</v>
+        <v>16.8539714813232</v>
       </c>
       <c r="H197" t="n">
         <v>400</v>
@@ -6169,7 +6169,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G200" t="n">
-        <v>16.349084854126</v>
+        <v>16.3490829467773</v>
       </c>
       <c r="H200" t="n">
         <v>2900</v>
@@ -6198,7 +6198,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G201" t="n">
-        <v>16.5693988800049</v>
+        <v>16.5693969726562</v>
       </c>
       <c r="H201" t="n">
         <v>2000</v>
@@ -6256,7 +6256,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>18.0840530395508</v>
+        <v>18.0840549468994</v>
       </c>
       <c r="H203" t="n">
         <v>18000</v>
@@ -6372,7 +6372,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>19.369213104248</v>
+        <v>19.3692150115967</v>
       </c>
       <c r="H207" t="n">
         <v>5100</v>
@@ -6401,7 +6401,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G208" t="n">
-        <v>18.9561252593994</v>
+        <v>18.956127166748</v>
       </c>
       <c r="H208" t="n">
         <v>1800</v>
@@ -6430,7 +6430,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G209" t="n">
-        <v>19.002025604248</v>
+        <v>19.0020236968994</v>
       </c>
       <c r="H209" t="n">
         <v>1100</v>
@@ -6459,7 +6459,7 @@
         <v>20.6800003051758</v>
       </c>
       <c r="G210" t="n">
-        <v>18.9836654663086</v>
+        <v>18.9836673736572</v>
       </c>
       <c r="H210" t="n">
         <v>900</v>
@@ -6633,7 +6633,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H216" t="n">
         <v>400</v>
@@ -6691,7 +6691,7 @@
         <v>22.1650009155273</v>
       </c>
       <c r="G218" t="n">
-        <v>20.3468551635742</v>
+        <v>20.3468532562256</v>
       </c>
       <c r="H218" t="n">
         <v>6000</v>
@@ -6720,7 +6720,7 @@
         <v>22.5249996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>20.6773242950439</v>
+        <v>20.6773223876953</v>
       </c>
       <c r="H219" t="n">
         <v>2000</v>
@@ -6778,7 +6778,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G221" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H221" t="n">
         <v>2900</v>
@@ -6894,7 +6894,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G225" t="n">
-        <v>21.1867980957031</v>
+        <v>21.1867961883545</v>
       </c>
       <c r="H225" t="n">
         <v>5500</v>
@@ -6923,7 +6923,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G226" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H226" t="n">
         <v>9100</v>
@@ -6952,7 +6952,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G227" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H227" t="n">
         <v>6900</v>
@@ -7155,7 +7155,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G234" t="n">
-        <v>21.2969551086426</v>
+        <v>21.2969570159912</v>
       </c>
       <c r="H234" t="n">
         <v>3800</v>
@@ -7213,7 +7213,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H236" t="n">
         <v>200</v>
@@ -7242,7 +7242,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G237" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H237" t="n">
         <v>115</v>
@@ -7329,7 +7329,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G240" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H240" t="n">
         <v>550</v>
@@ -7387,7 +7387,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G242" t="n">
-        <v>20.9297657012939</v>
+        <v>20.9297637939453</v>
       </c>
       <c r="H242" t="n">
         <v>1115</v>
@@ -7532,7 +7532,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G247" t="n">
-        <v>19.8281993865967</v>
+        <v>19.8282012939453</v>
       </c>
       <c r="H247" t="n">
         <v>11926</v>
@@ -7764,7 +7764,7 @@
         <v>21</v>
       </c>
       <c r="G255" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H255" t="n">
         <v>2005</v>
@@ -7851,7 +7851,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G258" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H258" t="n">
         <v>120</v>
@@ -7880,7 +7880,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G259" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H259" t="n">
         <v>745</v>
@@ -7938,7 +7938,7 @@
         <v>21</v>
       </c>
       <c r="G261" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H261" t="n">
         <v>565</v>
@@ -7967,7 +7967,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G262" t="n">
-        <v>19.53786277771</v>
+        <v>19.5378646850586</v>
       </c>
       <c r="H262" t="n">
         <v>2949</v>
@@ -7996,7 +7996,7 @@
         <v>21</v>
       </c>
       <c r="G263" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H263" t="n">
         <v>1250</v>
@@ -8025,7 +8025,7 @@
         <v>21</v>
       </c>
       <c r="G264" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H264" t="n">
         <v>6111</v>
@@ -8054,7 +8054,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G265" t="n">
-        <v>19.53786277771</v>
+        <v>19.5378646850586</v>
       </c>
       <c r="H265" t="n">
         <v>200</v>
@@ -8083,7 +8083,7 @@
         <v>21</v>
       </c>
       <c r="G266" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H266" t="n">
         <v>120</v>
@@ -8228,7 +8228,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G271" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H271" t="n">
         <v>100</v>
@@ -8257,7 +8257,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H272" t="n">
         <v>1646</v>
@@ -9272,7 +9272,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G307" t="n">
-        <v>20.2893199920654</v>
+        <v>20.2893218994141</v>
       </c>
       <c r="H307" t="n">
         <v>250</v>
@@ -9330,7 +9330,7 @@
         <v>21</v>
       </c>
       <c r="G309" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H309" t="n">
         <v>1476</v>
@@ -9359,7 +9359,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G310" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H310" t="n">
         <v>495</v>
@@ -9388,7 +9388,7 @@
         <v>21</v>
       </c>
       <c r="G311" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H311" t="n">
         <v>675</v>
@@ -9417,7 +9417,7 @@
         <v>21</v>
       </c>
       <c r="G312" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H312" t="n">
         <v>265</v>
@@ -9446,7 +9446,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G313" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H313" t="n">
         <v>3230</v>
@@ -9475,7 +9475,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G314" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H314" t="n">
         <v>320</v>
@@ -9504,7 +9504,7 @@
         <v>21</v>
       </c>
       <c r="G315" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H315" t="n">
         <v>50</v>
@@ -9533,7 +9533,7 @@
         <v>21</v>
       </c>
       <c r="G316" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H316" t="n">
         <v>465</v>
@@ -9562,7 +9562,7 @@
         <v>21</v>
       </c>
       <c r="G317" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H317" t="n">
         <v>3</v>
@@ -9591,7 +9591,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G318" t="n">
-        <v>19.3500003814697</v>
+        <v>19.3499984741211</v>
       </c>
       <c r="H318" t="n">
         <v>30</v>
@@ -9620,7 +9620,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>19.3500003814697</v>
+        <v>19.3499984741211</v>
       </c>
       <c r="H319" t="n">
         <v>326</v>
@@ -9649,7 +9649,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G320" t="n">
-        <v>19.53786277771</v>
+        <v>19.5378646850586</v>
       </c>
       <c r="H320" t="n">
         <v>422</v>
@@ -9678,7 +9678,7 @@
         <v>21</v>
       </c>
       <c r="G321" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H321" t="n">
         <v>286</v>
@@ -9707,7 +9707,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G322" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H322" t="n">
         <v>360</v>
@@ -9765,7 +9765,7 @@
         <v>21</v>
       </c>
       <c r="G324" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H324" t="n">
         <v>940</v>
@@ -9968,7 +9968,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H331" t="n">
         <v>380</v>
@@ -9997,7 +9997,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G332" t="n">
-        <v>19.3500003814697</v>
+        <v>19.3499984741211</v>
       </c>
       <c r="H332" t="n">
         <v>163</v>
@@ -10026,7 +10026,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>19.1621360778809</v>
+        <v>19.1621341705322</v>
       </c>
       <c r="H333" t="n">
         <v>9842</v>
@@ -10055,7 +10055,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G334" t="n">
-        <v>18.9742736816406</v>
+        <v>18.974271774292</v>
       </c>
       <c r="H334" t="n">
         <v>1547</v>
@@ -10084,7 +10084,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>18.9742736816406</v>
+        <v>18.974271774292</v>
       </c>
       <c r="H335" t="n">
         <v>4339</v>
@@ -10113,7 +10113,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G336" t="n">
-        <v>18.9742736816406</v>
+        <v>18.974271774292</v>
       </c>
       <c r="H336" t="n">
         <v>4539</v>
@@ -10142,7 +10142,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>19.1621360778809</v>
+        <v>19.1621341705322</v>
       </c>
       <c r="H337" t="n">
         <v>1942</v>
@@ -10171,7 +10171,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G338" t="n">
-        <v>19.1621360778809</v>
+        <v>19.1621341705322</v>
       </c>
       <c r="H338" t="n">
         <v>284</v>
@@ -10200,7 +10200,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G339" t="n">
-        <v>19.3500003814697</v>
+        <v>19.3499984741211</v>
       </c>
       <c r="H339" t="n">
         <v>2218</v>
@@ -10229,7 +10229,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>19.53786277771</v>
+        <v>19.5378646850586</v>
       </c>
       <c r="H340" t="n">
         <v>5407</v>
@@ -10258,7 +10258,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G341" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H341" t="n">
         <v>3251</v>
@@ -10316,7 +10316,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G343" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H343" t="n">
         <v>100</v>
@@ -10345,7 +10345,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H344" t="n">
         <v>33</v>
@@ -10432,7 +10432,7 @@
         <v>21</v>
       </c>
       <c r="G347" t="n">
-        <v>19.7257270812988</v>
+        <v>19.7257289886475</v>
       </c>
       <c r="H347" t="n">
         <v>1330</v>
@@ -10461,7 +10461,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H348" t="n">
         <v>928</v>
@@ -10490,7 +10490,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G349" t="n">
-        <v>19.9135913848877</v>
+        <v>19.9135932922363</v>
       </c>
       <c r="H349" t="n">
         <v>1366</v>
@@ -10519,7 +10519,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G350" t="n">
-        <v>20.2893199920654</v>
+        <v>20.2893218994141</v>
       </c>
       <c r="H350" t="n">
         <v>18012</v>
@@ -10722,7 +10722,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>20.2893199920654</v>
+        <v>20.2893218994141</v>
       </c>
       <c r="H357" t="n">
         <v>291</v>
@@ -11070,7 +11070,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>23.1072826385498</v>
+        <v>23.1072807312012</v>
       </c>
       <c r="H369" t="n">
         <v>15210</v>
@@ -11534,7 +11534,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G385" t="n">
-        <v>24.6101932525635</v>
+        <v>24.6101951599121</v>
       </c>
       <c r="H385" t="n">
         <v>9687</v>
@@ -11882,7 +11882,7 @@
         <v>26</v>
       </c>
       <c r="G397" t="n">
-        <v>24.4223289489746</v>
+        <v>24.4223308563232</v>
       </c>
       <c r="H397" t="n">
         <v>777</v>
@@ -11911,7 +11911,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>24.6101932525635</v>
+        <v>24.6101951599121</v>
       </c>
       <c r="H398" t="n">
         <v>1281</v>
@@ -11969,7 +11969,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G400" t="n">
-        <v>25.737377166748</v>
+        <v>25.7373790740967</v>
       </c>
       <c r="H400" t="n">
         <v>3487</v>
@@ -12085,7 +12085,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>24.798059463501</v>
+        <v>24.7980575561523</v>
       </c>
       <c r="H404" t="n">
         <v>285</v>
@@ -12172,7 +12172,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G407" t="n">
-        <v>24.798059463501</v>
+        <v>24.7980575561523</v>
       </c>
       <c r="H407" t="n">
         <v>658</v>
@@ -12230,7 +12230,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G409" t="n">
-        <v>23.29514503479</v>
+        <v>23.2951431274414</v>
       </c>
       <c r="H409" t="n">
         <v>3492</v>
@@ -12317,7 +12317,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>24.2344646453857</v>
+        <v>24.2344665527344</v>
       </c>
       <c r="H412" t="n">
         <v>600</v>
@@ -12404,7 +12404,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G415" t="n">
-        <v>24.2344646453857</v>
+        <v>24.2344665527344</v>
       </c>
       <c r="H415" t="n">
         <v>140</v>
@@ -12433,7 +12433,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G416" t="n">
-        <v>24.2344646453857</v>
+        <v>24.2344665527344</v>
       </c>
       <c r="H416" t="n">
         <v>87</v>
@@ -12520,7 +12520,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G419" t="n">
-        <v>23.29514503479</v>
+        <v>23.2951431274414</v>
       </c>
       <c r="H419" t="n">
         <v>210</v>
@@ -12578,7 +12578,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>23.29514503479</v>
+        <v>23.2951431274414</v>
       </c>
       <c r="H421" t="n">
         <v>2392</v>
@@ -12723,7 +12723,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G426" t="n">
-        <v>24.6101932525635</v>
+        <v>24.6101951599121</v>
       </c>
       <c r="H426" t="n">
         <v>3659</v>
@@ -12781,7 +12781,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>24.798059463501</v>
+        <v>24.7980575561523</v>
       </c>
       <c r="H428" t="n">
         <v>4557</v>
@@ -12984,7 +12984,7 @@
         <v>26</v>
       </c>
       <c r="G435" t="n">
-        <v>24.4223289489746</v>
+        <v>24.4223308563232</v>
       </c>
       <c r="H435" t="n">
         <v>16881</v>
@@ -13071,7 +13071,7 @@
         <v>26</v>
       </c>
       <c r="G438" t="n">
-        <v>24.4223289489746</v>
+        <v>24.4223308563232</v>
       </c>
       <c r="H438" t="n">
         <v>193</v>
@@ -13129,7 +13129,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G440" t="n">
-        <v>24.798059463501</v>
+        <v>24.7980575561523</v>
       </c>
       <c r="H440" t="n">
         <v>111</v>
@@ -13564,7 +13564,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>24.6101932525635</v>
+        <v>24.6101951599121</v>
       </c>
       <c r="H455" t="n">
         <v>1466</v>
@@ -13651,7 +13651,7 @@
         <v>26</v>
       </c>
       <c r="G458" t="n">
-        <v>24.4223289489746</v>
+        <v>24.4223308563232</v>
       </c>
       <c r="H458" t="n">
         <v>809</v>
@@ -13738,7 +13738,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G461" t="n">
-        <v>23.1072826385498</v>
+        <v>23.1072807312012</v>
       </c>
       <c r="H461" t="n">
         <v>2523</v>
@@ -13767,7 +13767,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>19.53786277771</v>
+        <v>19.5378646850586</v>
       </c>
       <c r="H462" t="n">
         <v>4429</v>
@@ -13883,7 +13883,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G466" t="n">
-        <v>18.410680770874</v>
+        <v>18.4106788635254</v>
       </c>
       <c r="H466" t="n">
         <v>944</v>
@@ -14028,7 +14028,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G471" t="n">
-        <v>16.1563129425049</v>
+        <v>16.1563110351562</v>
       </c>
       <c r="H471" t="n">
         <v>2772</v>
@@ -14202,7 +14202,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G477" t="n">
-        <v>14.2776689529419</v>
+        <v>14.2776699066162</v>
       </c>
       <c r="H477" t="n">
         <v>1705</v>
@@ -14231,7 +14231,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G478" t="n">
-        <v>14.2776689529419</v>
+        <v>14.2776699066162</v>
       </c>
       <c r="H478" t="n">
         <v>1810</v>
@@ -14260,7 +14260,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G479" t="n">
-        <v>13.9958734512329</v>
+        <v>13.9958724975586</v>
       </c>
       <c r="H479" t="n">
         <v>200</v>
@@ -14347,7 +14347,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>15.6866512298584</v>
+        <v>15.6866502761841</v>
       </c>
       <c r="H482" t="n">
         <v>4167</v>
@@ -14376,7 +14376,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>15.6866512298584</v>
+        <v>15.6866502761841</v>
       </c>
       <c r="H483" t="n">
         <v>3514</v>
@@ -14492,7 +14492,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G487" t="n">
-        <v>16.1563129425049</v>
+        <v>16.1563110351562</v>
       </c>
       <c r="H487" t="n">
         <v>12961</v>
@@ -14579,7 +14579,7 @@
         <v>17.25</v>
       </c>
       <c r="G490" t="n">
-        <v>16.203275680542</v>
+        <v>16.2032775878906</v>
       </c>
       <c r="H490" t="n">
         <v>6624</v>
@@ -14695,7 +14695,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>15.6866512298584</v>
+        <v>15.6866502761841</v>
       </c>
       <c r="H494" t="n">
         <v>5139</v>
@@ -14753,7 +14753,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G496" t="n">
-        <v>16.1563129425049</v>
+        <v>16.1563110351562</v>
       </c>
       <c r="H496" t="n">
         <v>3600</v>
@@ -14811,7 +14811,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G498" t="n">
-        <v>15.6866512298584</v>
+        <v>15.6866502761841</v>
       </c>
       <c r="H498" t="n">
         <v>7270</v>
@@ -14927,7 +14927,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G502" t="n">
-        <v>16.8138332366943</v>
+        <v>16.813835144043</v>
       </c>
       <c r="H502" t="n">
         <v>3773</v>
@@ -15130,7 +15130,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G509" t="n">
-        <v>17.2365283966064</v>
+        <v>17.2365303039551</v>
       </c>
       <c r="H509" t="n">
         <v>1503</v>
@@ -15159,7 +15159,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G510" t="n">
-        <v>17.1895637512207</v>
+        <v>17.1895618438721</v>
       </c>
       <c r="H510" t="n">
         <v>255</v>
@@ -15217,7 +15217,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G512" t="n">
-        <v>16.7668704986572</v>
+        <v>16.7668685913086</v>
       </c>
       <c r="H512" t="n">
         <v>1779</v>
@@ -15246,7 +15246,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G513" t="n">
-        <v>16.7668704986572</v>
+        <v>16.7668685913086</v>
       </c>
       <c r="H513" t="n">
         <v>40</v>
@@ -15333,7 +15333,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>17.1895637512207</v>
+        <v>17.1895618438721</v>
       </c>
       <c r="H516" t="n">
         <v>1360</v>
@@ -15391,7 +15391,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G518" t="n">
-        <v>17.2365283966064</v>
+        <v>17.2365303039551</v>
       </c>
       <c r="H518" t="n">
         <v>1647</v>
@@ -15594,7 +15594,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G525" t="n">
-        <v>18.1288833618164</v>
+        <v>18.1288814544678</v>
       </c>
       <c r="H525" t="n">
         <v>5337</v>
@@ -15855,7 +15855,7 @@
         <v>19</v>
       </c>
       <c r="G534" t="n">
-        <v>17.8470859527588</v>
+        <v>17.8470878601074</v>
       </c>
       <c r="H534" t="n">
         <v>4414</v>
@@ -15884,7 +15884,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>18.410680770874</v>
+        <v>18.4106788635254</v>
       </c>
       <c r="H535" t="n">
         <v>1991</v>
@@ -15942,7 +15942,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>17.1895637512207</v>
+        <v>17.1895618438721</v>
       </c>
       <c r="H537" t="n">
         <v>7342</v>
@@ -15971,7 +15971,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>17.4243907928467</v>
+        <v>17.4243927001953</v>
       </c>
       <c r="H538" t="n">
         <v>589</v>
@@ -16029,7 +16029,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G540" t="n">
-        <v>17.2365283966064</v>
+        <v>17.2365303039551</v>
       </c>
       <c r="H540" t="n">
         <v>1317</v>
@@ -16087,7 +16087,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>16.8138332366943</v>
+        <v>16.813835144043</v>
       </c>
       <c r="H542" t="n">
         <v>756</v>
@@ -16116,7 +16116,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G543" t="n">
-        <v>17.2365283966064</v>
+        <v>17.2365303039551</v>
       </c>
       <c r="H543" t="n">
         <v>668</v>
@@ -16145,7 +16145,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G544" t="n">
-        <v>17.4243907928467</v>
+        <v>17.4243927001953</v>
       </c>
       <c r="H544" t="n">
         <v>800</v>
@@ -16174,7 +16174,7 @@
         <v>18.5</v>
       </c>
       <c r="G545" t="n">
-        <v>17.3774280548096</v>
+        <v>17.3774261474609</v>
       </c>
       <c r="H545" t="n">
         <v>23094</v>
@@ -16203,7 +16203,7 @@
         <v>19</v>
       </c>
       <c r="G546" t="n">
-        <v>17.8470859527588</v>
+        <v>17.8470878601074</v>
       </c>
       <c r="H546" t="n">
         <v>250</v>
@@ -16261,7 +16261,7 @@
         <v>18.5</v>
       </c>
       <c r="G548" t="n">
-        <v>17.3774280548096</v>
+        <v>17.3774261474609</v>
       </c>
       <c r="H548" t="n">
         <v>1240</v>
@@ -16812,7 +16812,7 @@
         <v>15.75</v>
       </c>
       <c r="G567" t="n">
-        <v>14.7942953109741</v>
+        <v>14.7942962646484</v>
       </c>
       <c r="H567" t="n">
         <v>14601</v>
@@ -17189,7 +17189,7 @@
         <v>15.75</v>
       </c>
       <c r="G580" t="n">
-        <v>14.7942953109741</v>
+        <v>14.7942962646484</v>
       </c>
       <c r="H580" t="n">
         <v>8207</v>
@@ -17247,7 +17247,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>14.4655332565308</v>
+        <v>14.4655342102051</v>
       </c>
       <c r="H582" t="n">
         <v>1389</v>
@@ -17450,7 +17450,7 @@
         <v>15.75</v>
       </c>
       <c r="G589" t="n">
-        <v>14.7942953109741</v>
+        <v>14.7942962646484</v>
       </c>
       <c r="H589" t="n">
         <v>4722</v>
@@ -17508,7 +17508,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G591" t="n">
-        <v>14.4655332565308</v>
+        <v>14.4655342102051</v>
       </c>
       <c r="H591" t="n">
         <v>6347</v>
@@ -17566,7 +17566,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G593" t="n">
-        <v>14.1837377548218</v>
+        <v>14.1837387084961</v>
       </c>
       <c r="H593" t="n">
         <v>6222</v>
@@ -17595,7 +17595,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G594" t="n">
-        <v>13.9958734512329</v>
+        <v>13.9958724975586</v>
       </c>
       <c r="H594" t="n">
         <v>11633</v>
@@ -17624,7 +17624,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G595" t="n">
-        <v>14.0428400039673</v>
+        <v>14.042839050293</v>
       </c>
       <c r="H595" t="n">
         <v>5431</v>
@@ -17653,7 +17653,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G596" t="n">
-        <v>13.9019422531128</v>
+        <v>13.9019412994385</v>
       </c>
       <c r="H596" t="n">
         <v>7311</v>
@@ -17711,7 +17711,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>13.9019422531128</v>
+        <v>13.9019412994385</v>
       </c>
       <c r="H598" t="n">
         <v>6014</v>
@@ -17769,7 +17769,7 @@
         <v>14.5</v>
       </c>
       <c r="G600" t="n">
-        <v>13.6201457977295</v>
+        <v>13.6201448440552</v>
       </c>
       <c r="H600" t="n">
         <v>17122</v>
@@ -62783,6 +62783,35 @@
         <v>731357</v>
       </c>
       <c r="I2152" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2153" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2153" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2153" t="n">
+        <v>25</v>
+      </c>
+      <c r="E2153" t="n">
+        <v>23.7000007629395</v>
+      </c>
+      <c r="F2153" t="n">
+        <v>24</v>
+      </c>
+      <c r="G2153" t="n">
+        <v>24</v>
+      </c>
+      <c r="H2153" t="n">
+        <v>42134</v>
+      </c>
+      <c r="I2153" t="s">
         <v>9</v>
       </c>
     </row>
